--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\tsclient\D\test-site — копия BackUp\workhouse\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78CC3675-9493-4BC2-820B-DB29FB41BFFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303B01A-3E7B-4D9A-8B70-1A5313677BE8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="756">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -1728,9 +1728,6 @@
     <t>Наконечники для підкачування шин</t>
   </si>
   <si>
-    <t>Наконечник для підкачування шин із затискним важелем та виходом «ялинка»</t>
-  </si>
-  <si>
     <t>Наконечник затискний важелевого типу для швидкого та герметичного приєднання пневматичних шлангів до
 вентилів автомобільних шин. Завдяки затискному механізму забезпечує надійну фіксацію на вентилі однією
 рукою, що значно спрощує процес накачування та контроль тиску.
@@ -2551,9 +2548,6 @@
     <t>child1_13.jpg</t>
   </si>
   <si>
-    <t>Кран запірний кульовий з двома приєднаннями із зовнішньою різьбою</t>
-  </si>
-  <si>
     <t>Кран запірний кульовий з двома приєднаннями із зовнішньою різьбою призначений для оперативного
 перекриття потоків рідин та стисненого повітря в трубопровідних системах.
 Особливості та властивості:
@@ -2650,16 +2644,6 @@
     <t>Штекер прямий паливного швидкороз’ємного з’єднання зі штуцером «ялинка» (відповідає SAE J2044)</t>
   </si>
   <si>
-    <t>Штекер прямий паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» (відповідає SAE J2044).
-Призначений для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
-його парів, а також для швидкого з’єднання з відповідним гніздом.
-Особливості та властивості:
-1. Матеріал штекера — поліамід РА12
-2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
-3. Номінальний робочий тиск — 5 бар
-4. Еластичний ущільнювач — NBR, FPM</t>
-  </si>
-  <si>
     <t>child3_small_137.jpg</t>
   </si>
   <si>
@@ -2669,16 +2653,6 @@
     <t>Гніздо пряме паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» (відповідає SAE J2044)</t>
   </si>
   <si>
-    <t>Гніздо пряме паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» (відповідає SAE J2044).
-Призначене для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
-його парів, а також для швидкого з’єднання з відповідним штекером.
-Особливості та властивості:
-1. Матеріал штекера — поліамід РА12
-2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
-3. Номінальний робочий тиск — 5 бар
-4. Еластичний ущільнювач — NBR, FPM</t>
-  </si>
-  <si>
     <t>child3_small_138.jpg</t>
   </si>
   <si>
@@ -2686,16 +2660,6 @@
   </si>
   <si>
     <t>Гніздо кутове паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» (відповідає SAE J2044)</t>
-  </si>
-  <si>
-    <t>Гніздо кутове паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» (відповідає SAE J2044).
-Призначене для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
-його парів, а також для швидкого з’єднання з відповідним штекером.
-Особливості та властивості:
-1. Матеріал штекера — поліамід РА12
-2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
-3. Номінальний робочий тиск — 5 бар
-4. Еластичний ущільнювач — NBR, FPM</t>
   </si>
   <si>
     <t>child3_small_139.jpg</t>
@@ -2922,40 +2886,10 @@
     <t>child3_big_150.jpg</t>
   </si>
   <si>
-    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом та двома штуцерами типу «ялинка» (відповідає SAE J2044)</t>
-  </si>
-  <si>
-    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом та двома штуцерами типу «ялинка», що
-відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
-системах подачі бензину, дизельного палива та його парів.
-Комбіноване виконання з одним гніздом та двома штуцерами типу «ялинка» забезпечує можливість
-швидкороз’ємного підключення до штатного штекера магістралі з одночасним розведенням потоку на два
-додаткових рукави або трубки відповідного внутрішнього діаметра.
-Особливості та властивості:
-1. Матеріал штекера — поліамід РА12
-2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
-3. Номінальний робочий тиск — 5 бар
-4. Еластичний ущільнювач — NBR, FPM
-5. Орієнтація багатоступеневих штуцерів — кутова (90°)</t>
-  </si>
-  <si>
     <t>child3_small_151.jpg</t>
   </si>
   <si>
     <t>child3_big_151.jpg</t>
-  </si>
-  <si>
-    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом і штекером та штуцером типу «ялинка»,
-що відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
-системах подачі бензину, дизельного палива та його парів.
-Комбіноване виконання з гніздом, штекером і штуцером типу «ялинка» забезпечує швидкороз’ємне
-підключення магістралі та додаткове приєднання рукава або трубки відповідного внутрішнього діаметра.
-Особливості та властивості:
-1. Матеріал штекера — поліамід РА12
-2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
-3. Номінальний робочий тиск — 5 бар
-4. Еластичний ущільнювач — NBR, FPM
-5. Орієнтація гніздо-штекер — прямолінійна (180°)</t>
   </si>
   <si>
     <t>child3_small_152.jpg</t>
@@ -3460,6 +3394,304 @@
   </si>
   <si>
     <t>child3_big_96а.jpg</t>
+  </si>
+  <si>
+    <t>Ніпель редукційний різьбовий для пневмо- та гідросистем з різними типами різьблення</t>
+  </si>
+  <si>
+    <t>З’єднувач різьбовий редукційний (ніпель) для пневмо- та гідросистем
+Високоякісний сполучний елемент, призначений для швидкого та надійного з’єднання елементів трубопроводів, шлангів, гідравлічних вузлів та пневматичних компонентів, що мають різьбові виходи різних діаметрів.Завдяки редукційній конструкції, виріб забезпечує плавний та герметичний перехід між лініями високого чи низького тиску з різними типорозмірами різьблення.
+Особливості та властивості:Надійний матеріал: Виготовлений із високоякісної латуні, що гарантує стійкість до корозії, температурних коливань та механічних навантажень.
+Повна герметичність: Оснащений еластичним ущільнювальним гумовим кільцем (O-ring), яке запобігає витоку повітря, мастила чи робочої рідини навіть в умовах вібрації.
+Надійна фіксація: Додаткова контргайка у комплекті дозволяє міцно зафіксувати ніпель у потрібному положенні та захищає від самовільного розкручування.
+Універсальність: Підходить для використання як у мобільній техніці (пневмосистеми вантажівок, причепів, спецтехніки), так і в промисловому гідравлічному обладнанні.</t>
+  </si>
+  <si>
+    <t>child3_small_99.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_99.jpg</t>
+  </si>
+  <si>
+    <t>Ніпель редукційний з внутрішньою та зовнішньою різьбою для пневмо- та гідросистем</t>
+  </si>
+  <si>
+    <t>Ніпель редукційний з внутрішньою та зовнішньою різьбою для пневмо- та гідросистем
+Надійний і функціональний сполучний елемент (перехідник), призначений для герметичного з’єднання вузлів, агрегатів та магістралей, які мають різьбові виходи різних діаметрів і типів.
+Завдяки комбінації внутрішньої та зовнішньої різьби, цей редукційний ніпель дозволяє швидко адаптувати пневматичні та гідравлічні лінії під потрібний розмір без необхідності заміни дорогих вузлів системи.
+Особливості та властивості:Комбіноване різьблення: Наявність зовнішньої різьби з одного боку та внутрішньої з іншого забезпечує універсальність монтажу та дозволяє легко переходити з більшого діаметра на менший (і навпаки).
+Преміум-матеріал: Виготовлений із високоякісної латуні, що гарантує абсолютну стійкість до корозії, хімічних сполук, різких перепадів температур та високого тиску.
+Максимальна герметичність: До комплекту входить еластичне гумове ущільнювальне кільце круглого перерізу (O-ring). Воно повністю виключає ризик витоку стисненого повітря, робочих рідин або мастила.
+Надійна фіксація: Оснащений міцною металевою контргайкою, яка жорстко фіксує ніпель у корпусі чи панелі (перебірці) та захищає з'єднання від самовільного розкручування під впливом постійних вібрацій вантажівки чи обладнання.
+Технічні характеристики групи:Робоче середовище: Стиснене повітря, мінеральні оливи, дизельне пальне, вода, гідравлічні рідини.
+Матеріал корпусу: Латунь.Матеріал контргайки: Сталь із захисним покриттям або латунь.
+Ущільнення: Маслобензостійка гума (NBR) / Viton.
+Сфера застосування: Пневматичні гальмівні системи та підвіска вантажних автомобілів, причепів, напівпричепів (DAF, MAN, Scania, Volvo, Mercedes-Benz, Schmitz, Krone), спецтехніка, а також промислове гідравлічне обладнання</t>
+  </si>
+  <si>
+    <t>child3_small_100.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_100.jpg</t>
+  </si>
+  <si>
+    <t>З’єднувач кутовий з внутрішньою та зовнішньою різьбою для пневмо- та гідросистем</t>
+  </si>
+  <si>
+    <t>З’єднувач кутовий (коліно редукційне) з внутрішньою та зовнішньою різьбою для пневмо- та гідросистем
+Всокоякісний кутовий сполучний елемент (перехідник), призначений для герметичного з’єднання магістралей, вузлів та компонентів під кутом. Завдяки кутовій конструкції, цей штуцер дозволяє компактно та безпечно прокладати трубопроводи у місцях з обмеженим простором, запобігаючи зламам і перегинам шлангів.Поєднання зовнішньої різьби великого діаметра та внутрішньої різьби меншого розміру забезпечує плавний і надійний редукційний перехід між лініями високого або низького тиску з різними типорозмірами.
+Особливості та властивості:Кутова конструкція (90°): Забезпечує оптимальний радіус повороту пневматичних чи гідравлічних ліній, що дозволяє суттєво економити монтажний простір.
+Преміум-матеріал: Виготовлений із міцного металу (латунь/конструкційна сталь з антикорозійним покриттям), що гарантує стійкість до механічних пошкоджень, високого тиску та температурних коливань.
+Максимальна герметичність: Точність виконання різьбових з'єднань мінімізує ризики витоку стисненого повітря або робочих рідин навіть в умовах підвищеної вібрації.
+Універсальність монтажу: Підходить для використання як перебіркова деталь (через технологічні отвори панелей) для надійної жорсткої фіксації магістралей.</t>
+  </si>
+  <si>
+    <t>child3_small_101.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_101.jpg</t>
+  </si>
+  <si>
+    <t>З’єднувач кутовий з внутрішньою та зовнішньою різьбою для пневмо- та гідросистем
+Високоякісний сполучний елемент (перехідник), призначений для надійного та герметичного з’єднання магістралей, вузлів та компонентів під кутом. Завдяки кутовій конструкції (90°), цей штуцер дозволяє компактно та безпечно прокладати трубопроводи у місцях з обмеженим простором, повністю запобігаючи зламам, перегинам та передчасному зносу шлангів і трубок.
+Рівнопрохідна конструкція із зовнішньою та внутрішньою різьбою однакового діаметра забезпечує стабільний потік робочого середовища без зміни тиску в лінії та спрощує монтаж систем у важкодоступних зонах.
+Особливості та властивості:Кутова конструкція: Забезпечує оптимальний і безпечний поворот пневматичних чи гідравлічних ліній, що дозволяє суттєво економити монтажний простір вантажівки чи обладнання.
+Преміум-матеріал: Виготовлений із міцного металу із захисним антикорозійним покриттям, що гарантує високу стійкість до механічних навантажень, високого тиску та різких температурних коливань.
+Максимальна герметичність: Висока точність виконання різьбових з'єднань повністю мінімізує ризики витоку стисненого повітря, робочих рідин або мастила в умовах постійної лінійної вібрації.
+Зручність монтажу: Універсальна комбінація внутрішньої та зовнішньої різьби дозволяє використовувати деталь як прямий кутовий перехідник або в перегородках (перебірках) для жорсткої фіксації ліній.</t>
+  </si>
+  <si>
+    <t>child3_small_102.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_102.jpg</t>
+  </si>
+  <si>
+    <t>child1_17.jpg</t>
+  </si>
+  <si>
+    <t>Швидкороз'ємні з'єднання систем SCR (AdBlue/DEF) за стандартом SAE J2044</t>
+  </si>
+  <si>
+    <t>Гніздо пряме швидкороз’ємного з’єднання систем подачі AdBlue/DEF зі штуцером типу «ялинка» (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Гніздо пряме швидкороз’ємного з’єднання систем подачі AdBlue/DEF та охолодження зі штуцером типу «ялинка»
+(відповідає SAE J2044). Призначене для герметичного підключення рукавів або трубок у системах подачі
+AdBlue/DEF і циркуляції охолоджувальної рідини, а також для швидкого з’єднання з відповідним штекером.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — EPDM</t>
+  </si>
+  <si>
+    <t>child3_small_170.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_170.jpg</t>
+  </si>
+  <si>
+    <t>Гніздо кутове 45° швидкороз’ємного з’єднання систем подачі AdBlue/DEF зі штуцером типу «ялинка» (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Гніздо кутове 45° швидкороз’ємного з’єднання систем подачі AdBlue/DEF та охолодження зі штуцером типу
+«ялинка» (відповідає SAE J2044). Призначене для герметичного підключення рукавів або трубок у системах подачі
+AdBlue/DEF і циркуляції охолоджувальної рідини, а також для швидкого з’єднання з відповідним штекером.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — EPDM</t>
+  </si>
+  <si>
+    <t>child3_small_171.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_171.jpg</t>
+  </si>
+  <si>
+    <t>Гніздо кутове 90° швидкороз’ємного з’єднання систем подачі AdBlue/DEF зі штуцером типу «ялинка» (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Гніздо кутове 90° швидкороз’ємного з’єднання систем подачі AdBlue/DEF та охолодження зі штуцером типу
+«ялинка» (відповідає SAE J2044). Призначене для герметичного підключення рукавів або трубок у системах подачі
+AdBlue/DEF і циркуляції охолоджувальної рідини, а також для швидкого з’єднання з відповідним штекером.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — EPDM</t>
+  </si>
+  <si>
+    <t>child3_small_172.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_172.jpg</t>
+  </si>
+  <si>
+    <t>child3_small_173.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_173.jpg</t>
+  </si>
+  <si>
+    <t>child3_small_174.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_174.jpg</t>
+  </si>
+  <si>
+    <t>Штекер прямий паливного швидкороз’ємного з’єднання зі штуцером «ялинка» з ущільненням (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Штекер прямий паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» з ущільненням (відповідає SAE J2044).
+Призначений для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
+його парів, а також для швидкого з’єднання з відповідним гніздом.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM</t>
+  </si>
+  <si>
+    <t>Гніздо пряме паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» з ущільненням (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Гніздо пряме паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» з ущільненням (відповідає SAE J2044).
+Призначене для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
+його парів, а також для швидкого з’єднання з відповідним штекером.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM</t>
+  </si>
+  <si>
+    <t>Гніздо кутове паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» з ущільненням (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Гніздо кутове паливного швидкороз’ємного з’єднання зі штуцером типу «ялинка» з ущільненням (відповідає SAE J2044).
+Призначене для герметичного підключення рукавів або трубок у системах подачі бензину, дизельного палива та
+його парів, а також для швидкого з’єднання з відповідним штекером.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом і штекером (збільшена довжина) та штуцером типу «ялинка» (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом і штекером (збільшена довжина) та штуцером типу «ялинка»,
+що відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
+системах подачі бензину, дизельного палива та його парів.
+Комбіноване виконання з гніздом, штекером і штуцером типу «ялинка» забезпечує швидкороз’ємне
+підключення магістралі та додаткове приєднання рукава або трубки відповідного внутрішнього діаметра.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM
+5. Орієнтація гніздо-штекер — прямолінійна (180°)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом та двома штуцерами типу «ялинка» з ущільненням (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом та двома штуцерами типу «ялинка» з ущільненням , що
+відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
+системах подачі бензину, дизельного палива та його парів.
+Комбіноване виконання з одним гніздом та двома штуцерами типу «ялинка» забезпечує можливість
+швидкороз’ємного підключення до штатного штекера магістралі з одночасним розведенням потоку на два
+додаткових рукави або трубки відповідного внутрішнього діаметра.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM
+5. Орієнтація багатоступеневих штуцерів — кутова (90°)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом і штекером та штуцером типу «ялинка» з ущільненням (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з гніздом і штекером та штуцером типу «ялинка»  з ущільненням,
+що відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
+системах подачі бензину, дизельного палива та його парів.
+Комбіноване виконання з гніздом, штекером і штуцером типу «ялинка» забезпечує швидкороз’ємне
+підключення магістралі та додаткове приєднання рукава або трубки відповідного внутрішнього діаметра.
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM
+5. Орієнтація гніздо-штекер — прямолінійна (180°)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з штекером і гніздом та штуцером типу «ялинка» (відповідає SAE J2044)</t>
+  </si>
+  <si>
+    <t>Трійник паливного швидкороз’ємного з’єднання комбінований з штекером і гніздом та штуцером типу «ялинка»,
+що відповідає SAE J2044, призначений для герметичного з’єднання та розгалуження паливних магістралей у
+системах подачі бензину, дизельного палива та його парів.
+Комбіноване виконання з гніздом, штекером і штуцером типу «ялинка» забезпечує швидкороз’ємне
+підключення магістралі та додаткове приєднання рукава або трубки відповідного внутрішнього діаметра.
+Спеціальний багатоступеневий профіль штуцера «ялинка» розроблений для прямого монтажу поліамідних
+трубок без використання додаткових ущільнювачів, що відповідає стандартам конвеєрної збірки (OEM).
+Особливості та властивості:
+1. Матеріал штекера — поліамід РА12
+2. Діапазон робочих температур — від - 40°C до +100°C, з піковою температурою до +130°C
+3. Номінальний робочий тиск — 5 бар
+4. Еластичний ущільнювач — NBR, FPM
+5. Орієнтація гніздо-штекер — кутова (90°)</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий з двома приєднаннями із зовнішньою різьбою, керувальна ручка (флажок) з пластику</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий з двома приєднаннями із зовнішньою різьбою, ручка-важіль із алюмінію</t>
+  </si>
+  <si>
+    <t>Наконечник для підкачування шин із затискним важелем та прямим виходом «ялинка» латунний</t>
+  </si>
+  <si>
+    <t>Наконечник для підкачування шин із затискним важелем та прямим виходом «ялинка» алюмінієвий</t>
+  </si>
+  <si>
+    <t>Наконечник для підкачування шин із затискним металевим важелем та кутовим виходом «ялинка»</t>
+  </si>
+  <si>
+    <t>Наконечник для підкачування шин із затискним пластиковим важелем та кутовим виходом «ялинка»</t>
+  </si>
+  <si>
+    <t>З'єднувач пневматичний прямий цанговий подовжений</t>
+  </si>
+  <si>
+    <t>З'єднувач перехідний пневматичний прямий із цанговим приєднанням та зовнішньою різьбою подовжений</t>
+  </si>
+  <si>
+    <t>З'єднувач пневматичний перехідний Т-подібний із самозамикаючою швидкороз'ємною муфтою та двома прямими цанговими виходами</t>
+  </si>
+  <si>
+    <t>Швидкорознімний тристоронній пневматичний з’єднувач Т-подібної форми із самозапірною швидкорознімною
+муфтою та двома прямими цанговими виходами для пластикових трубок призначений для швидкого підключення
+пневматичних магістралей до різних пневматичних вузлів та агрегатів.
+Фіксація трубки здійснюється цанговим затискним механізмом, який надійно утримує її в зоні герметичного
+ущільнення. Вбудована розпірна (розблокувальна) втулка при натисканні розтискає цанговий елемент і
+забезпечує безпечне та швидке вилучення трубки.
+Швидкорознімна муфта оснащена самозапірним клапанним механізмом, що автоматично перекриває потік
+повітря при роз’єднанні та запобігає витоку робочого середовища.
+Конструкція забезпечує стабільну герметичність з’єднання, зберігає геометрію трубки без її деформації та
+допускає багаторазове використання з’єднувача.
+Особливості та властивості:
+1. Матеріал корпусу цангового з'єднувача та розпірної втулки — пластик
+2. Матеріал цангового механізму — алюміній
+3. Матеріал ущільнювального кільця — NBR (бутадієн-нітрильний каучук)
+4. Матеріал быстроразъемной муфти — алюміній
+5. Розташування цангових виводів — пряме
+6. Виконання быстроразъемной муфти — євро тип (Euro-type)</t>
   </si>
 </sst>
 </file>
@@ -3496,14 +3728,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3819,8 +4048,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="9" max="9" width="48.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3850,7 +4084,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3914,7 +4148,7 @@
       <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3946,7 +4180,7 @@
       <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3978,7 +4212,7 @@
       <c r="I5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4010,7 +4244,7 @@
       <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4042,7 +4276,7 @@
       <c r="I7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4074,7 +4308,7 @@
       <c r="I8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4106,7 +4340,7 @@
       <c r="I9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4138,7 +4372,7 @@
       <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4170,7 +4404,7 @@
       <c r="I11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4202,7 +4436,7 @@
       <c r="I12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4234,7 +4468,7 @@
       <c r="I13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4266,7 +4500,7 @@
       <c r="I14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4290,15 +4524,15 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>63</v>
+        <v>754</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>64</v>
+        <v>755</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4330,7 +4564,7 @@
       <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4362,7 +4596,7 @@
       <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4394,7 +4628,7 @@
       <c r="I18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4426,7 +4660,7 @@
       <c r="I19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4458,7 +4692,7 @@
       <c r="I20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4490,7 +4724,7 @@
       <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4522,7 +4756,7 @@
       <c r="I22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4554,7 +4788,7 @@
       <c r="I23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4586,7 +4820,7 @@
       <c r="I24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -4618,7 +4852,7 @@
       <c r="I25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -4650,7 +4884,7 @@
       <c r="I26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4682,7 +4916,7 @@
       <c r="I27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -4714,7 +4948,7 @@
       <c r="I28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4746,7 +4980,7 @@
       <c r="I29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>119</v>
       </c>
     </row>
@@ -4778,7 +5012,7 @@
       <c r="I30" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4810,7 +5044,7 @@
       <c r="I31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4842,7 +5076,7 @@
       <c r="I32" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1" t="s">
         <v>130</v>
       </c>
     </row>
@@ -4874,7 +5108,7 @@
       <c r="I33" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4906,7 +5140,7 @@
       <c r="I34" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4938,7 +5172,7 @@
       <c r="I35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4970,7 +5204,7 @@
       <c r="I36" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5002,11 +5236,11 @@
       <c r="I37" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -5016,7 +5250,7 @@
       <c r="C38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -5034,7 +5268,7 @@
       <c r="I38" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -5066,7 +5300,7 @@
       <c r="I39" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5098,7 +5332,7 @@
       <c r="I40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5130,7 +5364,7 @@
       <c r="I41" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5162,7 +5396,7 @@
       <c r="I42" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5194,7 +5428,7 @@
       <c r="I43" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5226,7 +5460,7 @@
       <c r="I44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5258,7 +5492,7 @@
       <c r="I45" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5290,7 +5524,7 @@
       <c r="I46" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5322,7 +5556,7 @@
       <c r="I47" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>202</v>
       </c>
     </row>
@@ -5354,7 +5588,7 @@
       <c r="I48" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5386,11 +5620,11 @@
       <c r="I49" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5400,7 +5634,7 @@
       <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -5418,11 +5652,11 @@
       <c r="I50" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5432,7 +5666,7 @@
       <c r="C51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -5450,7 +5684,7 @@
       <c r="I51" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5482,7 +5716,7 @@
       <c r="I52" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>226</v>
       </c>
     </row>
@@ -5514,7 +5748,7 @@
       <c r="I53" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5546,7 +5780,7 @@
       <c r="I54" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>234</v>
       </c>
     </row>
@@ -5578,7 +5812,7 @@
       <c r="I55" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5610,7 +5844,7 @@
       <c r="I56" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="1" t="s">
         <v>242</v>
       </c>
     </row>
@@ -5642,7 +5876,7 @@
       <c r="I57" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="1" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5674,7 +5908,7 @@
       <c r="I58" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="1" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5706,7 +5940,7 @@
       <c r="I59" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="1" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5738,7 +5972,7 @@
       <c r="I60" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="1" t="s">
         <v>261</v>
       </c>
     </row>
@@ -5770,7 +6004,7 @@
       <c r="I61" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="1" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5802,7 +6036,7 @@
       <c r="I62" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="1" t="s">
         <v>269</v>
       </c>
     </row>
@@ -5834,7 +6068,7 @@
       <c r="I63" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="1" t="s">
         <v>276</v>
       </c>
     </row>
@@ -5866,7 +6100,7 @@
       <c r="I64" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -5898,7 +6132,7 @@
       <c r="I65" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="1" t="s">
         <v>284</v>
       </c>
     </row>
@@ -5930,7 +6164,7 @@
       <c r="I66" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="1" t="s">
         <v>288</v>
       </c>
     </row>
@@ -5962,7 +6196,7 @@
       <c r="I67" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="1" t="s">
         <v>292</v>
       </c>
     </row>
@@ -5994,7 +6228,7 @@
       <c r="I68" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="1" t="s">
         <v>296</v>
       </c>
     </row>
@@ -6026,7 +6260,7 @@
       <c r="I69" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6058,7 +6292,7 @@
       <c r="I70" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="1" t="s">
         <v>304</v>
       </c>
     </row>
@@ -6090,7 +6324,7 @@
       <c r="I71" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="1" t="s">
         <v>308</v>
       </c>
     </row>
@@ -6122,7 +6356,7 @@
       <c r="I72" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="1" t="s">
         <v>312</v>
       </c>
     </row>
@@ -6154,7 +6388,7 @@
       <c r="I73" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="1" t="s">
         <v>316</v>
       </c>
     </row>
@@ -6186,7 +6420,7 @@
       <c r="I74" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="1" t="s">
         <v>320</v>
       </c>
     </row>
@@ -6208,16 +6442,16 @@
         <v>323</v>
       </c>
       <c r="G75" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="J75" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -6238,16 +6472,16 @@
         <v>323</v>
       </c>
       <c r="G76" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="I76" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="J76" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -6268,16 +6502,16 @@
         <v>323</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>324</v>
+        <v>750</v>
       </c>
       <c r="H77" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="J77" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -6298,16 +6532,16 @@
         <v>323</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>324</v>
+        <v>751</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="J78" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -6321,25 +6555,25 @@
         <v>219</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G79" s="2" t="s">
+      <c r="H79" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="J79" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6353,25 +6587,25 @@
         <v>219</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="J80" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="J80" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6385,25 +6619,25 @@
         <v>219</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H81" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="J81" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="J81" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6417,25 +6651,25 @@
         <v>219</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G82" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="J82" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="J82" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6449,25 +6683,25 @@
         <v>219</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F83" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G83" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="J83" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="J83" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6481,25 +6715,25 @@
         <v>219</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G84" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="J84" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="J84" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -6513,25 +6747,25 @@
         <v>219</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F85" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G85" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="J85" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6545,25 +6779,25 @@
         <v>219</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F86" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G86" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="I86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="J86" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6577,25 +6811,25 @@
         <v>219</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G87" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="J87" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="J87" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6609,25 +6843,25 @@
         <v>219</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="J88" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6641,25 +6875,25 @@
         <v>219</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F89" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G89" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="I89" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="J89" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="J89" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6673,25 +6907,25 @@
         <v>219</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F90" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="J90" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="J90" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6705,25 +6939,25 @@
         <v>219</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G91" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H91" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="I91" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="J91" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="J91" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6737,25 +6971,25 @@
         <v>219</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G92" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="H92" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="J92" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="J92" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6769,25 +7003,25 @@
         <v>219</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G93" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="H93" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="J93" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6801,25 +7035,25 @@
         <v>219</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G94" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="I94" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="J94" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="J94" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6833,25 +7067,25 @@
         <v>219</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G95" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="I95" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="J95" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="J95" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6865,25 +7099,25 @@
         <v>219</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="J96" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -6897,158 +7131,158 @@
         <v>219</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G97" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H97" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="J97" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="J97" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>413</v>
+        <v>699</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>414</v>
+        <v>700</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J98" t="s">
-        <v>416</v>
+        <v>701</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>417</v>
+        <v>334</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>418</v>
+        <v>704</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="J99" t="s">
-        <v>420</v>
+        <v>705</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>421</v>
+        <v>707</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>422</v>
+        <v>708</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="J100" t="s">
-        <v>424</v>
+        <v>709</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>425</v>
+        <v>707</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>426</v>
+        <v>711</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="J101" t="s">
-        <v>428</v>
+        <v>712</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>10</v>
@@ -7057,30 +7291,30 @@
         <v>11</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="F102" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="H102" s="1" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="J102" t="s">
-        <v>432</v>
+        <v>414</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>10</v>
@@ -7089,30 +7323,30 @@
         <v>11</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="J103" t="s">
-        <v>436</v>
+        <v>418</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>10</v>
@@ -7121,1466 +7355,1466 @@
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="F104" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="J104" t="s">
-        <v>440</v>
+        <v>422</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J105" t="s">
-        <v>448</v>
+        <v>426</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="J106" t="s">
-        <v>452</v>
+        <v>430</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="J107" t="s">
-        <v>456</v>
+        <v>434</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="J108" t="s">
-        <v>460</v>
+        <v>438</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="F109" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="H109" s="1" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="J109" t="s">
-        <v>464</v>
+        <v>446</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="J110" t="s">
-        <v>468</v>
+        <v>450</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="J111" t="s">
-        <v>472</v>
+        <v>454</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="J112" t="s">
-        <v>476</v>
+        <v>458</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F113" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>477</v>
+        <v>442</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="J113" t="s">
-        <v>480</v>
+        <v>462</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F114" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="J114" t="s">
-        <v>484</v>
+        <v>466</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="J115" t="s">
-        <v>488</v>
+        <v>470</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="J116" t="s">
-        <v>490</v>
+        <v>474</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>491</v>
+        <v>442</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="J117" t="s">
-        <v>494</v>
+        <v>478</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="J118" t="s">
-        <v>498</v>
+        <v>482</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="J119" t="s">
-        <v>502</v>
+        <v>486</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>503</v>
+        <v>442</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="J120" t="s">
-        <v>506</v>
+        <v>488</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>507</v>
+        <v>442</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="J121" t="s">
-        <v>510</v>
+        <v>492</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
+        <v>124</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>125</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>126</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>127</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>129</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D126" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="G122" s="2" t="s">
+      <c r="H126" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="J126" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="J122" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>130</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="J123" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>131</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="J124" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>132</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="J125" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>133</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="J126" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>441</v>
+        <v>321</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>442</v>
+        <v>322</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>535</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="E127" s="1"/>
       <c r="F127" s="1" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="J127" t="s">
-        <v>539</v>
+        <v>518</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>441</v>
+        <v>218</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>442</v>
+        <v>219</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>540</v>
+        <v>746</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>541</v>
+        <v>522</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="J128" t="s">
-        <v>543</v>
+        <v>523</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>544</v>
+        <v>218</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>545</v>
+        <v>219</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>549</v>
+        <v>747</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="J129" t="s">
-        <v>552</v>
+        <v>526</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>544</v>
+        <v>218</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>545</v>
+        <v>219</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="J130" t="s">
-        <v>556</v>
+        <v>530</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>544</v>
+        <v>440</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>545</v>
+        <v>441</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>557</v>
+        <v>532</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="J131" t="s">
-        <v>560</v>
+        <v>536</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>544</v>
+        <v>440</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>545</v>
+        <v>441</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>562</v>
+        <v>539</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="J132" t="s">
-        <v>564</v>
+        <v>540</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F133" s="1" t="s">
+      <c r="G133" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="J133" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>569</v>
+      <c r="G134" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>570</v>
+        <v>735</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="J134" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>573</v>
+      <c r="G135" s="1" t="s">
+        <v>736</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>574</v>
+        <v>737</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="J135" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G136" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J136" t="s">
-        <v>579</v>
+        <v>558</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="F137" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G137" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J137" t="s">
-        <v>582</v>
+        <v>562</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G138" s="1" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="J138" t="s">
-        <v>586</v>
+        <v>566</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G139" s="2" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J139" t="s">
-        <v>589</v>
+        <v>570</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="G140" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="H140" s="1" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J140" t="s">
-        <v>593</v>
+        <v>573</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G141" s="2" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J141" t="s">
-        <v>595</v>
+        <v>576</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>596</v>
+      <c r="G142" s="1" t="s">
+        <v>578</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="J142" t="s">
-        <v>599</v>
+        <v>580</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G143" s="2" t="s">
-        <v>600</v>
+        <v>553</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="J143" t="s">
-        <v>603</v>
+        <v>583</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G144" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="J144" t="s">
-        <v>606</v>
+        <v>587</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="G145" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J145" t="s">
         <v>590</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="J145" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>10</v>
+        <v>542</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>11</v>
+        <v>543</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>146</v>
+        <v>544</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>609</v>
+        <v>546</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="J146" t="s">
-        <v>612</v>
+        <v>593</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>10</v>
+        <v>542</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>11</v>
+        <v>543</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>146</v>
+        <v>544</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>613</v>
+        <v>546</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>614</v>
+        <v>741</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="J147" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>10</v>
+        <v>542</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>11</v>
+        <v>543</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>146</v>
+        <v>544</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>617</v>
+        <v>546</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>618</v>
+        <v>743</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="J148" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>10</v>
+        <v>542</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>11</v>
+        <v>543</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>146</v>
+        <v>544</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>621</v>
+        <v>546</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>622</v>
+        <v>739</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>623</v>
+        <v>599</v>
       </c>
       <c r="J149" t="s">
-        <v>624</v>
+        <v>600</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>10</v>
@@ -8598,21 +8832,21 @@
         <v>148</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>625</v>
+        <v>601</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>626</v>
+        <v>602</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="J150" t="s">
-        <v>628</v>
+        <v>603</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>10</v>
@@ -8630,21 +8864,21 @@
         <v>148</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="J151" t="s">
-        <v>632</v>
+        <v>607</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>10</v>
@@ -8662,531 +8896,531 @@
         <v>148</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="J152" t="s">
-        <v>636</v>
+        <v>611</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>637</v>
+        <v>146</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>638</v>
+        <v>147</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>637</v>
+        <v>148</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>639</v>
+        <v>613</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="J153" t="s">
-        <v>642</v>
+        <v>615</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>637</v>
+        <v>146</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>638</v>
+        <v>147</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>637</v>
+        <v>148</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="J154" t="s">
-        <v>646</v>
+        <v>619</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>637</v>
+        <v>146</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>638</v>
+        <v>147</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>637</v>
+        <v>148</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>643</v>
+        <v>621</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>647</v>
+        <v>622</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="J155" t="s">
-        <v>649</v>
+        <v>623</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>637</v>
+        <v>146</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>638</v>
+        <v>147</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>637</v>
+        <v>148</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>650</v>
+        <v>626</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="J156" t="s">
-        <v>652</v>
+        <v>627</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="D157" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="J157" t="s">
-        <v>656</v>
+        <v>633</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="D158" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I158" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="J158" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="J158" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="J159" t="s">
-        <v>664</v>
+        <v>640</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="D160" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="J160" t="s">
-        <v>666</v>
+        <v>643</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
+        <v>165</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>166</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>167</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>168</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
         <v>169</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B165" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G161" s="1" t="s">
+      <c r="D165" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="J165" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="J161" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="E162" s="1"/>
-      <c r="F162" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="J162" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I163" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="J163" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="J164" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="J165" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>219</v>
+        <v>322</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>221</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>688</v>
+        <v>663</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="J166" t="s">
-        <v>691</v>
+        <v>665</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>219</v>
+        <v>667</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>693</v>
+        <v>13</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>752</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>694</v>
+        <v>96</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="J167" t="s">
-        <v>696</v>
+        <v>668</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>219</v>
+        <v>670</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>222</v>
+        <v>13</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="J168" t="s">
-        <v>701</v>
+        <v>672</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>702</v>
+        <v>674</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>218</v>
@@ -9195,28 +9429,317 @@
         <v>219</v>
       </c>
       <c r="D169" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="H169" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="J169" t="s">
-        <v>706</v>
+      <c r="F173" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>170</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>171</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>172</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>173</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>174</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>731</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\tsclient\D\test-site — копия BackUp\workhouse\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303B01A-3E7B-4D9A-8B70-1A5313677BE8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2913DBB6-C00D-42D3-A5E3-ADC87C01D05A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\tsclient\D\test-site — копия BackUp\workhouse\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2913DBB6-C00D-42D3-A5E3-ADC87C01D05A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DE960B-AF71-491E-A3BE-2AE16E6A751F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$J$179</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="762">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3692,6 +3695,27 @@
 4. Матеріал быстроразъемной муфти — алюміній
 5. Розташування цангових виводів — пряме
 6. Виконання быстроразъемной муфти — євро тип (Euro-type)</t>
+  </si>
+  <si>
+    <t>Гідравлічні крани кульові високого тиску</t>
+  </si>
+  <si>
+    <t>Гідравлічні крани кульові високого тиску з внутрішнім різбленням</t>
+  </si>
+  <si>
+    <t>child3_small_175.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_175.jpg</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішнім різбленням</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішнім різбленням для гідравлічних систем,
+призначений для перекриття потоків рідин
+Особливості та властивості:
+1. Виготовлений зі сталі, ручка-важіль із алюмінію.</t>
   </si>
 </sst>
 </file>
@@ -4048,7 +4072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -8215,7 +8239,7 @@
         <v>441</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>532</v>
+        <v>756</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>533</v>
@@ -8247,7 +8271,7 @@
         <v>441</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>532</v>
+        <v>756</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>533</v>
@@ -9738,7 +9762,40 @@
         <v>731</v>
       </c>
     </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>175</v>
+      </c>
+      <c r="B179" t="s">
+        <v>440</v>
+      </c>
+      <c r="C179" t="s">
+        <v>441</v>
+      </c>
+      <c r="D179" t="s">
+        <v>756</v>
+      </c>
+      <c r="E179" t="s">
+        <v>533</v>
+      </c>
+      <c r="F179" t="s">
+        <v>757</v>
+      </c>
+      <c r="G179" t="s">
+        <v>760</v>
+      </c>
+      <c r="H179" t="s">
+        <v>761</v>
+      </c>
+      <c r="I179" t="s">
+        <v>758</v>
+      </c>
+      <c r="J179" t="s">
+        <v>759</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:J179" xr:uid="{7FC527DB-17BF-453D-BE91-6A17C45BA147}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\tsclient\D\test-site — копия BackUp\workhouse\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DE960B-AF71-491E-A3BE-2AE16E6A751F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B060F684-F5E8-4D2A-888A-369B789ADE0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$J$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$J$182</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="776">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -1180,27 +1180,10 @@
     <t>child3_big_48.jpg</t>
   </si>
   <si>
-    <t>З’єднання швидкороз’ємне пневматичне системи VOSS 230 пряме в комплекте</t>
-  </si>
-  <si>
-    <t>Швидкороз’ємне пневматичне з’єднання системи VOSS 230 складається з двох частин: гнізда із зовнішньою
-різьбою та ніпеля з патрубком типу «ялинка» для приєднання трубок. З'єднання отримало назву за ім'ям компанії-
-розробника VOSS. Основне застосування — інтеграція в автомобільну пневмоапаратуру для швидкого
-універсального підключення та обслуговування.
-Перед монтажем пластикову трубку необхідно розігріти будівельним феном і насадити на штуцер. Додаткове
-кріплення не потрібне.
-Особливості та властивості:
-Матеріал з’єднувача- сталь, гальванічне цинкове покриття, жовта пасивація.
-Виконання - конструкція системи VOSS 230</t>
-  </si>
-  <si>
     <t>child3_small_49.jpg</t>
   </si>
   <si>
     <t>child3_big_49.jpg</t>
-  </si>
-  <si>
-    <t>З’єднання швидкороз’ємне пневматичне системи VOSS 230 кутове в комплекте</t>
   </si>
   <si>
     <t>child3_small_50.jpg</t>
@@ -1354,21 +1337,6 @@
   </si>
   <si>
     <t>child3_big_55.jpg</t>
-  </si>
-  <si>
-    <t>Гайка накидна з врізним кільцем 24° та опорною втулкою обтискного з'єднувача</t>
-  </si>
-  <si>
-    <t>Накидна гайка в комплекті з врізним кільцем та опорною втулкою призначена для компресійної фіксації
-поліамідних і металевих трубок у корпусі з’єднувача з внутрішнім конусом 24 градуси. Виготовлений відповідно до
-ISO 8434-1 / DIN 2353.
-Для досягнення максимальної щільності з’єднання врізне кільце слід змащувати маслом перед монтажем.
-Особливості та властивості:
-1. Матеріал гайки та врізного кільця — сталь, гальванічне цинкове покриття, жовта пасивація
-2. Матеріал опорної втулки — латунь
-3. Для з’єднання компресійного типу
-Склад комплекту:
-Накидна гайка, врізне кільце, опорна втулка (тільки для пластикових трубок)</t>
   </si>
   <si>
     <t>child3_small_56.jpg</t>
@@ -3700,22 +3668,127 @@
     <t>Гідравлічні крани кульові високого тиску</t>
   </si>
   <si>
-    <t>Гідравлічні крани кульові високого тиску з внутрішнім різбленням</t>
-  </si>
-  <si>
     <t>child3_small_175.jpg</t>
   </si>
   <si>
     <t>child3_big_175.jpg</t>
   </si>
   <si>
-    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішнім різбленням</t>
-  </si>
-  <si>
-    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішнім різбленням для гідравлічних систем,
+    <t>Комплекти</t>
+  </si>
+  <si>
+    <t>Комплект обтискного з'єднання</t>
+  </si>
+  <si>
+    <t>Комплект обтискного з'єднання
+Накидна гайка в комплекті з врізним кільцем та опорною втулкою призначена для компресійної фіксації
+поліамідних і металевих трубок у корпусі з’єднувача з внутрішнім конусом 24 градуси. Виготовлений відповідно до
+ISO 8434-1 / DIN 2353.
+Для досягнення максимальної щільності з’єднання врізне кільце слід змащувати маслом перед монтажем.
+Особливості та властивості:
+1. Матеріал гайки та врізного кільця — сталь, гальванічне цинкове покриття, жовта пасивація
+2. Матеріал опорної втулки — латунь
+3. Для з’єднання компресійного типу
+Склад комплекту:
+Накидна гайка, врізне кільце, опорна втулка (тільки для пластикових трубок)</t>
+  </si>
+  <si>
+    <t>child3_small_176.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_176.jpg</t>
+  </si>
+  <si>
+    <t>Гайка накидна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накидна гайка призначена для компресійної фіксації поліамідних і металевих трубок. Виготовлений відповідно до
+ISO 8434-1 / DIN 2353.
+Для досягнення максимальної щільності з’єднання врізне кільце слід змащувати маслом перед монтажем.
+Особливості та властивості:
+1. Матеріал гайки — сталь, гальванічне цинкове покриття, жовта пасивація
+2. Для з’єднання компресійного типу
+</t>
+  </si>
+  <si>
+    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS пряме</t>
+  </si>
+  <si>
+    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS пряме складається з двох частин: гнізда із зовнішньою
+різьбою та ніпеля з патрубком типу «ялинка» для приєднання трубок. З'єднання отримало назву за ім'ям компанії-
+розробника VOSS. Основне застосування — інтеграція в автомобільну пневмоапаратуру для швидкого
+універсального підключення та обслуговування.
+Перед монтажем пластикову трубку необхідно розігріти будівельним феном і насадити на штуцер. Додаткове
+кріплення не потрібне.
+Особливості та властивості:
+Матеріал з’єднувача- сталь, гальванічне цинкове покриття, жовта пасивація.
+Виконання - конструкція системи VOSS 230</t>
+  </si>
+  <si>
+    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS 230 кутове</t>
+  </si>
+  <si>
+    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS 230 кутове складається з двох частин: гнізда із зовнішньою
+різьбою та ніпеля з патрубком типу «ялинка» для приєднання трубок. З'єднання отримало назву за ім'ям компанії-
+розробника VOSS. Основне застосування — інтеграція в автомобільну пневмоапаратуру для швидкого
+універсального підключення та обслуговування.
+Перед монтажем пластикову трубку необхідно розігріти будівельним феном і насадити на штуцер. Додаткове
+кріплення не потрібне.
+Особливості та властивості:
+Матеріал з’єднувача- сталь, гальванічне цинкове покриття, жовта пасивація.
+Виконання - конструкція системи VOSS 230</t>
+  </si>
+  <si>
+    <t>Штекер швидкороз'ємного пневматичного з'єднання системи VOSS 232</t>
+  </si>
+  <si>
+    <t>Штекер швидкороз'ємного пневматичного з'єднання для ніпеля системи VOSS 232. З'єднання отримало назву за
+ім'ям компанії-розробника VOSS. Основне застосування — інтеграція в автомобільну пневмоапаратуру для
+швидкого універсального підключення та обслуговування.
+Особливості та властивості:
+Виготовлено з латуні, оснащено штекером і ущільнювальним гумовим кільцем.</t>
+  </si>
+  <si>
+    <t>child3_small_177.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_177.jpg</t>
+  </si>
+  <si>
+    <t>Гідравлічні крани кульові високого тиску з внутрішньою різьбою</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішньою різьбою</t>
+  </si>
+  <si>
+    <t>Кран запірний кульовий двоходовий з двома виходами з внутрішньою різьбою для гідравлічних систем,
 призначений для перекриття потоків рідин
 Особливості та властивості:
 1. Виготовлений зі сталі, ручка-важіль із алюмінію.</t>
+  </si>
+  <si>
+    <t>Кран кульовий у комплекті зі адаптерами та ущільнювальними кільцями</t>
+  </si>
+  <si>
+    <t>Кран кульовий у комплекті зі адаптерами та ущільнювальними кільцями.
+Призначений для повного перекриття потоку робочої рідини в гідравлічних системах високого тиску мобільної та стаціонарної техніки (зокрема, для адаптації під техніку з метричними стандартами різьби М20).
+Комплектація:
+Кран кульовий двоходовий (внутрішня різьба 1/2" BSP) — 1 шт.
+Адаптер прямий (штуцер–штуцер) AGM (M20x1.5) — AGR (1/2"-14 BSP) — 2 шт.
+Кільце ущільнювальне метало-гумове (1/2" BSP) — 2 шт.
+Технічні характеристики:
+Тип крана: двоходовий, запірний, кульовий.
+Матеріал корпусу: сталь.
+Матеріал ручки: алюміній (тип: ручка-важіль).
+Тип підключення крана: внутрішня різьба 1/2" BSP (з можливістю переходу на М20х1.5 за допомогою адаптерів із комплекту).
+Максимальний піковий тиск: 500 бар.
+Сумісність: підходить для встановлення на гідросистеми техніки виробництва СНД та інших машин, що використовують підключення М20х1.5.</t>
+  </si>
+  <si>
+    <t>child3_small_178.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_178.jpg</t>
   </si>
 </sst>
 </file>
@@ -4072,7 +4145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -4548,10 +4621,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -5665,19 +5738,19 @@
         <v>157</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>158</v>
+        <v>754</v>
       </c>
       <c r="G50" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -5697,19 +5770,19 @@
         <v>157</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>158</v>
+        <v>754</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>215</v>
+        <v>763</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>212</v>
+        <v>764</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5717,31 +5790,31 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="G52" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="J52" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5749,31 +5822,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G53" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5781,31 +5854,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G54" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5813,31 +5886,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5845,31 +5918,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G56" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5877,31 +5950,31 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>222</v>
+        <v>754</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>243</v>
+        <v>755</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>244</v>
+        <v>756</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5909,31 +5982,31 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G58" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5941,31 +6014,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G59" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5979,25 +6052,25 @@
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6011,25 +6084,25 @@
         <v>11</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="H61" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -6043,25 +6116,25 @@
         <v>11</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -6069,31 +6142,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -6101,31 +6174,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="H64" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -6133,31 +6206,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -6165,31 +6238,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -6197,31 +6270,31 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -6229,31 +6302,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -6261,31 +6334,31 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -6293,31 +6366,31 @@
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -6325,31 +6398,31 @@
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -6357,31 +6430,31 @@
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -6389,31 +6462,31 @@
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -6421,31 +6494,31 @@
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -6453,29 +6526,29 @@
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -6483,29 +6556,29 @@
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -6513,29 +6586,29 @@
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -6543,29 +6616,29 @@
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -6573,31 +6646,31 @@
         <v>80</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6605,31 +6678,31 @@
         <v>81</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="H80" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6637,31 +6710,31 @@
         <v>82</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6669,31 +6742,31 @@
         <v>83</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6701,31 +6774,31 @@
         <v>84</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6733,31 +6806,31 @@
         <v>85</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -6765,31 +6838,31 @@
         <v>86</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6797,31 +6870,31 @@
         <v>87</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6829,31 +6902,31 @@
         <v>88</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6861,31 +6934,31 @@
         <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6893,31 +6966,31 @@
         <v>90</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6925,31 +6998,31 @@
         <v>91</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6957,31 +7030,31 @@
         <v>92</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6989,31 +7062,31 @@
         <v>93</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -7021,31 +7094,31 @@
         <v>94</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -7053,31 +7126,31 @@
         <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -7085,31 +7158,31 @@
         <v>96</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -7117,31 +7190,31 @@
         <v>97</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -7149,31 +7222,31 @@
         <v>98</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -7181,31 +7254,31 @@
         <v>99</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -7213,31 +7286,31 @@
         <v>100</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -7245,31 +7318,31 @@
         <v>101</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -7277,31 +7350,31 @@
         <v>101</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G101" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="J101" s="1" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -7315,25 +7388,25 @@
         <v>11</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J102" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -7347,25 +7420,25 @@
         <v>11</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="H103" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -7379,25 +7452,25 @@
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -7411,25 +7484,25 @@
         <v>11</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -7443,25 +7516,25 @@
         <v>11</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -7475,25 +7548,25 @@
         <v>11</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -7507,25 +7580,25 @@
         <v>11</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -7533,31 +7606,31 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="J109" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -7565,31 +7638,31 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="H110" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -7597,31 +7670,31 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -7629,31 +7702,31 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7661,31 +7734,31 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -7693,31 +7766,31 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -7725,31 +7798,31 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7757,31 +7830,31 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7789,31 +7862,31 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7821,31 +7894,31 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -7853,31 +7926,31 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -7885,31 +7958,31 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -7917,31 +7990,31 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -7949,31 +8022,31 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -7981,31 +8054,31 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -8013,31 +8086,31 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -8045,31 +8118,31 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -8077,29 +8150,29 @@
         <v>129</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -8107,29 +8180,29 @@
         <v>130</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -8137,31 +8210,31 @@
         <v>131</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -8169,31 +8242,31 @@
         <v>132</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="I129" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="F129" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="J129" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -8201,31 +8274,31 @@
         <v>133</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -8233,31 +8306,31 @@
         <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F131" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="J131" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -8265,31 +8338,31 @@
         <v>135</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E132" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G132" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="H132" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -8297,31 +8370,31 @@
         <v>137</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="J133" t="s">
         <v>544</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J133" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -8329,31 +8402,31 @@
         <v>138</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="I134" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="J134" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8361,31 +8434,31 @@
         <v>139</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="J135" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8393,31 +8466,31 @@
         <v>140</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -8425,31 +8498,31 @@
         <v>141</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -8457,31 +8530,31 @@
         <v>142</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -8489,31 +8562,31 @@
         <v>143</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -8521,31 +8594,31 @@
         <v>144</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>547</v>
-      </c>
       <c r="H140" s="1" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -8553,31 +8626,31 @@
         <v>145</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E141" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="H141" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8585,31 +8658,31 @@
         <v>146</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -8617,31 +8690,31 @@
         <v>147</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8649,31 +8722,31 @@
         <v>148</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -8681,31 +8754,31 @@
         <v>149</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J145" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -8713,31 +8786,31 @@
         <v>150</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -8745,31 +8818,31 @@
         <v>151</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="J147" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -8777,31 +8850,31 @@
         <v>152</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="J148" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -8809,31 +8882,31 @@
         <v>153</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="J149" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -8856,16 +8929,16 @@
         <v>148</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -8888,16 +8961,16 @@
         <v>148</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -8920,16 +8993,16 @@
         <v>148</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8952,16 +9025,16 @@
         <v>148</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -8984,16 +9057,16 @@
         <v>148</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9016,16 +9089,16 @@
         <v>148</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9048,16 +9121,16 @@
         <v>148</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9065,31 +9138,31 @@
         <v>161</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D157" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J157" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9097,31 +9170,31 @@
         <v>162</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="G158" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="H158" s="1" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9129,31 +9202,31 @@
         <v>163</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F159" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G159" s="1" t="s">
+      <c r="H159" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="H159" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="J159" s="1" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9161,31 +9234,31 @@
         <v>164</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F160" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="H160" s="1" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -9193,31 +9266,31 @@
         <v>165</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -9225,31 +9298,31 @@
         <v>166</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -9257,31 +9330,31 @@
         <v>167</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -9289,31 +9362,31 @@
         <v>168</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J164" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -9321,66 +9394,66 @@
         <v>169</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>10</v>
@@ -9398,21 +9471,21 @@
         <v>95</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>96</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>10</v>
@@ -9430,176 +9503,176 @@
         <v>95</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="F169" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G169" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="F170" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G170" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="F171" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G171" s="1" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="F172" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="G172" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -9607,31 +9680,31 @@
         <v>170</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E174" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="J174" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="H174" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="I174" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -9639,31 +9712,31 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D175" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G175" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="E175" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>720</v>
-      </c>
       <c r="H175" s="1" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -9671,31 +9744,31 @@
         <v>172</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -9703,31 +9776,31 @@
         <v>173</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G177" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="J177" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9735,31 +9808,31 @@
         <v>174</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -9767,35 +9840,131 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C179" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D179" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E179" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F179" t="s">
+        <v>769</v>
+      </c>
+      <c r="G179" t="s">
+        <v>770</v>
+      </c>
+      <c r="H179" t="s">
+        <v>771</v>
+      </c>
+      <c r="I179" t="s">
+        <v>752</v>
+      </c>
+      <c r="J179" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>176</v>
+      </c>
+      <c r="B180" t="s">
+        <v>215</v>
+      </c>
+      <c r="C180" t="s">
+        <v>216</v>
+      </c>
+      <c r="D180" t="s">
+        <v>217</v>
+      </c>
+      <c r="E180" t="s">
+        <v>218</v>
+      </c>
+      <c r="F180" t="s">
+        <v>219</v>
+      </c>
+      <c r="G180" t="s">
+        <v>759</v>
+      </c>
+      <c r="H180" t="s">
+        <v>760</v>
+      </c>
+      <c r="I180" t="s">
         <v>757</v>
       </c>
-      <c r="G179" t="s">
-        <v>760</v>
-      </c>
-      <c r="H179" t="s">
-        <v>761</v>
-      </c>
-      <c r="I179" t="s">
+      <c r="J180" t="s">
         <v>758</v>
       </c>
-      <c r="J179" t="s">
-        <v>759</v>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>177</v>
+      </c>
+      <c r="B181" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>156</v>
+      </c>
+      <c r="E181" t="s">
+        <v>157</v>
+      </c>
+      <c r="F181" t="s">
+        <v>158</v>
+      </c>
+      <c r="G181" t="s">
+        <v>765</v>
+      </c>
+      <c r="H181" t="s">
+        <v>766</v>
+      </c>
+      <c r="I181" t="s">
+        <v>767</v>
+      </c>
+      <c r="J181" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>178</v>
+      </c>
+      <c r="B182" t="s">
+        <v>435</v>
+      </c>
+      <c r="C182" t="s">
+        <v>436</v>
+      </c>
+      <c r="D182" t="s">
+        <v>751</v>
+      </c>
+      <c r="E182" t="s">
+        <v>528</v>
+      </c>
+      <c r="F182" t="s">
+        <v>754</v>
+      </c>
+      <c r="G182" t="s">
+        <v>772</v>
+      </c>
+      <c r="H182" t="s">
+        <v>773</v>
+      </c>
+      <c r="I182" t="s">
+        <v>774</v>
+      </c>
+      <c r="J182" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J179" xr:uid="{7FC527DB-17BF-453D-BE91-6A17C45BA147}"/>
+  <autoFilter ref="A1:J182" xr:uid="{7FC527DB-17BF-453D-BE91-6A17C45BA147}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B060F684-F5E8-4D2A-888A-369B789ADE0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C000E4-764F-4A54-92B3-9F5CAAF1D3AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="779">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3674,9 +3674,6 @@
     <t>child3_big_175.jpg</t>
   </si>
   <si>
-    <t>Комплекти</t>
-  </si>
-  <si>
     <t>Комплект обтискного з'єднання</t>
   </si>
   <si>
@@ -3789,6 +3786,30 @@
   </si>
   <si>
     <t>child3_big_178.jpg</t>
+  </si>
+  <si>
+    <t>Комплект пневматичного з'єднання RAUFOSS ABC перехідний кутовий з двома виводами ABC Newline та зовнішньою різьбою</t>
+  </si>
+  <si>
+    <t>Комплект пневматичного з'єднання RAUFOSS ABC перехідний кутовий з двома виводами ABC Newline та зовнішньою різьбою
+Загальний опис товаруВисокотехнологічний монтажний комплект оригінальної системи RAUFOSS ABC™ SYSTEM. Призначений для побудови та ремонту надійних магістралей гальмівних систем і підвіски комерційного транспорту.
+Комплект складається з двох взаємопов'язаних елементів, які в зборі утворюють кутовий перехідний вузол. Конструкція забезпечує швидкий безінструментальний монтаж, абсолютну герметичність та стійкість до критичних експлуатаційних навантажень вантажних автомобілів.Приймальний порт (гніздо) безрізьбового з'єднання стандарту ABC™ SYSTEM призначений для високонадійного підключення вставних з'єднувачів різних конфігурацій із можливістю вільної самоорієнтації (обертання) з'єднувача відносно осі порту.
+Склад комплекту та технічні особливості деталей
+1. З'єднувач перехідний пневматичний кутовийТип: Кутовий фітинг із приймальним портом (гніздом) безрізьбового з'єднання та затискним муфтовим приєднанням.
+Форм-фактор: ABC INTEGRAL 90° (Raufoss Couplings).
+Матеріал корпусу: Поліамід РА12 (високоміцний інженерний пластик).
+Технологія виводу ABC Newline: Трубка надійно фіксується в муфтовому затискному гнізді типу ABC Newline за допомогою розрізного пружинного кільця з протиспрямованою гострою кромкою, що виключає самовільне від'єднання.
+2. З'єднувач перехідний пневматичний прямийТип: Прямий фітинг зі вставним безрізьбовим з'єднанням та зовнішньою різьбою.
+Форм-фактор: ABC SWIVEL ТYРЕ-1 (Raufoss Couplings). Прямий вставний штекер розроблений для швидкого безрізьбового з'єднання з приймальним портом кутового фітинга.
+Матеріал корпусу: Високоякісна латунь.
+Функціонал: Забезпечує перехід від жорсткого різьбового вузла системи (ресивер, клапан) до поворотного безрізьбового кутового з'єднання.
+Мобільність вузла: Завдяки системі безрізьбового стикування деталей, кутовий з'єднувач може вільно обертатися навколо своєї осі відносно прямого адаптера, що полегшує позиціонування трубок при монтажі та знімає внутрішнє напруження в магістралі під час вібрації.</t>
+  </si>
+  <si>
+    <t>child3_small_179.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_179.jpg</t>
   </si>
 </sst>
 </file>
@@ -4145,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5738,13 +5759,13 @@
         <v>157</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>754</v>
+        <v>158</v>
       </c>
       <c r="G50" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>762</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>211</v>
@@ -5770,13 +5791,13 @@
         <v>157</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>754</v>
+        <v>158</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>764</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>213</v>
@@ -5962,13 +5983,13 @@
         <v>218</v>
       </c>
       <c r="F57" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="H57" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>240</v>
@@ -9852,13 +9873,13 @@
         <v>528</v>
       </c>
       <c r="F179" t="s">
+        <v>768</v>
+      </c>
+      <c r="G179" t="s">
         <v>769</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>770</v>
-      </c>
-      <c r="H179" t="s">
-        <v>771</v>
       </c>
       <c r="I179" t="s">
         <v>752</v>
@@ -9887,16 +9908,16 @@
         <v>219</v>
       </c>
       <c r="G180" t="s">
+        <v>758</v>
+      </c>
+      <c r="H180" t="s">
         <v>759</v>
       </c>
-      <c r="H180" t="s">
-        <v>760</v>
-      </c>
       <c r="I180" t="s">
+        <v>756</v>
+      </c>
+      <c r="J180" t="s">
         <v>757</v>
-      </c>
-      <c r="J180" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -9919,16 +9940,16 @@
         <v>158</v>
       </c>
       <c r="G181" t="s">
+        <v>764</v>
+      </c>
+      <c r="H181" t="s">
         <v>765</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>766</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>767</v>
-      </c>
-      <c r="J181" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9948,19 +9969,51 @@
         <v>528</v>
       </c>
       <c r="F182" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
       <c r="G182" t="s">
+        <v>771</v>
+      </c>
+      <c r="H182" t="s">
         <v>772</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>773</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>774</v>
       </c>
-      <c r="J182" t="s">
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>179</v>
+      </c>
+      <c r="B183" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" t="s">
+        <v>146</v>
+      </c>
+      <c r="E183" t="s">
+        <v>147</v>
+      </c>
+      <c r="F183" t="s">
+        <v>148</v>
+      </c>
+      <c r="G183" t="s">
         <v>775</v>
+      </c>
+      <c r="H183" t="s">
+        <v>776</v>
+      </c>
+      <c r="I183" t="s">
+        <v>777</v>
+      </c>
+      <c r="J183" t="s">
+        <v>778</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C000E4-764F-4A54-92B3-9F5CAAF1D3AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582CB12A-AB96-483F-B4C5-730E00523E59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="791">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3722,9 +3722,6 @@
 Виконання - конструкція системи VOSS 230</t>
   </si>
   <si>
-    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS 230 кутове</t>
-  </si>
-  <si>
     <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS 230 кутове складається з двох частин: гнізда із зовнішньою
 різьбою та ніпеля з патрубком типу «ялинка» для приєднання трубок. З'єднання отримало назву за ім'ям компанії-
 розробника VOSS. Основне застосування — інтеграція в автомобільну пневмоапаратуру для швидкого
@@ -3810,6 +3807,62 @@
   </si>
   <si>
     <t>child3_big_179.jpg</t>
+  </si>
+  <si>
+    <t>Комплект з’єднання швидкороз’ємне пневматичне системи VOSS кутове</t>
+  </si>
+  <si>
+    <t>Гніздо швидкороз’ємної самозапірної пневматичної муфти з одного боку та накидною гайкою з пружиною з іншого боку для підключення до пневмосистеми</t>
+  </si>
+  <si>
+    <t>Гніздо швидкороз’ємної самозапірної пневматичної муфти, призначене для підключення пневмоінструменту,
+компресорів та інших елементів побутових і промислових пневмосистем. Вбудований клапан у муфті запобігає
+втраті стисненого повітря при роз’єднанні муфти.
+Особливості та характеристики:
+1. Матеріал муфти - сталь
+2. Підключення шланга (трубки) - накидна гайка з пружиною
+3. Виконання – євро тип (Euro-type)</t>
+  </si>
+  <si>
+    <t>child3_small_180.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_180.jpg</t>
+  </si>
+  <si>
+    <t>Муфта швидкороз'ємного самозапірного пневматичного з'єднання із зовнішньою різьбою для підключення до пневмосистеми</t>
+  </si>
+  <si>
+    <t>Муфта швидкороз’ємного самозапірного пневматичного з’єднання із зовнішньою різьбою призначена для швидкого, надійного та герметичного підключення пневмоінструменту, компресорів та інших елементів побутових або промислових пневмосистем.
+Головною перевагою моделі є вбудований автоматичний клапан, який миттєво перекриває потік стисненого повітря при від’єднанні інструменту. Це дозволяє проводити заміну обладнання «на гарячу» без необхідності щоразу вимикати компресор або скидати тиск у всій магістралі, що значно економить час та запобігає втратам ресурсів.
+Внутрішній механізм: латунні та сталеві елементи підвищеної зносостійкості для надійної фіксації.
+Вбудований поворотний шарнір  дозволяє муфті вільно обертатися навколо своєї осі, що повністю виключає перекручування, заломи та заплутування повітряного шланга під час активної роботи.
+Матеріал корпусу: високоякісна міцна сталь з антикорозійним покриттям, що гарантує тривалий термін служби в умовах високих навантажень.
+Тип профілю (роз'єму): євростандарт (Euro-type / DN 7.2) — найпопулярніший та універсальний тип швидкороз'ємних з'єднань.
+Тип підключення до лінії: зовнішня різьба (для вкручування в інструмент, блоки підготовки повітря або різьбові адаптери).</t>
+  </si>
+  <si>
+    <t>child3_small_181.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_181.jpg</t>
+  </si>
+  <si>
+    <t>Муфта швидкороз'ємного самозапірного пневматичного з'єднання із штуцерами типу «ялинка» для підключення до пневмосистеми</t>
+  </si>
+  <si>
+    <t>Муфта швидкороз’ємного самозапірного пневматичного з’єднання із штуцерами типу «ялинка» для підключення до пневмосистеми призначена для швидкого, надійного та герметичного з’єднання гнучких гумових, ПВХ або поліуретанових шлангів у побутових та промислових пневмолініях. Цей елемент є незамінним для нарощування загальної довжини повітряної магістралі, швидкого ремонту пошкоджених ділянок або підключення мобільного пневмоінструменту до компресора.
+Муфта оснащена вбудованим автоматичним клапаном, який миттєво перекриває потік стисненого повітря при роз’єднанні. Це дозволяє безпечно відключати інструмент або частину лінії «на гарячу», не зупиняючи роботу компресора та не скидаючи тиск у всій пневмосистемі, що значно підвищує ефективність робочого процесу.
+Матеріал корпусу: комбінація високоякісної міцної сталі та латуні, що забезпечує максимальну стійкість до механічних ударів, корозії та щоденного професійного зносу.
+Головною перевагою моделі є вбудований автоматичний клапан, який миттєво перекриває потік стисненого повітря при від’єднанні інструменту. Це дозволяє проводити заміну обладнання «на гарячу» без необхідності щоразу вимикати компресор або скидати тиск у всій магістралі, що значно економить час та запобігає втратам ресурсів.
+ Тип підключення шланга: штуцери типу «ялинка» з надійними фіксуючими насічками. Шланг щільно насаджується на штуцер і фіксується стандартним гвинтовим або черв'ячним хомутом.
+Тип профілю роз'єму: євростандарт (Euro-type / DN 7.2) — гарантує 100% сумісність із більшістю сучасного пневмообладнання та інструментів європейського типу.</t>
+  </si>
+  <si>
+    <t>child3_small_182.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_182.jpg</t>
   </si>
 </sst>
 </file>
@@ -4166,7 +4219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5794,10 +5847,10 @@
         <v>158</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>213</v>
@@ -9873,13 +9926,13 @@
         <v>528</v>
       </c>
       <c r="F179" t="s">
+        <v>767</v>
+      </c>
+      <c r="G179" t="s">
         <v>768</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>769</v>
-      </c>
-      <c r="H179" t="s">
-        <v>770</v>
       </c>
       <c r="I179" t="s">
         <v>752</v>
@@ -9940,16 +9993,16 @@
         <v>158</v>
       </c>
       <c r="G181" t="s">
+        <v>763</v>
+      </c>
+      <c r="H181" t="s">
         <v>764</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>765</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>766</v>
-      </c>
-      <c r="J181" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9969,19 +10022,19 @@
         <v>528</v>
       </c>
       <c r="F182" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G182" t="s">
+        <v>770</v>
+      </c>
+      <c r="H182" t="s">
         <v>771</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>772</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>773</v>
-      </c>
-      <c r="J182" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10004,16 +10057,112 @@
         <v>148</v>
       </c>
       <c r="G183" t="s">
+        <v>774</v>
+      </c>
+      <c r="H183" t="s">
         <v>775</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>776</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>777</v>
       </c>
-      <c r="J183" t="s">
-        <v>778</v>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>180</v>
+      </c>
+      <c r="B184" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" t="s">
+        <v>11</v>
+      </c>
+      <c r="D184" t="s">
+        <v>405</v>
+      </c>
+      <c r="E184" t="s">
+        <v>406</v>
+      </c>
+      <c r="F184" t="s">
+        <v>405</v>
+      </c>
+      <c r="G184" t="s">
+        <v>779</v>
+      </c>
+      <c r="H184" t="s">
+        <v>780</v>
+      </c>
+      <c r="I184" t="s">
+        <v>781</v>
+      </c>
+      <c r="J184" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>181</v>
+      </c>
+      <c r="B185" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" t="s">
+        <v>405</v>
+      </c>
+      <c r="E185" t="s">
+        <v>406</v>
+      </c>
+      <c r="F185" t="s">
+        <v>405</v>
+      </c>
+      <c r="G185" t="s">
+        <v>783</v>
+      </c>
+      <c r="H185" t="s">
+        <v>784</v>
+      </c>
+      <c r="I185" t="s">
+        <v>785</v>
+      </c>
+      <c r="J185" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>182</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
+        <v>405</v>
+      </c>
+      <c r="E186" t="s">
+        <v>406</v>
+      </c>
+      <c r="F186" t="s">
+        <v>405</v>
+      </c>
+      <c r="G186" t="s">
+        <v>787</v>
+      </c>
+      <c r="H186" t="s">
+        <v>788</v>
+      </c>
+      <c r="I186" t="s">
+        <v>789</v>
+      </c>
+      <c r="J186" t="s">
+        <v>790</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582CB12A-AB96-483F-B4C5-730E00523E59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3928B684-6CB2-4BAC-965C-937638D03264}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="915">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -867,9 +867,6 @@
   </si>
   <si>
     <t>Пневматичні з’єднувальні елементи для гальмівних і допоміжних систем транспортних засобів RAUFOSS ABC™ SYSTEM</t>
-  </si>
-  <si>
-    <t>З'єднувач перехідний пневматичний прямий із затискним муфтовим приєднанням та зовнішньою різьбою (RAUFOSS ABC™ SYSTEM)</t>
   </si>
   <si>
     <t>З’єднувач перехідний прямий: з одного боку — муфтове затискне гніздо типу ABC Newline (для пневматичних
@@ -3863,6 +3860,697 @@
   </si>
   <si>
     <t>child3_big_182.jpg</t>
+  </si>
+  <si>
+    <t>З'єднувач перехідний пневматичний прямий із затискним муфтовим приєднанням NEWLINE ТYРЕ-1 та зовнішньою різьбою (RAUFOSS ABC™ SYSTEM)</t>
+  </si>
+  <si>
+    <t>З'єднувач перехідний пневматичний прямий із затискним муфтовим приєднанням NEWLINE ТYРЕ-2 та зовнішньою різьбою (RAUFOSS ABC™ SYSTEM)</t>
+  </si>
+  <si>
+    <t>Прес-маслянки та ковпачки</t>
+  </si>
+  <si>
+    <t>father_6.jpg</t>
+  </si>
+  <si>
+    <t>Прес-маслянки для пластичних мастил та ковпачки</t>
+  </si>
+  <si>
+    <t>child1_18.jpg</t>
+  </si>
+  <si>
+    <t>Прес-маслянки для пластичних мастил</t>
+  </si>
+  <si>
+    <t>Прес-маслянка пряма (тип А)</t>
+  </si>
+  <si>
+    <t>Прес-маслянка призначена для дозованої подачі консистентного мастила до вузлів тертя механізмів через
+стандартний мастильний інструмент (шприц). Забезпечує герметичне з’єднання та запобігає витіканню мастила
+під час нагнітання.
+Конструкція включає корпус із різьбовим приєднанням та зворотний кульковий клапан, який унеможливлює
+зворотний вихід мастила і захищає вузол від забруднень.
+Застосовується в підшипникових вузлах, шарнірах, втулках та інших елементах, що працюють під
+навантаженням. Дає змогу проводити регламентне обслуговування без розбирання обладнання, знижує
+зношування та збільшує ресурс вузлів.
+Особливості та властивості:
+1. Матеріал - сталь з покриттям «білий цинк» (гальванічне цинкування).
+2. Прес-маслянки виготовляються за стандартом DIN 71412 і залежно від форми класифікуються за типами:
+тип A — пряма, стандартна
+тип B — кутова 45 градусів, для кутового доступу
+тип C — кутова 90 градусів, з прямим кутом для найтісніших місць</t>
+  </si>
+  <si>
+    <t>child3_small_183.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_183.jpg</t>
+  </si>
+  <si>
+    <t>Прес-маслянка кутова 45 градусів (тип В)</t>
+  </si>
+  <si>
+    <t>child3_small_184.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_184.jpg</t>
+  </si>
+  <si>
+    <t>Прес-маслянка кутова 90 градусів (тип С)</t>
+  </si>
+  <si>
+    <t>child3_small_185.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_185.jpg</t>
+  </si>
+  <si>
+    <t>Захисні ковпачки для прес-маслянок (різнокольорові)</t>
+  </si>
+  <si>
+    <t>Захисні пластикові ковпачки для прес-маслянок (різнокольорові) призначені для надійного захисту
+вузлів тертя від пилу та бруду, спрощення процесів технічного обслуговування та швидкої ідентифікації
+типу або місця встановлення. Вони сумісні зі стандартними типами прес-маслянок і надійно фіксуються
+на головці ніпеля.</t>
+  </si>
+  <si>
+    <t>child3_small_186.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_186.jpg</t>
+  </si>
+  <si>
+    <t>Рукави високого тиску для гідравлічних та пневматичних систем</t>
+  </si>
+  <si>
+    <t>child1_19.jpg</t>
+  </si>
+  <si>
+    <t>Рукави високого тиску однооплітни - 1SN (прями)</t>
+  </si>
+  <si>
+    <t>Одношаровий гнучкий трубопровід високого тиску. Призначений для транспортування гідравлічних рідин,
+мінеральних масел, емульсій, рідкого палива та стиснених газів.
+Оснащений одним шаром сталевого дротяного обплетення, що забезпечує оптимальний баланс між міцністю,
+легкістю та гнучкістю.
+Укомплектований універсальними прямими фітингами зі сферичним ніпелем та накидною гайкою (метрична
+різьба).
+Особливості та властивості:
+1. Технологія виробництва — відповідають стандарту EN 853 1SN.
+2. Внутрішній шар — маслостійка синтетична гума.
+3. Посилення — один шар сталевого дротяного обплетення.
+4. Зовнішній шар — синтетична гума, стійка до стирання та атмосферних впливів.
+5. Робоча температура — від -40°C до +100°C (короткочасно до +120°C).
+6. Розташування фітингів — пряме з обох сторін .
+7. Тип з’єднання — сфероконічне</t>
+  </si>
+  <si>
+    <t>child3_small_187.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_187.jpg</t>
+  </si>
+  <si>
+    <t>Рукави високого тиску двообплітни - 2SN (прями)</t>
+  </si>
+  <si>
+    <t>Двошаровий гнучкий трубопровід високого тиску. Призначений для транспортування гідравлічних рідин,
+мінеральних масел, емульсій, рідкого палива та стиснених газів.
+Оснащений двома високоміцними сталевими дротяними обплетеннями, що забезпечують підвищену стійкість
+до пікових навантажень та механічних пошкоджень при збереженні необхідної гнучкості.
+Укомплектований універсальними прямими фітингами зі сферичним ніпелем та накидною гайкою (метрична
+різьба).
+Особливості та властивості:
+1. Технологія виробництва — відповідають стандарту EN 853 2SN.
+2. Внутрішній шар — маслостійка синтетична гума.
+3. Посилення — два шари сталевого дротяного обплетення (підвищена міцність).
+4. Зовнішній шар — синтетична гума, стійка до стирання та атмосферних впливів.
+5. Робоча температура — від -40°C до +100°C (короткочасно до +120°C).
+6. Розташування фітингів — пряме з обох сторін .
+7. Тип з’єднання — сфероконічне</t>
+  </si>
+  <si>
+    <t>child3_small_188.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_188.jpg</t>
+  </si>
+  <si>
+    <t>Рукави високого тиску двообплітни - 2SN (кутови 90°)</t>
+  </si>
+  <si>
+    <t>Двошаровий гнучкий трубопровід високого тиску. Призначений для транспортування гідравлічних рідин,
+мінеральних масел, емульсій, рідкого палива та стиснених газів.
+Оснащений двома високоміцними сталевими дротяними обплетеннями, що забезпечують підвищену стійкість
+до пікових навантажень та механічних пошкоджень при збереженні необхідної гнучкості.
+Укомплектований універсальними фітингами зі сферичним ніпелем та накидною гайкою (метрична різьба): один
+прямий, другий — під кутом 90°.
+Особливості та властивості:
+1. Технологія виробництва — відповідають стандарту EN 853 2SN.
+2. Внутрішній шар — маслостійка синтетична гума.
+3. Посилення — два шари сталевого дротяного обплетення (підвищена міцність).
+4. Зовнішній шар — синтетична гума, стійка до стирання та атмосферних впливів.
+5. Робоча температура — від -40°C до +100°C (короткочасно до +120°C).
+6. Конфігурація фітингів — комбінована: з одного боку прямий фітинг, з іншого — під кутом 90°.
+7. Тип з’єднання — сфероконічне</t>
+  </si>
+  <si>
+    <t>child3_small_189.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_189.jpg</t>
+  </si>
+  <si>
+    <t>father_7.jpg</t>
+  </si>
+  <si>
+    <t>Універсальні формовані рукави та патрубки для систем охолодження та опалення SAE J20</t>
+  </si>
+  <si>
+    <t>child1_20.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий прямий (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок прямий універсальний — еластичний з’єднувальний елемент, призначений передусім
+для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним
+кордом, що забезпечує підвищену міцність, стійкість до тиску та температурних коливань. Характеризується
+високою еластичністю, довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — силіконовий HD-7770, гладкий, стійкий до охолоджувальних рідин (антифризів).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_190.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_190.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий прямий модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок прямий універсальний — еластичний з’єднувальний елемент, призначений передусім
+для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань. Внутрішній шар (лайнер)
+виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує стійкість до сучасних
+охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю, довговічністю та
+стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_191.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_191.jpg</t>
+  </si>
+  <si>
+    <t>Рукав силіконовий гофрований модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий рукав гофрований універсальний — еластичний з’єднувальний елемент, призначений передусім
+для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом
+та додатково підсиленого спіраллю зі сталевої проволоки, що забезпечує підвищену міцність, стійкість до
+вакууму, деформацій та перегинів.
+Гофрована конструкція надає виробу підвищену гнучкість і дозволяє використовувати його в умовах складної
+геометрії монтажу без втрати прохідного перерізу.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що забезпечує
+повну сумісність зі всіма охолоджувальними рідинами (антифризами) та хімічними реагентами.
+Характеризується високою еластичністю, довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Спіральне підсилення та гофрована конструкція — інтегрована спіраль зі сталевої проволоки формує гофровану
+структуру.
+4. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+5. Температурний діапазон експлуатації: від –50 °C до +175 °C
+6. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури рукава.</t>
+  </si>
+  <si>
+    <t>child3_small_192.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_192.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий кутовий 45° (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок кутовий 45 градусів універсальний — еластичний з’єднувальний елемент, призначений
+передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань. Характеризується високою
+еластичністю, довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — силіконовий HD-7770, гладкий, стійкий до охолоджувальних рідин (антифризів).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон.
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_193.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_193.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий кутовий 45° модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок кутовий 45 градусів універсальний — еластичний з’єднувальний елемент, призначений
+передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю,
+довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_194.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_194.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок гумовий кутовий системи охолодження та опалення 45° (універсальний)</t>
+  </si>
+  <si>
+    <t>Високотехнологічний кутовий гумовий патрубок 45 градусів, універсальний, спеціально розроблений для
+циркуляції антифризів і теплоносіїв у системах охолодження автотракторної та спеціальної техніки.
+Відповідність міжнародному стандарту SAE J20 R3 гарантує надійність у складних умовах експлуатації.
+Конструкція та особливості:
+1. Внутрішній шар – EPDM, стійкий до антифризу, води, озону та перепадів температури.
+2. Армування – один текстильний каркас для забезпечення міцності та форми.
+3. Зовнішній шар – EPDM або синтетична гума, стійка до атмосферних впливів та озону.
+4. Робочі температури – від −40 °C до +125 °C
+5. Застосування – системи охолодження та опалення автотракторів і спеціальної техніки</t>
+  </si>
+  <si>
+    <t>child3_small_195.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_195.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий кутовий 90° (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок кутовий 90 градусів універсальний — еластичний з’єднувальний елемент, призначений
+передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним
+кордом, що забезпечує підвищену міцність, стійкість до тиску та температурних коливань. Характеризується
+високою еластичністю, довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — силіконовий HD-7770, гладкий, стійкий до охолоджувальних рідин (антифризів).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон.
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_196.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_196.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий кутовий 90° модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок кутовий 90 градусів універсальний — еластичний з’єднувальний елемент, призначений
+передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю,
+довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_197.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_197.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок гумовий кутовий системи охолодження та опалення 90° (універсальний)</t>
+  </si>
+  <si>
+    <t>Високотехнологічний гумовий кутовий патрубок 90 градусів, універсальний, спеціально розроблений для
+циркуляції антифризів і теплоносіїв у системах охолодження автотракторної та спеціальної техніки.
+Відповідність міжнародному стандарту SAE J20 R3 гарантує надійність у складних умовах експлуатації.
+Конструкція та особливості:
+1. Внутрішній шар – EPDM, стійкий до антифризу, води, озону та перепадів температури.
+2. Армування – один текстильний каркас для забезпечення міцності та форми.
+3. Зовнішній шар – EPDM або синтетична гума, стійка до атмосферних впливів та озону.
+4. Робочі температури – від −40 °C до +125 °C
+5. Застосування – системи охолодження та опалення автотракторів і спеціальної техніки</t>
+  </si>
+  <si>
+    <t>child3_small_198.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_198.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий U-подібний 180° модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок U-подібний 180 градусів універсальний — еластичний з’єднувальний елемент,
+призначений передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах
+автомобільної, сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків,
+радіаторів, інтеркулерів та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю,
+довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_199.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_199.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий кутовий V-подібний 135° модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок кутовий V-подібний 135 градусів універсальний — еластичний з’єднувальний елемент,
+призначений передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах
+автомобільної, сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків,
+радіаторів, інтеркулерів та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю,
+довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_200.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_200.jpg</t>
+  </si>
+  <si>
+    <t>Патрубок силіконовий редукційний модифікований (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий патрубок редукційний універсальний — еластичний з’єднувальний елемент, призначений
+передусім для транспортування охолоджувальної рідини (антифризу), а також повітря в системах автомобільної,
+сільськогосподарської та спеціальної техніки. Використовується для з’єднання патрубків, радіаторів, інтеркулерів
+та інших вузлів, забезпечуючи перехід (редукцію) між елементами з різними діаметрами трубопроводів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує підвищену міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів. Характеризується високою еластичністю,
+довговічністю та стабільністю геометричних розмірів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ. Стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13).
+2. Армування — 4 шари текстильного корду (поліестер/нейлон).
+3. Зовнішній шар — силіконовий HD-7770, стійкий до впливу температур, озону, ультрафіолету та механічних
+навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R2
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури патрубка.</t>
+  </si>
+  <si>
+    <t>child3_small_201.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_201.jpg</t>
+  </si>
+  <si>
+    <t>Універсальні довгомірні рукави для систем охолодження та опалення SAE J20</t>
+  </si>
+  <si>
+    <t>child1_21.jpg</t>
+  </si>
+  <si>
+    <t>Рукав силіконовий для систем охолодження та опалення (універсальний)</t>
+  </si>
+  <si>
+    <t>Силіконовий модифікований рукав універсальний для систем охолодження та опалення — еластичний
+з’єднувальний елемент, призначений передусім для транспортування охолоджувальної рідини (антифризу) в
+автомобільній, сільськогосподарській та спеціальній техніці. Використовується для з’єднання патрубків,
+радіаторів та інших вузлів.
+Виготовлений із високоякісного силікону VMQ (Silicone Rubber) типу HD-7770, армованого текстильним кордом,
+що забезпечує достатню міцність, стійкість до тиску та температурних коливань.
+Внутрішній шар (лайнер) виконаний з модифікованого силікону помаранчевого кольору FVMQ, що підвищує
+стійкість до сучасних охолоджувальних рідин та хімічних реагентів.
+Конструкція та особливості:
+1. Внутрішній шар (лайнер) — виконаний з модифікованого силікону помаранчевого кольору FVMQ, стійкий до
+агресивних охолоджувальних рідин, включаючи сучасні антифризи (G12, G12++, G13)
+2. Армування — 1 шар текстильного корду (поліестер/нейлон)
+3. Зовнішній шар — силіконовий HD-7770 (VMQ), стійкий до впливу температур, озону, ультрафіолету та
+механічних навантажень
+4. Температурний діапазон експлуатації: від –50 °C до +175 °C
+5. За своїми характеристиками відповідає вимогам SAE J20 R3
+Не призначений для транспортування нафтопродуктів (бензину, дизельного палива, олив).
+Зважаючи на високу еластичність силікону, рекомендовано використовувати силові хомути типу T-bolt. Вони
+забезпечують рівномірне обтискання та надійну фіксацію по всій окружності, запобігаючи пошкодженню
+структури рукава.</t>
+  </si>
+  <si>
+    <t>child3_small_202.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_202.jpg</t>
+  </si>
+  <si>
+    <t>Рукав гумовий для систем охолодження та опалення (універсальний)</t>
+  </si>
+  <si>
+    <t>Високотехнологічний гумовий рукав, спеціально розроблений для циркуляції антифризів і теплоносіїв у системах
+охолодження автотракторної та спеціальної техніки.
+Відповідність міжнародному стандарту SAE J20 R3 гарантує надійність у складних умовах експлуатації.
+Конструкція та особливості:
+1. Внутрішній шар – EPDM, стійкий до антифризу, води, озону та перепадів температури.
+2. Армування – один текстильний каркас для забезпечення міцності та форми.
+3. Зовнішній шар – EPDM або синтетична гума, стійка до атмосферних впливів та озону.
+4. Робочі температури – від −40 °C до +125 °C
+5. Застосування – системи охолодження та опалення автотракторів і спеціальної техніки</t>
+  </si>
+  <si>
+    <t>child3_small_203.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_203.jpg</t>
+  </si>
+  <si>
+    <t>Рукава паливні низького тиску SAE J30 R7</t>
+  </si>
+  <si>
+    <t>child1_22.jpg</t>
+  </si>
+  <si>
+    <t>Рукав паливний низького тиску</t>
+  </si>
+  <si>
+    <t>Рукави, виготовлені відповідно до стандарту SAE J30 R7, призначені для транспортування бензину, дизельного
+палива та мінеральних олив у системах низького тиску. Застосовуються у паливних магістралях карбюраторних і
+дизельних двигунів, зворотних лініях, а також у промисловому та сільськогосподарському обладнанні.
+Особливості та властивості:
+1. Температурний діапазон – від −30 °C до +125 °C.
+2. Робочий тиск – приблизно 10–20 бар.
+3. Тип палива – бензин, дизельне паливо, мастила, біоетанол (E10–E85)
+4. Конструкція – синтетична гума (NBR), текстильне плетене армування, зовнішнє покриття з озоностійкої гумі.
+5. Обмеження – не призначений для систем високого тиску (паливного вприску)</t>
+  </si>
+  <si>
+    <t>child3_small_204.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_204.jpg</t>
+  </si>
+  <si>
+    <t>Трубки термопластичні для пневматичних автомобільних і промислових систем</t>
+  </si>
+  <si>
+    <t>child1_23.jpg</t>
+  </si>
+  <si>
+    <t>Трубки для пневматичних, автомобільних та промислових систем виготовлені з поліамідів PA11 та PA12
+відповідно до стандартів DIN 74324 та DIN 73378. Ці стандарти чітко регламентують параметри та характеристики
+експлуатаційних властивостей трубопроводів.
+Поліаміди PA11 та PA12 мають максимально схожі властивості, достатню еластичність у широкому діапазоні
+температур та забезпечують запас міцності, що неодноразово перевищує номінальний робочий тиск.
+Трубки з обох матеріалів широко застосовуються для побудови пневматичних систем комерційних автомобілів
+усіх відомих брендів, а також широко використовуються у промислових пневматичних системах.
+Властивості матеріалу:
+1. Висока механічна міцність — забезпечує надійність при роботі під тиском (особливо для PA11)
+2. Еластичність — зберігається у широкому діапазоні температур, стійкість до вібрацій та згинання
+3. Низьке водопоглинання (особливо PA12) — стабільність геометричних і механічних характеристик
+4. Стійкість до хімічних середовищ — масла, паливо, технічні рідини
+5. Зносостійкість — тривалий термін експлуатації в умовах динамічних навантажень
+6. Термостійкість — робота в діапазоні від −40 до +100 °C
+7. Низька газопроникність — важливо для пневматичних систем</t>
+  </si>
+  <si>
+    <t>child3_small_205.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_205.jpg</t>
+  </si>
+  <si>
+    <t>Пневмошланги (рукави) із самозапірними швидкороз’ємними з’єднаннями</t>
+  </si>
+  <si>
+    <t>child1_24.jpg</t>
+  </si>
+  <si>
+    <t>Шланг пневматичний спіральний (з муфтами БРС)</t>
+  </si>
+  <si>
+    <t>child3_small_206.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_206.jpg</t>
+  </si>
+  <si>
+    <t>Рукав пневматичний (з муфтами БРС)</t>
+  </si>
+  <si>
+    <t>child3_small_207.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_207.jpg</t>
+  </si>
+  <si>
+    <t>Пневматичні комплекти для продування</t>
+  </si>
+  <si>
+    <t>child1_25.jpg</t>
+  </si>
+  <si>
+    <t>Продувальний пістолет зі шлангом (комплект)</t>
+  </si>
+  <si>
+    <t>child3_small_208.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_208.jpg</t>
+  </si>
+  <si>
+    <t>Рукави пневматичні для підкачування шин у зборі</t>
+  </si>
+  <si>
+    <t>child1_26.jpg</t>
+  </si>
+  <si>
+    <t>child3_small_209.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_209.jpg</t>
+  </si>
+  <si>
+    <t>Багатоцільові рукави та трубки</t>
   </si>
 </sst>
 </file>
@@ -4219,7 +4907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -4695,10 +5383,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -5367,16 +6055,16 @@
         <v>148</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -5399,16 +6087,16 @@
         <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>149</v>
+        <v>791</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -5422,25 +6110,25 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -5454,25 +6142,25 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -5486,25 +6174,25 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G40" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5518,25 +6206,25 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G41" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -5550,25 +6238,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -5582,25 +6270,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G43" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -5614,25 +6302,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G44" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -5646,25 +6334,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G45" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -5678,30 +6366,30 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G46" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>10</v>
@@ -5710,30 +6398,30 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G47" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>10</v>
@@ -5742,25 +6430,25 @@
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G48" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H48" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -5774,25 +6462,25 @@
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G49" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -5806,25 +6494,25 @@
         <v>11</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="G50" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>761</v>
-      </c>
       <c r="I50" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -5838,25 +6526,25 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="G51" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5864,31 +6552,31 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="H52" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="J52" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5896,31 +6584,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="J53" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5928,31 +6616,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G54" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5960,31 +6648,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G55" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5992,31 +6680,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G56" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -6024,31 +6712,31 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G57" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="I57" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -6056,31 +6744,31 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G58" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -6088,31 +6776,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="G59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -6126,25 +6814,25 @@
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="H60" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="I60" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6158,25 +6846,25 @@
         <v>11</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="G61" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="J61" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -6190,25 +6878,25 @@
         <v>11</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="G62" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -6216,31 +6904,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D63" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -6248,31 +6936,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D64" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G64" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="I64" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -6280,31 +6968,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D65" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G65" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -6312,31 +7000,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D66" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G66" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="J66" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -6344,31 +7032,31 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D67" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G67" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -6376,31 +7064,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D68" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G68" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -6408,31 +7096,31 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D69" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G69" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -6440,31 +7128,31 @@
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D70" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G70" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -6472,31 +7160,31 @@
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D71" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G71" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="J71" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -6504,31 +7192,31 @@
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D72" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G72" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -6536,31 +7224,31 @@
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D73" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G73" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -6568,31 +7256,31 @@
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D74" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="G74" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -6600,29 +7288,29 @@
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H75" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -6630,29 +7318,29 @@
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="I76" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -6660,29 +7348,29 @@
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H77" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -6690,29 +7378,29 @@
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -6720,31 +7408,31 @@
         <v>80</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D79" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G79" s="2" t="s">
+      <c r="H79" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6752,31 +7440,31 @@
         <v>81</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D80" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="J80" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6784,31 +7472,31 @@
         <v>82</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D81" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H81" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="J81" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6816,31 +7504,31 @@
         <v>83</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D82" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G82" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="J82" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6848,31 +7536,31 @@
         <v>84</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D83" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F83" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G83" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="J83" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6880,31 +7568,31 @@
         <v>85</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D84" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G84" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="J84" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -6912,31 +7600,31 @@
         <v>86</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D85" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F85" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G85" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6944,31 +7632,31 @@
         <v>87</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D86" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F86" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G86" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="I86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6976,31 +7664,31 @@
         <v>88</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D87" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G87" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="J87" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -7008,31 +7696,31 @@
         <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D88" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -7040,31 +7728,31 @@
         <v>90</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D89" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F89" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G89" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="I89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="J89" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -7072,31 +7760,31 @@
         <v>91</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D90" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F90" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="J90" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -7104,31 +7792,31 @@
         <v>92</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D91" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G91" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H91" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="I91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="J91" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,31 +7824,31 @@
         <v>93</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D92" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G92" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="J92" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -7168,31 +7856,31 @@
         <v>94</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D93" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G93" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="H93" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -7200,31 +7888,31 @@
         <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D94" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G94" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="I94" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="J94" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -7232,31 +7920,31 @@
         <v>96</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D95" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G95" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="I95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="J95" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -7264,31 +7952,31 @@
         <v>97</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D96" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G96" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -7296,31 +7984,31 @@
         <v>98</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D97" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G97" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H97" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="J97" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -7328,31 +8016,31 @@
         <v>99</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D98" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G98" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -7360,31 +8048,31 @@
         <v>100</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D99" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G99" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="J99" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -7392,31 +8080,31 @@
         <v>101</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D100" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="J100" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -7424,31 +8112,31 @@
         <v>101</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D101" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H101" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="J101" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -7462,25 +8150,25 @@
         <v>11</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="F102" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="G102" s="2" t="s">
+      <c r="H102" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="J102" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -7494,25 +8182,25 @@
         <v>11</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G103" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="J103" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -7526,25 +8214,25 @@
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F104" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G104" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="I104" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="J104" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -7558,25 +8246,25 @@
         <v>11</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G105" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="J105" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -7590,25 +8278,25 @@
         <v>11</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F106" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G106" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="J106" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -7622,25 +8310,25 @@
         <v>11</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G107" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="J107" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -7654,25 +8342,25 @@
         <v>11</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F108" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G108" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H108" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="I108" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="I108" s="1" t="s">
+      <c r="J108" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -7680,31 +8368,31 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="F109" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="I109" s="1" t="s">
+      <c r="J109" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -7712,31 +8400,31 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G110" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H110" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="I110" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="J110" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -7744,31 +8432,31 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G111" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="H111" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="I111" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="J111" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -7776,31 +8464,31 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G112" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="I112" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="J112" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7808,31 +8496,31 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F113" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G113" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="I113" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="J113" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -7840,31 +8528,31 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F114" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G114" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H114" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="J114" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -7872,31 +8560,31 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G115" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H115" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="I115" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="J115" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7904,31 +8592,31 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G116" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H116" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="I116" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="I116" s="1" t="s">
+      <c r="J116" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7936,31 +8624,31 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G117" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="I117" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="J117" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7968,31 +8656,31 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G118" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H118" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="J118" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -8000,31 +8688,31 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G119" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H119" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="I119" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="I119" s="1" t="s">
+      <c r="J119" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -8032,31 +8720,31 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G120" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H120" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="I120" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8064,31 +8752,31 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G121" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H121" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="I121" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="J121" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -8096,31 +8784,31 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F122" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G122" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="H122" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="I122" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="J122" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8128,31 +8816,31 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F123" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G123" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="H123" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="I123" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="J123" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -8160,31 +8848,31 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F124" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G124" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H124" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="I124" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I124" s="1" t="s">
+      <c r="J124" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -8192,31 +8880,31 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F125" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G125" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="H125" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="I125" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="J125" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -8224,29 +8912,29 @@
         <v>129</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="H126" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I126" s="1" t="s">
+      <c r="J126" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -8254,29 +8942,29 @@
         <v>130</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="H127" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="J127" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -8284,31 +8972,31 @@
         <v>131</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D128" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="F128" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="H128" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="H128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="I128" s="1" t="s">
+      <c r="J128" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -8316,31 +9004,31 @@
         <v>132</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D129" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="F129" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H129" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="I129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="J129" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -8348,31 +9036,31 @@
         <v>133</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D130" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="F130" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G130" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="I130" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="I130" s="1" t="s">
+      <c r="J130" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -8380,31 +9068,31 @@
         <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D131" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G131" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="G131" s="2" t="s">
+      <c r="H131" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="J131" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -8412,31 +9100,31 @@
         <v>135</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D132" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G132" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="J132" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -8444,31 +9132,31 @@
         <v>137</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G133" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="I133" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J133" t="s">
         <v>543</v>
-      </c>
-      <c r="J133" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -8476,31 +9164,31 @@
         <v>138</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G134" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="I134" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="J134" t="s">
         <v>546</v>
-      </c>
-      <c r="J134" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8508,31 +9196,31 @@
         <v>139</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G135" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="I135" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J135" t="s">
         <v>549</v>
-      </c>
-      <c r="J135" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8540,31 +9228,31 @@
         <v>140</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G136" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="J136" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -8572,31 +9260,31 @@
         <v>141</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="F137" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G137" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="I137" s="1" t="s">
+      <c r="J137" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -8604,31 +9292,31 @@
         <v>142</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G138" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H138" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="J138" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -8636,31 +9324,31 @@
         <v>143</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F139" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G139" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="H139" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="H139" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="J139" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -8668,31 +9356,31 @@
         <v>144</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="G140" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="G140" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="H140" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="J140" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -8700,31 +9388,31 @@
         <v>145</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G141" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H141" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="J141" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8732,31 +9420,31 @@
         <v>146</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G142" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="H142" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="H142" s="1" t="s">
+      <c r="I142" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="J142" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -8764,31 +9452,31 @@
         <v>147</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F143" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G143" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H143" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="J143" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="J143" s="1" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8796,31 +9484,31 @@
         <v>148</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G144" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H144" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="I144" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="J144" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -8828,31 +9516,31 @@
         <v>149</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F145" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G145" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="H145" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="H145" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="I145" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J145" t="s">
         <v>584</v>
-      </c>
-      <c r="J145" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -8860,31 +9548,31 @@
         <v>150</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="F146" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F146" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G146" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="H146" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="I146" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="J146" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -8892,31 +9580,31 @@
         <v>151</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F147" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G147" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="H147" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="H147" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="I147" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J147" t="s">
         <v>590</v>
-      </c>
-      <c r="J147" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -8924,31 +9612,31 @@
         <v>152</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F148" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G148" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="H148" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="H148" s="1" t="s">
-        <v>738</v>
-      </c>
       <c r="I148" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="J148" t="s">
         <v>592</v>
-      </c>
-      <c r="J148" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -8956,31 +9644,31 @@
         <v>153</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="E149" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="F149" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F149" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="G149" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H149" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="H149" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="I149" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="J149" t="s">
         <v>594</v>
-      </c>
-      <c r="J149" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -9003,16 +9691,16 @@
         <v>148</v>
       </c>
       <c r="G150" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="H150" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="I150" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="I150" s="1" t="s">
+      <c r="J150" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -9035,16 +9723,16 @@
         <v>148</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="I151" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="J151" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -9067,16 +9755,16 @@
         <v>148</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="I152" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="J152" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -9099,16 +9787,16 @@
         <v>148</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="I153" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="J153" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -9131,16 +9819,16 @@
         <v>148</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="I154" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="J154" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9163,16 +9851,16 @@
         <v>148</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="I155" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="I155" s="1" t="s">
+      <c r="J155" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9195,16 +9883,16 @@
         <v>148</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="I156" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="J156" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9212,31 +9900,31 @@
         <v>161</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D157" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="F157" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="G157" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="F157" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G157" s="1" t="s">
+      <c r="H157" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="H157" s="1" t="s">
+      <c r="I157" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="I157" s="1" t="s">
+      <c r="J157" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9244,31 +9932,31 @@
         <v>162</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D158" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F158" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="H158" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="H158" s="1" t="s">
+      <c r="I158" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="I158" s="1" t="s">
+      <c r="J158" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9276,31 +9964,31 @@
         <v>163</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D159" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F159" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H159" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="J159" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="J159" s="1" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9308,31 +9996,31 @@
         <v>164</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D160" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F160" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -9340,31 +10028,31 @@
         <v>165</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D161" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F161" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G161" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="H161" s="1" t="s">
+      <c r="I161" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="J161" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -9372,31 +10060,31 @@
         <v>166</v>
       </c>
       <c r="B162" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D162" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E162" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F162" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="H162" s="1" t="s">
+      <c r="I162" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="I162" s="1" t="s">
+      <c r="J162" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -9404,31 +10092,31 @@
         <v>167</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D163" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E163" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F163" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="H163" s="1" t="s">
+      <c r="I163" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="I163" s="1" t="s">
+      <c r="J163" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -9436,31 +10124,31 @@
         <v>168</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D164" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E164" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F164" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="H164" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="I164" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="J164" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -9468,66 +10156,66 @@
         <v>169</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D165" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E165" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="F165" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H165" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="J165" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>658</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="G166" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="H166" s="1" t="s">
+      <c r="I166" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="I166" s="1" t="s">
+      <c r="J166" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>10</v>
@@ -9545,21 +10233,21 @@
         <v>95</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>96</v>
       </c>
       <c r="I167" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="J167" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>10</v>
@@ -9577,176 +10265,176 @@
         <v>95</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H168" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="I168" s="1" t="s">
+      <c r="J168" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G169" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G169" s="2" t="s">
+      <c r="H169" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="I169" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="J169" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G170" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G170" s="2" t="s">
+      <c r="H170" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="I170" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="I170" s="1" t="s">
+      <c r="J170" s="1" t="s">
         <v>677</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G171" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G171" s="1" t="s">
+      <c r="H171" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="I171" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="I171" s="1" t="s">
+      <c r="J171" s="1" t="s">
         <v>682</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G172" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G172" s="2" t="s">
+      <c r="H172" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="H172" s="1" t="s">
+      <c r="I172" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="I172" s="1" t="s">
+      <c r="J172" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G173" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G173" s="2" t="s">
+      <c r="H173" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="H173" s="1" t="s">
+      <c r="I173" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="I173" s="1" t="s">
+      <c r="J173" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -9754,31 +10442,31 @@
         <v>170</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D174" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G174" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="H174" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="H174" s="1" t="s">
+      <c r="I174" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="J174" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -9786,31 +10474,31 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D175" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E175" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="G175" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="H175" s="1" t="s">
+      <c r="I175" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="I175" s="1" t="s">
+      <c r="J175" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -9818,31 +10506,31 @@
         <v>172</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D176" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E176" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="G176" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="H176" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="I176" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="I176" s="1" t="s">
+      <c r="J176" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -9850,31 +10538,31 @@
         <v>173</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D177" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E177" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F177" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="G177" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="H177" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="I177" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J177" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9882,31 +10570,31 @@
         <v>174</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D178" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G178" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="E178" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="H178" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="H178" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="I178" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="J178" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -9914,31 +10602,31 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
+        <v>434</v>
+      </c>
+      <c r="C179" t="s">
         <v>435</v>
       </c>
-      <c r="C179" t="s">
-        <v>436</v>
-      </c>
       <c r="D179" t="s">
+        <v>750</v>
+      </c>
+      <c r="E179" t="s">
+        <v>527</v>
+      </c>
+      <c r="F179" t="s">
+        <v>766</v>
+      </c>
+      <c r="G179" t="s">
+        <v>767</v>
+      </c>
+      <c r="H179" t="s">
+        <v>768</v>
+      </c>
+      <c r="I179" t="s">
         <v>751</v>
       </c>
-      <c r="E179" t="s">
-        <v>528</v>
-      </c>
-      <c r="F179" t="s">
-        <v>767</v>
-      </c>
-      <c r="G179" t="s">
-        <v>768</v>
-      </c>
-      <c r="H179" t="s">
-        <v>769</v>
-      </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>752</v>
-      </c>
-      <c r="J179" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -9946,31 +10634,31 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
+        <v>214</v>
+      </c>
+      <c r="C180" t="s">
         <v>215</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>216</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>217</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>218</v>
       </c>
-      <c r="F180" t="s">
-        <v>219</v>
-      </c>
       <c r="G180" t="s">
+        <v>757</v>
+      </c>
+      <c r="H180" t="s">
         <v>758</v>
       </c>
-      <c r="H180" t="s">
-        <v>759</v>
-      </c>
       <c r="I180" t="s">
+        <v>755</v>
+      </c>
+      <c r="J180" t="s">
         <v>756</v>
-      </c>
-      <c r="J180" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -9984,25 +10672,25 @@
         <v>11</v>
       </c>
       <c r="D181" t="s">
+        <v>155</v>
+      </c>
+      <c r="E181" t="s">
         <v>156</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>157</v>
       </c>
-      <c r="F181" t="s">
-        <v>158</v>
-      </c>
       <c r="G181" t="s">
+        <v>762</v>
+      </c>
+      <c r="H181" t="s">
         <v>763</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>764</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>765</v>
-      </c>
-      <c r="J181" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -10010,31 +10698,31 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
+        <v>434</v>
+      </c>
+      <c r="C182" t="s">
         <v>435</v>
       </c>
-      <c r="C182" t="s">
-        <v>436</v>
-      </c>
       <c r="D182" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E182" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F182" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G182" t="s">
+        <v>769</v>
+      </c>
+      <c r="H182" t="s">
         <v>770</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>771</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>772</v>
-      </c>
-      <c r="J182" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10057,16 +10745,16 @@
         <v>148</v>
       </c>
       <c r="G183" t="s">
+        <v>773</v>
+      </c>
+      <c r="H183" t="s">
         <v>774</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>775</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>776</v>
-      </c>
-      <c r="J183" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -10080,25 +10768,25 @@
         <v>11</v>
       </c>
       <c r="D184" t="s">
+        <v>404</v>
+      </c>
+      <c r="E184" t="s">
         <v>405</v>
       </c>
-      <c r="E184" t="s">
-        <v>406</v>
-      </c>
       <c r="F184" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G184" t="s">
+        <v>778</v>
+      </c>
+      <c r="H184" t="s">
         <v>779</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>780</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>781</v>
-      </c>
-      <c r="J184" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,25 +10800,25 @@
         <v>11</v>
       </c>
       <c r="D185" t="s">
+        <v>404</v>
+      </c>
+      <c r="E185" t="s">
         <v>405</v>
       </c>
-      <c r="E185" t="s">
-        <v>406</v>
-      </c>
       <c r="F185" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G185" t="s">
+        <v>782</v>
+      </c>
+      <c r="H185" t="s">
         <v>783</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>784</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>785</v>
-      </c>
-      <c r="J185" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -10144,25 +10832,889 @@
         <v>11</v>
       </c>
       <c r="D186" t="s">
+        <v>404</v>
+      </c>
+      <c r="E186" t="s">
         <v>405</v>
       </c>
-      <c r="E186" t="s">
-        <v>406</v>
-      </c>
       <c r="F186" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G186" t="s">
+        <v>786</v>
+      </c>
+      <c r="H186" t="s">
         <v>787</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>788</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>789</v>
       </c>
-      <c r="J186" t="s">
-        <v>790</v>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>183</v>
+      </c>
+      <c r="B187" t="s">
+        <v>792</v>
+      </c>
+      <c r="C187" t="s">
+        <v>793</v>
+      </c>
+      <c r="D187" t="s">
+        <v>794</v>
+      </c>
+      <c r="E187" t="s">
+        <v>795</v>
+      </c>
+      <c r="F187" t="s">
+        <v>796</v>
+      </c>
+      <c r="G187" t="s">
+        <v>797</v>
+      </c>
+      <c r="H187" t="s">
+        <v>798</v>
+      </c>
+      <c r="I187" t="s">
+        <v>799</v>
+      </c>
+      <c r="J187" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>184</v>
+      </c>
+      <c r="B188" t="s">
+        <v>792</v>
+      </c>
+      <c r="C188" t="s">
+        <v>793</v>
+      </c>
+      <c r="D188" t="s">
+        <v>794</v>
+      </c>
+      <c r="E188" t="s">
+        <v>795</v>
+      </c>
+      <c r="F188" t="s">
+        <v>796</v>
+      </c>
+      <c r="G188" t="s">
+        <v>801</v>
+      </c>
+      <c r="H188" t="s">
+        <v>798</v>
+      </c>
+      <c r="I188" t="s">
+        <v>802</v>
+      </c>
+      <c r="J188" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>185</v>
+      </c>
+      <c r="B189" t="s">
+        <v>792</v>
+      </c>
+      <c r="C189" t="s">
+        <v>793</v>
+      </c>
+      <c r="D189" t="s">
+        <v>794</v>
+      </c>
+      <c r="E189" t="s">
+        <v>795</v>
+      </c>
+      <c r="F189" t="s">
+        <v>796</v>
+      </c>
+      <c r="G189" t="s">
+        <v>804</v>
+      </c>
+      <c r="H189" t="s">
+        <v>798</v>
+      </c>
+      <c r="I189" t="s">
+        <v>805</v>
+      </c>
+      <c r="J189" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>186</v>
+      </c>
+      <c r="B190" t="s">
+        <v>792</v>
+      </c>
+      <c r="C190" t="s">
+        <v>793</v>
+      </c>
+      <c r="D190" t="s">
+        <v>794</v>
+      </c>
+      <c r="E190" t="s">
+        <v>795</v>
+      </c>
+      <c r="F190" t="s">
+        <v>807</v>
+      </c>
+      <c r="G190" t="s">
+        <v>807</v>
+      </c>
+      <c r="H190" t="s">
+        <v>808</v>
+      </c>
+      <c r="I190" t="s">
+        <v>809</v>
+      </c>
+      <c r="J190" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>187</v>
+      </c>
+      <c r="B191" t="s">
+        <v>434</v>
+      </c>
+      <c r="C191" t="s">
+        <v>435</v>
+      </c>
+      <c r="D191" t="s">
+        <v>811</v>
+      </c>
+      <c r="E191" t="s">
+        <v>812</v>
+      </c>
+      <c r="F191" t="s">
+        <v>811</v>
+      </c>
+      <c r="G191" t="s">
+        <v>813</v>
+      </c>
+      <c r="H191" t="s">
+        <v>814</v>
+      </c>
+      <c r="I191" t="s">
+        <v>815</v>
+      </c>
+      <c r="J191" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>188</v>
+      </c>
+      <c r="B192" t="s">
+        <v>434</v>
+      </c>
+      <c r="C192" t="s">
+        <v>435</v>
+      </c>
+      <c r="D192" t="s">
+        <v>811</v>
+      </c>
+      <c r="E192" t="s">
+        <v>812</v>
+      </c>
+      <c r="F192" t="s">
+        <v>811</v>
+      </c>
+      <c r="G192" t="s">
+        <v>817</v>
+      </c>
+      <c r="H192" t="s">
+        <v>818</v>
+      </c>
+      <c r="I192" t="s">
+        <v>819</v>
+      </c>
+      <c r="J192" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>189</v>
+      </c>
+      <c r="B193" t="s">
+        <v>434</v>
+      </c>
+      <c r="C193" t="s">
+        <v>435</v>
+      </c>
+      <c r="D193" t="s">
+        <v>811</v>
+      </c>
+      <c r="E193" t="s">
+        <v>812</v>
+      </c>
+      <c r="F193" t="s">
+        <v>811</v>
+      </c>
+      <c r="G193" t="s">
+        <v>821</v>
+      </c>
+      <c r="H193" t="s">
+        <v>822</v>
+      </c>
+      <c r="I193" t="s">
+        <v>823</v>
+      </c>
+      <c r="J193" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>190</v>
+      </c>
+      <c r="B194" t="s">
+        <v>914</v>
+      </c>
+      <c r="C194" t="s">
+        <v>825</v>
+      </c>
+      <c r="D194" t="s">
+        <v>826</v>
+      </c>
+      <c r="E194" t="s">
+        <v>827</v>
+      </c>
+      <c r="F194" t="s">
+        <v>826</v>
+      </c>
+      <c r="G194" t="s">
+        <v>828</v>
+      </c>
+      <c r="H194" t="s">
+        <v>829</v>
+      </c>
+      <c r="I194" t="s">
+        <v>830</v>
+      </c>
+      <c r="J194" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>191</v>
+      </c>
+      <c r="B195" t="s">
+        <v>914</v>
+      </c>
+      <c r="C195" t="s">
+        <v>825</v>
+      </c>
+      <c r="D195" t="s">
+        <v>826</v>
+      </c>
+      <c r="E195" t="s">
+        <v>827</v>
+      </c>
+      <c r="F195" t="s">
+        <v>826</v>
+      </c>
+      <c r="G195" t="s">
+        <v>832</v>
+      </c>
+      <c r="H195" t="s">
+        <v>833</v>
+      </c>
+      <c r="I195" t="s">
+        <v>834</v>
+      </c>
+      <c r="J195" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>192</v>
+      </c>
+      <c r="B196" t="s">
+        <v>914</v>
+      </c>
+      <c r="C196" t="s">
+        <v>825</v>
+      </c>
+      <c r="D196" t="s">
+        <v>826</v>
+      </c>
+      <c r="E196" t="s">
+        <v>827</v>
+      </c>
+      <c r="F196" t="s">
+        <v>826</v>
+      </c>
+      <c r="G196" t="s">
+        <v>836</v>
+      </c>
+      <c r="H196" t="s">
+        <v>837</v>
+      </c>
+      <c r="I196" t="s">
+        <v>838</v>
+      </c>
+      <c r="J196" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>193</v>
+      </c>
+      <c r="B197" t="s">
+        <v>914</v>
+      </c>
+      <c r="C197" t="s">
+        <v>825</v>
+      </c>
+      <c r="D197" t="s">
+        <v>826</v>
+      </c>
+      <c r="E197" t="s">
+        <v>827</v>
+      </c>
+      <c r="F197" t="s">
+        <v>826</v>
+      </c>
+      <c r="G197" t="s">
+        <v>840</v>
+      </c>
+      <c r="H197" t="s">
+        <v>841</v>
+      </c>
+      <c r="I197" t="s">
+        <v>842</v>
+      </c>
+      <c r="J197" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>194</v>
+      </c>
+      <c r="B198" t="s">
+        <v>914</v>
+      </c>
+      <c r="C198" t="s">
+        <v>825</v>
+      </c>
+      <c r="D198" t="s">
+        <v>826</v>
+      </c>
+      <c r="E198" t="s">
+        <v>827</v>
+      </c>
+      <c r="F198" t="s">
+        <v>826</v>
+      </c>
+      <c r="G198" t="s">
+        <v>844</v>
+      </c>
+      <c r="H198" t="s">
+        <v>845</v>
+      </c>
+      <c r="I198" t="s">
+        <v>846</v>
+      </c>
+      <c r="J198" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>195</v>
+      </c>
+      <c r="B199" t="s">
+        <v>914</v>
+      </c>
+      <c r="C199" t="s">
+        <v>825</v>
+      </c>
+      <c r="D199" t="s">
+        <v>826</v>
+      </c>
+      <c r="E199" t="s">
+        <v>827</v>
+      </c>
+      <c r="F199" t="s">
+        <v>826</v>
+      </c>
+      <c r="G199" t="s">
+        <v>848</v>
+      </c>
+      <c r="H199" t="s">
+        <v>849</v>
+      </c>
+      <c r="I199" t="s">
+        <v>850</v>
+      </c>
+      <c r="J199" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>196</v>
+      </c>
+      <c r="B200" t="s">
+        <v>914</v>
+      </c>
+      <c r="C200" t="s">
+        <v>825</v>
+      </c>
+      <c r="D200" t="s">
+        <v>826</v>
+      </c>
+      <c r="E200" t="s">
+        <v>827</v>
+      </c>
+      <c r="F200" t="s">
+        <v>826</v>
+      </c>
+      <c r="G200" t="s">
+        <v>852</v>
+      </c>
+      <c r="H200" t="s">
+        <v>853</v>
+      </c>
+      <c r="I200" t="s">
+        <v>854</v>
+      </c>
+      <c r="J200" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>197</v>
+      </c>
+      <c r="B201" t="s">
+        <v>914</v>
+      </c>
+      <c r="C201" t="s">
+        <v>825</v>
+      </c>
+      <c r="D201" t="s">
+        <v>826</v>
+      </c>
+      <c r="E201" t="s">
+        <v>827</v>
+      </c>
+      <c r="F201" t="s">
+        <v>826</v>
+      </c>
+      <c r="G201" t="s">
+        <v>856</v>
+      </c>
+      <c r="H201" t="s">
+        <v>857</v>
+      </c>
+      <c r="I201" t="s">
+        <v>858</v>
+      </c>
+      <c r="J201" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>198</v>
+      </c>
+      <c r="B202" t="s">
+        <v>914</v>
+      </c>
+      <c r="C202" t="s">
+        <v>825</v>
+      </c>
+      <c r="D202" t="s">
+        <v>826</v>
+      </c>
+      <c r="E202" t="s">
+        <v>827</v>
+      </c>
+      <c r="F202" t="s">
+        <v>826</v>
+      </c>
+      <c r="G202" t="s">
+        <v>860</v>
+      </c>
+      <c r="H202" t="s">
+        <v>861</v>
+      </c>
+      <c r="I202" t="s">
+        <v>862</v>
+      </c>
+      <c r="J202" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>199</v>
+      </c>
+      <c r="B203" t="s">
+        <v>914</v>
+      </c>
+      <c r="C203" t="s">
+        <v>825</v>
+      </c>
+      <c r="D203" t="s">
+        <v>826</v>
+      </c>
+      <c r="E203" t="s">
+        <v>827</v>
+      </c>
+      <c r="F203" t="s">
+        <v>826</v>
+      </c>
+      <c r="G203" t="s">
+        <v>864</v>
+      </c>
+      <c r="H203" t="s">
+        <v>865</v>
+      </c>
+      <c r="I203" t="s">
+        <v>866</v>
+      </c>
+      <c r="J203" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>200</v>
+      </c>
+      <c r="B204" t="s">
+        <v>914</v>
+      </c>
+      <c r="C204" t="s">
+        <v>825</v>
+      </c>
+      <c r="D204" t="s">
+        <v>826</v>
+      </c>
+      <c r="E204" t="s">
+        <v>827</v>
+      </c>
+      <c r="F204" t="s">
+        <v>826</v>
+      </c>
+      <c r="G204" t="s">
+        <v>868</v>
+      </c>
+      <c r="H204" t="s">
+        <v>869</v>
+      </c>
+      <c r="I204" t="s">
+        <v>870</v>
+      </c>
+      <c r="J204" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>201</v>
+      </c>
+      <c r="B205" t="s">
+        <v>914</v>
+      </c>
+      <c r="C205" t="s">
+        <v>825</v>
+      </c>
+      <c r="D205" t="s">
+        <v>826</v>
+      </c>
+      <c r="E205" t="s">
+        <v>827</v>
+      </c>
+      <c r="F205" t="s">
+        <v>826</v>
+      </c>
+      <c r="G205" t="s">
+        <v>872</v>
+      </c>
+      <c r="H205" t="s">
+        <v>873</v>
+      </c>
+      <c r="I205" t="s">
+        <v>874</v>
+      </c>
+      <c r="J205" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>202</v>
+      </c>
+      <c r="B206" t="s">
+        <v>914</v>
+      </c>
+      <c r="C206" t="s">
+        <v>825</v>
+      </c>
+      <c r="D206" t="s">
+        <v>876</v>
+      </c>
+      <c r="E206" t="s">
+        <v>877</v>
+      </c>
+      <c r="F206" t="s">
+        <v>876</v>
+      </c>
+      <c r="G206" t="s">
+        <v>878</v>
+      </c>
+      <c r="H206" t="s">
+        <v>879</v>
+      </c>
+      <c r="I206" t="s">
+        <v>880</v>
+      </c>
+      <c r="J206" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>203</v>
+      </c>
+      <c r="B207" t="s">
+        <v>914</v>
+      </c>
+      <c r="C207" t="s">
+        <v>825</v>
+      </c>
+      <c r="D207" t="s">
+        <v>876</v>
+      </c>
+      <c r="E207" t="s">
+        <v>877</v>
+      </c>
+      <c r="F207" t="s">
+        <v>876</v>
+      </c>
+      <c r="G207" t="s">
+        <v>882</v>
+      </c>
+      <c r="H207" t="s">
+        <v>883</v>
+      </c>
+      <c r="I207" t="s">
+        <v>884</v>
+      </c>
+      <c r="J207" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>204</v>
+      </c>
+      <c r="B208" t="s">
+        <v>914</v>
+      </c>
+      <c r="C208" t="s">
+        <v>825</v>
+      </c>
+      <c r="D208" t="s">
+        <v>886</v>
+      </c>
+      <c r="E208" t="s">
+        <v>887</v>
+      </c>
+      <c r="F208" t="s">
+        <v>888</v>
+      </c>
+      <c r="G208" t="s">
+        <v>888</v>
+      </c>
+      <c r="H208" t="s">
+        <v>889</v>
+      </c>
+      <c r="I208" t="s">
+        <v>890</v>
+      </c>
+      <c r="J208" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>205</v>
+      </c>
+      <c r="B209" t="s">
+        <v>914</v>
+      </c>
+      <c r="C209" t="s">
+        <v>825</v>
+      </c>
+      <c r="D209" t="s">
+        <v>892</v>
+      </c>
+      <c r="E209" t="s">
+        <v>893</v>
+      </c>
+      <c r="F209" t="s">
+        <v>892</v>
+      </c>
+      <c r="G209" t="s">
+        <v>892</v>
+      </c>
+      <c r="H209" t="s">
+        <v>894</v>
+      </c>
+      <c r="I209" t="s">
+        <v>895</v>
+      </c>
+      <c r="J209" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>206</v>
+      </c>
+      <c r="B210" t="s">
+        <v>914</v>
+      </c>
+      <c r="C210" t="s">
+        <v>825</v>
+      </c>
+      <c r="D210" t="s">
+        <v>897</v>
+      </c>
+      <c r="E210" t="s">
+        <v>898</v>
+      </c>
+      <c r="F210" t="s">
+        <v>897</v>
+      </c>
+      <c r="G210" t="s">
+        <v>899</v>
+      </c>
+      <c r="H210" t="s">
+        <v>899</v>
+      </c>
+      <c r="I210" t="s">
+        <v>900</v>
+      </c>
+      <c r="J210" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>207</v>
+      </c>
+      <c r="B211" t="s">
+        <v>914</v>
+      </c>
+      <c r="C211" t="s">
+        <v>825</v>
+      </c>
+      <c r="D211" t="s">
+        <v>897</v>
+      </c>
+      <c r="E211" t="s">
+        <v>898</v>
+      </c>
+      <c r="F211" t="s">
+        <v>897</v>
+      </c>
+      <c r="G211" t="s">
+        <v>902</v>
+      </c>
+      <c r="H211" t="s">
+        <v>902</v>
+      </c>
+      <c r="I211" t="s">
+        <v>903</v>
+      </c>
+      <c r="J211" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>208</v>
+      </c>
+      <c r="B212" t="s">
+        <v>914</v>
+      </c>
+      <c r="C212" t="s">
+        <v>825</v>
+      </c>
+      <c r="D212" t="s">
+        <v>905</v>
+      </c>
+      <c r="E212" t="s">
+        <v>906</v>
+      </c>
+      <c r="F212" t="s">
+        <v>905</v>
+      </c>
+      <c r="G212" t="s">
+        <v>907</v>
+      </c>
+      <c r="H212" t="s">
+        <v>907</v>
+      </c>
+      <c r="I212" t="s">
+        <v>908</v>
+      </c>
+      <c r="J212" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>209</v>
+      </c>
+      <c r="B213" t="s">
+        <v>914</v>
+      </c>
+      <c r="C213" t="s">
+        <v>825</v>
+      </c>
+      <c r="D213" t="s">
+        <v>910</v>
+      </c>
+      <c r="E213" t="s">
+        <v>911</v>
+      </c>
+      <c r="F213" t="s">
+        <v>910</v>
+      </c>
+      <c r="G213" t="s">
+        <v>910</v>
+      </c>
+      <c r="H213" t="s">
+        <v>910</v>
+      </c>
+      <c r="I213" t="s">
+        <v>912</v>
+      </c>
+      <c r="J213" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3928B684-6CB2-4BAC-965C-937638D03264}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A0E6CA-F802-467A-8FAC-B450CB22764F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="919">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3172,9 +3172,6 @@
   </si>
   <si>
     <t>child3_big_166.jpg</t>
-  </si>
-  <si>
-    <t>Муфта БРС з одностороннім розніманням для гідравлічних систем</t>
   </si>
   <si>
     <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням. Кожна
@@ -4551,6 +4548,21 @@
   </si>
   <si>
     <t>Багатоцільові рукави та трубки</t>
+  </si>
+  <si>
+    <t>Муфта БРС ЄВРО з двостороннім розніманням для гідравлічних систем зовнішня різьба</t>
+  </si>
+  <si>
+    <t>Муфта БРС ЄВРО з одностороннім розніманням для гідравлічних систем внутрішня різьба</t>
+  </si>
+  <si>
+    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 1</t>
+  </si>
+  <si>
+    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 2</t>
+  </si>
+  <si>
+    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 3</t>
   </si>
 </sst>
 </file>
@@ -5383,10 +5395,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -6055,7 +6067,7 @@
         <v>148</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>149</v>
@@ -6087,7 +6099,7 @@
         <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>152</v>
@@ -6503,10 +6515,10 @@
         <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>760</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>210</v>
@@ -6535,10 +6547,10 @@
         <v>157</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>212</v>
@@ -6727,10 +6739,10 @@
         <v>218</v>
       </c>
       <c r="G57" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>239</v>
@@ -7301,7 +7313,7 @@
         <v>317</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>318</v>
@@ -7331,7 +7343,7 @@
         <v>317</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>318</v>
@@ -7361,7 +7373,7 @@
         <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>323</v>
@@ -7391,7 +7403,7 @@
         <v>317</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>323</v>
@@ -8031,16 +8043,16 @@
         <v>328</v>
       </c>
       <c r="G98" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8063,16 +8075,16 @@
         <v>328</v>
       </c>
       <c r="G99" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="J99" s="1" t="s">
         <v>699</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8095,16 +8107,16 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="J100" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8127,16 +8139,16 @@
         <v>328</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H101" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="J101" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -8987,7 +8999,7 @@
         <v>514</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>516</v>
@@ -9019,7 +9031,7 @@
         <v>514</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>519</v>
@@ -9074,7 +9086,7 @@
         <v>435</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>527</v>
@@ -9106,7 +9118,7 @@
         <v>435</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>527</v>
@@ -9147,10 +9159,10 @@
         <v>540</v>
       </c>
       <c r="G133" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>726</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>727</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>542</v>
@@ -9179,10 +9191,10 @@
         <v>540</v>
       </c>
       <c r="G134" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>729</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>545</v>
@@ -9211,10 +9223,10 @@
         <v>540</v>
       </c>
       <c r="G135" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>731</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>548</v>
@@ -9531,10 +9543,10 @@
         <v>540</v>
       </c>
       <c r="G145" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="H145" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>739</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>583</v>
@@ -9595,10 +9607,10 @@
         <v>540</v>
       </c>
       <c r="G147" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="H147" s="1" t="s">
         <v>734</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>735</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>589</v>
@@ -9627,10 +9639,10 @@
         <v>540</v>
       </c>
       <c r="G148" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="H148" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>591</v>
@@ -9659,10 +9671,10 @@
         <v>540</v>
       </c>
       <c r="G149" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="H149" s="1" t="s">
         <v>732</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>733</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>593</v>
@@ -9947,7 +9959,7 @@
         <v>623</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>629</v>
+        <v>914</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>630</v>
@@ -9979,7 +9991,7 @@
         <v>623</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>629</v>
+        <v>915</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>633</v>
@@ -10107,16 +10119,16 @@
         <v>623</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="H163" s="1" t="s">
+      <c r="I163" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="I163" s="1" t="s">
+      <c r="J163" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -10139,16 +10151,16 @@
         <v>623</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="H164" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="I164" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="J164" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -10171,21 +10183,21 @@
         <v>623</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>647</v>
+        <v>918</v>
       </c>
       <c r="H165" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="J165" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>315</v>
@@ -10194,28 +10206,28 @@
         <v>316</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="G166" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="H166" s="1" t="s">
+      <c r="I166" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="I166" s="1" t="s">
+      <c r="J166" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>10</v>
@@ -10233,21 +10245,21 @@
         <v>95</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>96</v>
       </c>
       <c r="I167" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="J167" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>10</v>
@@ -10265,21 +10277,21 @@
         <v>95</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H168" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="I168" s="1" t="s">
+      <c r="J168" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>214</v>
@@ -10297,21 +10309,21 @@
         <v>218</v>
       </c>
       <c r="G169" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="I169" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="J169" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>214</v>
@@ -10329,21 +10341,21 @@
         <v>218</v>
       </c>
       <c r="G170" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="H170" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="I170" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="I170" s="1" t="s">
+      <c r="J170" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>214</v>
@@ -10361,21 +10373,21 @@
         <v>218</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="H171" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="I171" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="I171" s="1" t="s">
+      <c r="J171" s="1" t="s">
         <v>681</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>214</v>
@@ -10393,21 +10405,21 @@
         <v>218</v>
       </c>
       <c r="G172" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="H172" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="H172" s="1" t="s">
+      <c r="I172" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="I172" s="1" t="s">
+      <c r="J172" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>214</v>
@@ -10425,16 +10437,16 @@
         <v>328</v>
       </c>
       <c r="G173" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="H173" s="1" t="s">
+      <c r="I173" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="I173" s="1" t="s">
+      <c r="J173" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -10448,25 +10460,25 @@
         <v>537</v>
       </c>
       <c r="D174" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="G174" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="H174" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="H174" s="1" t="s">
+      <c r="I174" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="J174" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -10480,25 +10492,25 @@
         <v>537</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E175" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="G175" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="H175" s="1" t="s">
+      <c r="I175" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="I175" s="1" t="s">
+      <c r="J175" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -10512,25 +10524,25 @@
         <v>537</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E176" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="G176" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="H176" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="I176" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="I176" s="1" t="s">
+      <c r="J176" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -10544,25 +10556,25 @@
         <v>537</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E177" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="F177" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="G177" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="H177" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="I177" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J177" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -10576,25 +10588,25 @@
         <v>537</v>
       </c>
       <c r="D178" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="G178" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="E178" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="H178" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="H178" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="I178" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="J178" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -10608,25 +10620,25 @@
         <v>435</v>
       </c>
       <c r="D179" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E179" t="s">
         <v>527</v>
       </c>
       <c r="F179" t="s">
+        <v>765</v>
+      </c>
+      <c r="G179" t="s">
         <v>766</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>767</v>
       </c>
-      <c r="H179" t="s">
-        <v>768</v>
-      </c>
       <c r="I179" t="s">
+        <v>750</v>
+      </c>
+      <c r="J179" t="s">
         <v>751</v>
-      </c>
-      <c r="J179" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -10649,16 +10661,16 @@
         <v>218</v>
       </c>
       <c r="G180" t="s">
+        <v>756</v>
+      </c>
+      <c r="H180" t="s">
         <v>757</v>
       </c>
-      <c r="H180" t="s">
-        <v>758</v>
-      </c>
       <c r="I180" t="s">
+        <v>754</v>
+      </c>
+      <c r="J180" t="s">
         <v>755</v>
-      </c>
-      <c r="J180" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -10681,16 +10693,16 @@
         <v>157</v>
       </c>
       <c r="G181" t="s">
+        <v>761</v>
+      </c>
+      <c r="H181" t="s">
         <v>762</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>763</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>764</v>
-      </c>
-      <c r="J181" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -10704,25 +10716,25 @@
         <v>435</v>
       </c>
       <c r="D182" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E182" t="s">
         <v>527</v>
       </c>
       <c r="F182" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G182" t="s">
+        <v>768</v>
+      </c>
+      <c r="H182" t="s">
         <v>769</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>770</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>771</v>
-      </c>
-      <c r="J182" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10745,16 +10757,16 @@
         <v>148</v>
       </c>
       <c r="G183" t="s">
+        <v>772</v>
+      </c>
+      <c r="H183" t="s">
         <v>773</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>774</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>775</v>
-      </c>
-      <c r="J183" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -10777,16 +10789,16 @@
         <v>404</v>
       </c>
       <c r="G184" t="s">
+        <v>777</v>
+      </c>
+      <c r="H184" t="s">
         <v>778</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>779</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>780</v>
-      </c>
-      <c r="J184" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -10809,16 +10821,16 @@
         <v>404</v>
       </c>
       <c r="G185" t="s">
+        <v>781</v>
+      </c>
+      <c r="H185" t="s">
         <v>782</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>783</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>784</v>
-      </c>
-      <c r="J185" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -10841,16 +10853,16 @@
         <v>404</v>
       </c>
       <c r="G186" t="s">
+        <v>785</v>
+      </c>
+      <c r="H186" t="s">
         <v>786</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>787</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>788</v>
-      </c>
-      <c r="J186" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -10858,31 +10870,31 @@
         <v>183</v>
       </c>
       <c r="B187" t="s">
+        <v>791</v>
+      </c>
+      <c r="C187" t="s">
         <v>792</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>793</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>794</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>795</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>796</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>797</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>798</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>799</v>
-      </c>
-      <c r="J187" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -10890,31 +10902,31 @@
         <v>184</v>
       </c>
       <c r="B188" t="s">
+        <v>791</v>
+      </c>
+      <c r="C188" t="s">
         <v>792</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>793</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>794</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>795</v>
       </c>
-      <c r="F188" t="s">
-        <v>796</v>
-      </c>
       <c r="G188" t="s">
+        <v>800</v>
+      </c>
+      <c r="H188" t="s">
+        <v>797</v>
+      </c>
+      <c r="I188" t="s">
         <v>801</v>
       </c>
-      <c r="H188" t="s">
-        <v>798</v>
-      </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>802</v>
-      </c>
-      <c r="J188" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -10922,31 +10934,31 @@
         <v>185</v>
       </c>
       <c r="B189" t="s">
+        <v>791</v>
+      </c>
+      <c r="C189" t="s">
         <v>792</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
         <v>793</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>794</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>795</v>
       </c>
-      <c r="F189" t="s">
-        <v>796</v>
-      </c>
       <c r="G189" t="s">
+        <v>803</v>
+      </c>
+      <c r="H189" t="s">
+        <v>797</v>
+      </c>
+      <c r="I189" t="s">
         <v>804</v>
       </c>
-      <c r="H189" t="s">
-        <v>798</v>
-      </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>805</v>
-      </c>
-      <c r="J189" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -10954,31 +10966,31 @@
         <v>186</v>
       </c>
       <c r="B190" t="s">
+        <v>791</v>
+      </c>
+      <c r="C190" t="s">
         <v>792</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>793</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>794</v>
       </c>
-      <c r="E190" t="s">
-        <v>795</v>
-      </c>
       <c r="F190" t="s">
+        <v>806</v>
+      </c>
+      <c r="G190" t="s">
+        <v>806</v>
+      </c>
+      <c r="H190" t="s">
         <v>807</v>
       </c>
-      <c r="G190" t="s">
-        <v>807</v>
-      </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>808</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>809</v>
-      </c>
-      <c r="J190" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -10992,25 +11004,25 @@
         <v>435</v>
       </c>
       <c r="D191" t="s">
+        <v>810</v>
+      </c>
+      <c r="E191" t="s">
         <v>811</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
+        <v>810</v>
+      </c>
+      <c r="G191" t="s">
         <v>812</v>
       </c>
-      <c r="F191" t="s">
-        <v>811</v>
-      </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>813</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>814</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>815</v>
-      </c>
-      <c r="J191" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -11024,25 +11036,25 @@
         <v>435</v>
       </c>
       <c r="D192" t="s">
+        <v>810</v>
+      </c>
+      <c r="E192" t="s">
         <v>811</v>
       </c>
-      <c r="E192" t="s">
-        <v>812</v>
-      </c>
       <c r="F192" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G192" t="s">
+        <v>816</v>
+      </c>
+      <c r="H192" t="s">
         <v>817</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>818</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>819</v>
-      </c>
-      <c r="J192" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -11056,25 +11068,25 @@
         <v>435</v>
       </c>
       <c r="D193" t="s">
+        <v>810</v>
+      </c>
+      <c r="E193" t="s">
         <v>811</v>
       </c>
-      <c r="E193" t="s">
-        <v>812</v>
-      </c>
       <c r="F193" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G193" t="s">
+        <v>820</v>
+      </c>
+      <c r="H193" t="s">
         <v>821</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>822</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>823</v>
-      </c>
-      <c r="J193" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -11082,31 +11094,31 @@
         <v>190</v>
       </c>
       <c r="B194" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C194" t="s">
+        <v>824</v>
+      </c>
+      <c r="D194" t="s">
         <v>825</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>826</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
+        <v>825</v>
+      </c>
+      <c r="G194" t="s">
         <v>827</v>
       </c>
-      <c r="F194" t="s">
-        <v>826</v>
-      </c>
-      <c r="G194" t="s">
+      <c r="H194" t="s">
         <v>828</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>829</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>830</v>
-      </c>
-      <c r="J194" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -11114,31 +11126,31 @@
         <v>191</v>
       </c>
       <c r="B195" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C195" t="s">
+        <v>824</v>
+      </c>
+      <c r="D195" t="s">
         <v>825</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>826</v>
       </c>
-      <c r="E195" t="s">
-        <v>827</v>
-      </c>
       <c r="F195" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G195" t="s">
+        <v>831</v>
+      </c>
+      <c r="H195" t="s">
         <v>832</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>833</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>834</v>
-      </c>
-      <c r="J195" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -11146,31 +11158,31 @@
         <v>192</v>
       </c>
       <c r="B196" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C196" t="s">
+        <v>824</v>
+      </c>
+      <c r="D196" t="s">
         <v>825</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>826</v>
       </c>
-      <c r="E196" t="s">
-        <v>827</v>
-      </c>
       <c r="F196" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G196" t="s">
+        <v>835</v>
+      </c>
+      <c r="H196" t="s">
         <v>836</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>837</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>838</v>
-      </c>
-      <c r="J196" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -11178,31 +11190,31 @@
         <v>193</v>
       </c>
       <c r="B197" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C197" t="s">
+        <v>824</v>
+      </c>
+      <c r="D197" t="s">
         <v>825</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>826</v>
       </c>
-      <c r="E197" t="s">
-        <v>827</v>
-      </c>
       <c r="F197" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G197" t="s">
+        <v>839</v>
+      </c>
+      <c r="H197" t="s">
         <v>840</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>841</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>842</v>
-      </c>
-      <c r="J197" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -11210,31 +11222,31 @@
         <v>194</v>
       </c>
       <c r="B198" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C198" t="s">
+        <v>824</v>
+      </c>
+      <c r="D198" t="s">
         <v>825</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>826</v>
       </c>
-      <c r="E198" t="s">
-        <v>827</v>
-      </c>
       <c r="F198" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G198" t="s">
+        <v>843</v>
+      </c>
+      <c r="H198" t="s">
         <v>844</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>845</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>846</v>
-      </c>
-      <c r="J198" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -11242,31 +11254,31 @@
         <v>195</v>
       </c>
       <c r="B199" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C199" t="s">
+        <v>824</v>
+      </c>
+      <c r="D199" t="s">
         <v>825</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>826</v>
       </c>
-      <c r="E199" t="s">
-        <v>827</v>
-      </c>
       <c r="F199" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G199" t="s">
+        <v>847</v>
+      </c>
+      <c r="H199" t="s">
         <v>848</v>
       </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>849</v>
       </c>
-      <c r="I199" t="s">
+      <c r="J199" t="s">
         <v>850</v>
-      </c>
-      <c r="J199" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -11274,31 +11286,31 @@
         <v>196</v>
       </c>
       <c r="B200" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C200" t="s">
+        <v>824</v>
+      </c>
+      <c r="D200" t="s">
         <v>825</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
         <v>826</v>
       </c>
-      <c r="E200" t="s">
-        <v>827</v>
-      </c>
       <c r="F200" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G200" t="s">
+        <v>851</v>
+      </c>
+      <c r="H200" t="s">
         <v>852</v>
       </c>
-      <c r="H200" t="s">
+      <c r="I200" t="s">
         <v>853</v>
       </c>
-      <c r="I200" t="s">
+      <c r="J200" t="s">
         <v>854</v>
-      </c>
-      <c r="J200" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -11306,31 +11318,31 @@
         <v>197</v>
       </c>
       <c r="B201" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C201" t="s">
+        <v>824</v>
+      </c>
+      <c r="D201" t="s">
         <v>825</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
         <v>826</v>
       </c>
-      <c r="E201" t="s">
-        <v>827</v>
-      </c>
       <c r="F201" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G201" t="s">
+        <v>855</v>
+      </c>
+      <c r="H201" t="s">
         <v>856</v>
       </c>
-      <c r="H201" t="s">
+      <c r="I201" t="s">
         <v>857</v>
       </c>
-      <c r="I201" t="s">
+      <c r="J201" t="s">
         <v>858</v>
-      </c>
-      <c r="J201" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -11338,31 +11350,31 @@
         <v>198</v>
       </c>
       <c r="B202" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C202" t="s">
+        <v>824</v>
+      </c>
+      <c r="D202" t="s">
         <v>825</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
         <v>826</v>
       </c>
-      <c r="E202" t="s">
-        <v>827</v>
-      </c>
       <c r="F202" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G202" t="s">
+        <v>859</v>
+      </c>
+      <c r="H202" t="s">
         <v>860</v>
       </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>861</v>
       </c>
-      <c r="I202" t="s">
+      <c r="J202" t="s">
         <v>862</v>
-      </c>
-      <c r="J202" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -11370,31 +11382,31 @@
         <v>199</v>
       </c>
       <c r="B203" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C203" t="s">
+        <v>824</v>
+      </c>
+      <c r="D203" t="s">
         <v>825</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
         <v>826</v>
       </c>
-      <c r="E203" t="s">
-        <v>827</v>
-      </c>
       <c r="F203" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G203" t="s">
+        <v>863</v>
+      </c>
+      <c r="H203" t="s">
         <v>864</v>
       </c>
-      <c r="H203" t="s">
+      <c r="I203" t="s">
         <v>865</v>
       </c>
-      <c r="I203" t="s">
+      <c r="J203" t="s">
         <v>866</v>
-      </c>
-      <c r="J203" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -11402,31 +11414,31 @@
         <v>200</v>
       </c>
       <c r="B204" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C204" t="s">
+        <v>824</v>
+      </c>
+      <c r="D204" t="s">
         <v>825</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
         <v>826</v>
       </c>
-      <c r="E204" t="s">
-        <v>827</v>
-      </c>
       <c r="F204" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G204" t="s">
+        <v>867</v>
+      </c>
+      <c r="H204" t="s">
         <v>868</v>
       </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>869</v>
       </c>
-      <c r="I204" t="s">
+      <c r="J204" t="s">
         <v>870</v>
-      </c>
-      <c r="J204" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -11434,31 +11446,31 @@
         <v>201</v>
       </c>
       <c r="B205" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C205" t="s">
+        <v>824</v>
+      </c>
+      <c r="D205" t="s">
         <v>825</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>826</v>
       </c>
-      <c r="E205" t="s">
-        <v>827</v>
-      </c>
       <c r="F205" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G205" t="s">
+        <v>871</v>
+      </c>
+      <c r="H205" t="s">
         <v>872</v>
       </c>
-      <c r="H205" t="s">
+      <c r="I205" t="s">
         <v>873</v>
       </c>
-      <c r="I205" t="s">
+      <c r="J205" t="s">
         <v>874</v>
-      </c>
-      <c r="J205" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -11466,31 +11478,31 @@
         <v>202</v>
       </c>
       <c r="B206" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C206" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D206" t="s">
+        <v>875</v>
+      </c>
+      <c r="E206" t="s">
         <v>876</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
+        <v>875</v>
+      </c>
+      <c r="G206" t="s">
         <v>877</v>
       </c>
-      <c r="F206" t="s">
-        <v>876</v>
-      </c>
-      <c r="G206" t="s">
+      <c r="H206" t="s">
         <v>878</v>
       </c>
-      <c r="H206" t="s">
+      <c r="I206" t="s">
         <v>879</v>
       </c>
-      <c r="I206" t="s">
+      <c r="J206" t="s">
         <v>880</v>
-      </c>
-      <c r="J206" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -11498,31 +11510,31 @@
         <v>203</v>
       </c>
       <c r="B207" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C207" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D207" t="s">
+        <v>875</v>
+      </c>
+      <c r="E207" t="s">
         <v>876</v>
       </c>
-      <c r="E207" t="s">
-        <v>877</v>
-      </c>
       <c r="F207" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G207" t="s">
+        <v>881</v>
+      </c>
+      <c r="H207" t="s">
         <v>882</v>
       </c>
-      <c r="H207" t="s">
+      <c r="I207" t="s">
         <v>883</v>
       </c>
-      <c r="I207" t="s">
+      <c r="J207" t="s">
         <v>884</v>
-      </c>
-      <c r="J207" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -11530,31 +11542,31 @@
         <v>204</v>
       </c>
       <c r="B208" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C208" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D208" t="s">
+        <v>885</v>
+      </c>
+      <c r="E208" t="s">
         <v>886</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>887</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
+        <v>887</v>
+      </c>
+      <c r="H208" t="s">
         <v>888</v>
       </c>
-      <c r="G208" t="s">
-        <v>888</v>
-      </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
         <v>889</v>
       </c>
-      <c r="I208" t="s">
+      <c r="J208" t="s">
         <v>890</v>
-      </c>
-      <c r="J208" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -11562,31 +11574,31 @@
         <v>205</v>
       </c>
       <c r="B209" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C209" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D209" t="s">
+        <v>891</v>
+      </c>
+      <c r="E209" t="s">
         <v>892</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
+        <v>891</v>
+      </c>
+      <c r="G209" t="s">
+        <v>891</v>
+      </c>
+      <c r="H209" t="s">
         <v>893</v>
       </c>
-      <c r="F209" t="s">
-        <v>892</v>
-      </c>
-      <c r="G209" t="s">
-        <v>892</v>
-      </c>
-      <c r="H209" t="s">
+      <c r="I209" t="s">
         <v>894</v>
       </c>
-      <c r="I209" t="s">
+      <c r="J209" t="s">
         <v>895</v>
-      </c>
-      <c r="J209" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -11594,31 +11606,31 @@
         <v>206</v>
       </c>
       <c r="B210" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C210" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D210" t="s">
+        <v>896</v>
+      </c>
+      <c r="E210" t="s">
         <v>897</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
+        <v>896</v>
+      </c>
+      <c r="G210" t="s">
         <v>898</v>
       </c>
-      <c r="F210" t="s">
-        <v>897</v>
-      </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
+        <v>898</v>
+      </c>
+      <c r="I210" t="s">
         <v>899</v>
       </c>
-      <c r="H210" t="s">
-        <v>899</v>
-      </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>900</v>
-      </c>
-      <c r="J210" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -11626,31 +11638,31 @@
         <v>207</v>
       </c>
       <c r="B211" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C211" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D211" t="s">
+        <v>896</v>
+      </c>
+      <c r="E211" t="s">
         <v>897</v>
       </c>
-      <c r="E211" t="s">
-        <v>898</v>
-      </c>
       <c r="F211" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G211" t="s">
+        <v>901</v>
+      </c>
+      <c r="H211" t="s">
+        <v>901</v>
+      </c>
+      <c r="I211" t="s">
         <v>902</v>
       </c>
-      <c r="H211" t="s">
-        <v>902</v>
-      </c>
-      <c r="I211" t="s">
+      <c r="J211" t="s">
         <v>903</v>
-      </c>
-      <c r="J211" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -11658,31 +11670,31 @@
         <v>208</v>
       </c>
       <c r="B212" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C212" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D212" t="s">
+        <v>904</v>
+      </c>
+      <c r="E212" t="s">
         <v>905</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
+        <v>904</v>
+      </c>
+      <c r="G212" t="s">
         <v>906</v>
       </c>
-      <c r="F212" t="s">
-        <v>905</v>
-      </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
+        <v>906</v>
+      </c>
+      <c r="I212" t="s">
         <v>907</v>
       </c>
-      <c r="H212" t="s">
-        <v>907</v>
-      </c>
-      <c r="I212" t="s">
+      <c r="J212" t="s">
         <v>908</v>
-      </c>
-      <c r="J212" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -11690,31 +11702,31 @@
         <v>209</v>
       </c>
       <c r="B213" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C213" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D213" t="s">
+        <v>909</v>
+      </c>
+      <c r="E213" t="s">
         <v>910</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
+        <v>909</v>
+      </c>
+      <c r="G213" t="s">
+        <v>909</v>
+      </c>
+      <c r="H213" t="s">
+        <v>909</v>
+      </c>
+      <c r="I213" t="s">
         <v>911</v>
       </c>
-      <c r="F213" t="s">
-        <v>910</v>
-      </c>
-      <c r="G213" t="s">
-        <v>910</v>
-      </c>
-      <c r="H213" t="s">
-        <v>910</v>
-      </c>
-      <c r="I213" t="s">
+      <c r="J213" t="s">
         <v>912</v>
-      </c>
-      <c r="J213" t="s">
-        <v>913</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A0E6CA-F802-467A-8FAC-B450CB22764F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9066CDEC-DBB1-408C-9B0E-4F1D4B72631B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -4923,6 +4923,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="7" max="7" width="72.140625" customWidth="1"/>
     <col min="9" max="9" width="48.85546875" customWidth="1"/>
     <col min="10" max="10" width="31.5703125" customWidth="1"/>
   </cols>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9066CDEC-DBB1-408C-9B0E-4F1D4B72631B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09951669-3FB0-4819-80F2-8162A29B988E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$J$182</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="10"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="920">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -4563,6 +4563,9 @@
   </si>
   <si>
     <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 3</t>
+  </si>
+  <si>
+    <t>З’єднувач кутовий з зовнішньою та внутрішньою різьбою для пневмо- та гідросистем</t>
   </si>
 </sst>
 </file>
@@ -8108,7 +8111,7 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>700</v>
+        <v>919</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>701</v>
@@ -8122,7 +8125,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>214</v>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09951669-3FB0-4819-80F2-8162A29B988E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CA4FDD-C543-4903-8BDA-550F0E3AA7E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="922">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3863,12 +3863,6 @@
   </si>
   <si>
     <t>З'єднувач перехідний пневматичний прямий із затискним муфтовим приєднанням NEWLINE ТYРЕ-2 та зовнішньою різьбою (RAUFOSS ABC™ SYSTEM)</t>
-  </si>
-  <si>
-    <t>Прес-маслянки та ковпачки</t>
-  </si>
-  <si>
-    <t>father_6.jpg</t>
   </si>
   <si>
     <t>Прес-маслянки для пластичних мастил та ковпачки</t>
@@ -4566,6 +4560,18 @@
   </si>
   <si>
     <t>З’єднувач кутовий з зовнішньою та внутрішньою різьбою для пневмо- та гідросистем</t>
+  </si>
+  <si>
+    <t>child1_30.jpg</t>
+  </si>
+  <si>
+    <t>child1_27.jpg</t>
+  </si>
+  <si>
+    <t>child1_28.jpg</t>
+  </si>
+  <si>
+    <t>child1_29.jpg</t>
   </si>
 </sst>
 </file>
@@ -4602,11 +4608,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5023,7 +5032,7 @@
       <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5055,7 +5064,7 @@
       <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5087,7 +5096,7 @@
       <c r="I5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5119,7 +5128,7 @@
       <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5151,7 +5160,7 @@
       <c r="I7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5183,7 +5192,7 @@
       <c r="I8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5215,7 +5224,7 @@
       <c r="I9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5247,7 +5256,7 @@
       <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5279,7 +5288,7 @@
       <c r="I11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5311,7 +5320,7 @@
       <c r="I12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5343,7 +5352,7 @@
       <c r="I13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5375,7 +5384,7 @@
       <c r="I14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5407,7 +5416,7 @@
       <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5439,7 +5448,7 @@
       <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5471,7 +5480,7 @@
       <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>76</v>
       </c>
     </row>
@@ -5503,7 +5512,7 @@
       <c r="I18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5535,7 +5544,7 @@
       <c r="I19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5567,7 +5576,7 @@
       <c r="I20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5599,7 +5608,7 @@
       <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5631,7 +5640,7 @@
       <c r="I22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5663,7 +5672,7 @@
       <c r="I23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>98</v>
       </c>
     </row>
@@ -5695,7 +5704,7 @@
       <c r="I24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5727,7 +5736,7 @@
       <c r="I25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5759,7 +5768,7 @@
       <c r="I26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5791,7 +5800,7 @@
       <c r="I27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5823,7 +5832,7 @@
       <c r="I28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5855,7 +5864,7 @@
       <c r="I29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5887,7 +5896,7 @@
       <c r="I30" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5919,7 +5928,7 @@
       <c r="I31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5951,7 +5960,7 @@
       <c r="I32" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5983,7 +5992,7 @@
       <c r="I33" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6015,7 +6024,7 @@
       <c r="I34" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6047,7 +6056,7 @@
       <c r="I35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6079,7 +6088,7 @@
       <c r="I36" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6111,11 +6120,11 @@
       <c r="I37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -6125,7 +6134,7 @@
       <c r="C38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -6143,7 +6152,7 @@
       <c r="I38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6175,7 +6184,7 @@
       <c r="I39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6207,7 +6216,7 @@
       <c r="I40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6239,7 +6248,7 @@
       <c r="I41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>176</v>
       </c>
     </row>
@@ -6271,7 +6280,7 @@
       <c r="I42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>180</v>
       </c>
     </row>
@@ -6303,7 +6312,7 @@
       <c r="I43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6335,7 +6344,7 @@
       <c r="I44" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6367,7 +6376,7 @@
       <c r="I45" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>192</v>
       </c>
     </row>
@@ -6399,7 +6408,7 @@
       <c r="I46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>196</v>
       </c>
     </row>
@@ -6431,7 +6440,7 @@
       <c r="I47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6463,7 +6472,7 @@
       <c r="I48" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6495,11 +6504,11 @@
       <c r="I49" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6509,7 +6518,7 @@
       <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -6527,11 +6536,11 @@
       <c r="I50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -6541,7 +6550,7 @@
       <c r="C51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -6559,7 +6568,7 @@
       <c r="I51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6591,7 +6600,7 @@
       <c r="I52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6623,7 +6632,7 @@
       <c r="I53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6655,7 +6664,7 @@
       <c r="I54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6687,7 +6696,7 @@
       <c r="I55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" t="s">
         <v>234</v>
       </c>
     </row>
@@ -6719,7 +6728,7 @@
       <c r="I56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>238</v>
       </c>
     </row>
@@ -6751,7 +6760,7 @@
       <c r="I57" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6783,7 +6792,7 @@
       <c r="I58" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6815,7 +6824,7 @@
       <c r="I59" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6847,7 +6856,7 @@
       <c r="I60" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>255</v>
       </c>
     </row>
@@ -6879,7 +6888,7 @@
       <c r="I61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" t="s">
         <v>259</v>
       </c>
     </row>
@@ -6911,7 +6920,7 @@
       <c r="I62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" t="s">
         <v>263</v>
       </c>
     </row>
@@ -6943,7 +6952,7 @@
       <c r="I63" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6975,7 +6984,7 @@
       <c r="I64" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" t="s">
         <v>274</v>
       </c>
     </row>
@@ -7007,7 +7016,7 @@
       <c r="I65" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7039,7 +7048,7 @@
       <c r="I66" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" t="s">
         <v>282</v>
       </c>
     </row>
@@ -7071,7 +7080,7 @@
       <c r="I67" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" t="s">
         <v>286</v>
       </c>
     </row>
@@ -7103,7 +7112,7 @@
       <c r="I68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" t="s">
         <v>290</v>
       </c>
     </row>
@@ -7135,7 +7144,7 @@
       <c r="I69" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" t="s">
         <v>294</v>
       </c>
     </row>
@@ -7167,7 +7176,7 @@
       <c r="I70" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" t="s">
         <v>298</v>
       </c>
     </row>
@@ -7199,7 +7208,7 @@
       <c r="I71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" t="s">
         <v>302</v>
       </c>
     </row>
@@ -7231,7 +7240,7 @@
       <c r="I72" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7263,7 +7272,7 @@
       <c r="I73" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" t="s">
         <v>310</v>
       </c>
     </row>
@@ -7295,7 +7304,7 @@
       <c r="I74" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" t="s">
         <v>314</v>
       </c>
     </row>
@@ -7312,7 +7321,9 @@
       <c r="D75" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E75" s="1"/>
+      <c r="E75" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="F75" s="1" t="s">
         <v>317</v>
       </c>
@@ -7325,7 +7336,7 @@
       <c r="I75" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" t="s">
         <v>320</v>
       </c>
     </row>
@@ -7342,7 +7353,9 @@
       <c r="D76" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E76" s="1"/>
+      <c r="E76" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="F76" s="1" t="s">
         <v>317</v>
       </c>
@@ -7355,7 +7368,7 @@
       <c r="I76" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" t="s">
         <v>322</v>
       </c>
     </row>
@@ -7372,7 +7385,9 @@
       <c r="D77" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E77" s="1"/>
+      <c r="E77" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="F77" s="1" t="s">
         <v>317</v>
       </c>
@@ -7385,7 +7400,7 @@
       <c r="I77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" t="s">
         <v>325</v>
       </c>
     </row>
@@ -7402,7 +7417,9 @@
       <c r="D78" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E78" s="1"/>
+      <c r="E78" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="F78" s="1" t="s">
         <v>317</v>
       </c>
@@ -7415,7 +7432,7 @@
       <c r="I78" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" t="s">
         <v>327</v>
       </c>
     </row>
@@ -7447,7 +7464,7 @@
       <c r="I79" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" t="s">
         <v>333</v>
       </c>
     </row>
@@ -7479,7 +7496,7 @@
       <c r="I80" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" t="s">
         <v>336</v>
       </c>
     </row>
@@ -7511,7 +7528,7 @@
       <c r="I81" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" t="s">
         <v>340</v>
       </c>
     </row>
@@ -7543,7 +7560,7 @@
       <c r="I82" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7575,7 +7592,7 @@
       <c r="I83" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="J83" t="s">
         <v>348</v>
       </c>
     </row>
@@ -7607,7 +7624,7 @@
       <c r="I84" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" t="s">
         <v>352</v>
       </c>
     </row>
@@ -7639,7 +7656,7 @@
       <c r="I85" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" t="s">
         <v>356</v>
       </c>
     </row>
@@ -7671,7 +7688,7 @@
       <c r="I86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" t="s">
         <v>359</v>
       </c>
     </row>
@@ -7703,7 +7720,7 @@
       <c r="I87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" t="s">
         <v>363</v>
       </c>
     </row>
@@ -7735,7 +7752,7 @@
       <c r="I88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="J88" t="s">
         <v>367</v>
       </c>
     </row>
@@ -7767,7 +7784,7 @@
       <c r="I89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="J89" t="s">
         <v>371</v>
       </c>
     </row>
@@ -7799,7 +7816,7 @@
       <c r="I90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="J90" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7831,7 +7848,7 @@
       <c r="I91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="J91" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7863,7 +7880,7 @@
       <c r="I92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J92" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7895,7 +7912,7 @@
       <c r="I93" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="J93" t="s">
         <v>387</v>
       </c>
     </row>
@@ -7927,7 +7944,7 @@
       <c r="I94" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="J94" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7959,7 +7976,7 @@
       <c r="I95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="J95" s="1" t="s">
+      <c r="J95" t="s">
         <v>395</v>
       </c>
     </row>
@@ -7991,7 +8008,7 @@
       <c r="I96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="J96" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8023,7 +8040,7 @@
       <c r="I97" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="J97" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8055,7 +8072,7 @@
       <c r="I98" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="J98" t="s">
         <v>695</v>
       </c>
     </row>
@@ -8078,7 +8095,7 @@
       <c r="F99" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" t="s">
         <v>696</v>
       </c>
       <c r="H99" s="1" t="s">
@@ -8087,7 +8104,7 @@
       <c r="I99" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="J99" s="1" t="s">
+      <c r="J99" t="s">
         <v>699</v>
       </c>
     </row>
@@ -8111,7 +8128,7 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>701</v>
@@ -8119,7 +8136,7 @@
       <c r="I100" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="J100" s="1" t="s">
+      <c r="J100" t="s">
         <v>703</v>
       </c>
     </row>
@@ -8151,7 +8168,7 @@
       <c r="I101" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="J101" t="s">
         <v>706</v>
       </c>
     </row>
@@ -8183,7 +8200,7 @@
       <c r="I102" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" t="s">
         <v>409</v>
       </c>
     </row>
@@ -8215,7 +8232,7 @@
       <c r="I103" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="J103" t="s">
         <v>413</v>
       </c>
     </row>
@@ -8247,7 +8264,7 @@
       <c r="I104" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="J104" s="1" t="s">
+      <c r="J104" t="s">
         <v>417</v>
       </c>
     </row>
@@ -8279,7 +8296,7 @@
       <c r="I105" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="J105" t="s">
         <v>421</v>
       </c>
     </row>
@@ -8311,7 +8328,7 @@
       <c r="I106" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="J106" s="1" t="s">
+      <c r="J106" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8343,7 +8360,7 @@
       <c r="I107" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="J107" t="s">
         <v>429</v>
       </c>
     </row>
@@ -8375,7 +8392,7 @@
       <c r="I108" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J108" s="1" t="s">
+      <c r="J108" t="s">
         <v>433</v>
       </c>
     </row>
@@ -8407,7 +8424,7 @@
       <c r="I109" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="J109" s="1" t="s">
+      <c r="J109" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8439,7 +8456,7 @@
       <c r="I110" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J110" s="1" t="s">
+      <c r="J110" t="s">
         <v>445</v>
       </c>
     </row>
@@ -8471,7 +8488,7 @@
       <c r="I111" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="J111" t="s">
         <v>449</v>
       </c>
     </row>
@@ -8503,7 +8520,7 @@
       <c r="I112" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="J112" s="1" t="s">
+      <c r="J112" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8535,7 +8552,7 @@
       <c r="I113" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="J113" s="1" t="s">
+      <c r="J113" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8567,7 +8584,7 @@
       <c r="I114" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="J114" s="1" t="s">
+      <c r="J114" t="s">
         <v>461</v>
       </c>
     </row>
@@ -8599,7 +8616,7 @@
       <c r="I115" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="J115" s="1" t="s">
+      <c r="J115" t="s">
         <v>465</v>
       </c>
     </row>
@@ -8631,7 +8648,7 @@
       <c r="I116" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="J116" s="1" t="s">
+      <c r="J116" t="s">
         <v>469</v>
       </c>
     </row>
@@ -8663,7 +8680,7 @@
       <c r="I117" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J117" s="1" t="s">
+      <c r="J117" t="s">
         <v>473</v>
       </c>
     </row>
@@ -8695,7 +8712,7 @@
       <c r="I118" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="J118" s="1" t="s">
+      <c r="J118" t="s">
         <v>477</v>
       </c>
     </row>
@@ -8727,7 +8744,7 @@
       <c r="I119" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="J119" s="1" t="s">
+      <c r="J119" t="s">
         <v>481</v>
       </c>
     </row>
@@ -8759,7 +8776,7 @@
       <c r="I120" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J120" s="1" t="s">
+      <c r="J120" t="s">
         <v>483</v>
       </c>
     </row>
@@ -8791,7 +8808,7 @@
       <c r="I121" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="J121" s="1" t="s">
+      <c r="J121" t="s">
         <v>487</v>
       </c>
     </row>
@@ -8823,7 +8840,7 @@
       <c r="I122" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="J122" t="s">
         <v>491</v>
       </c>
     </row>
@@ -8855,7 +8872,7 @@
       <c r="I123" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J123" s="1" t="s">
+      <c r="J123" t="s">
         <v>495</v>
       </c>
     </row>
@@ -8887,7 +8904,7 @@
       <c r="I124" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="J124" s="1" t="s">
+      <c r="J124" t="s">
         <v>499</v>
       </c>
     </row>
@@ -8919,7 +8936,7 @@
       <c r="I125" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="J125" s="1" t="s">
+      <c r="J125" t="s">
         <v>503</v>
       </c>
     </row>
@@ -8936,7 +8953,9 @@
       <c r="D126" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E126" s="1"/>
+      <c r="E126" s="1" t="s">
+        <v>919</v>
+      </c>
       <c r="F126" s="1" t="s">
         <v>504</v>
       </c>
@@ -8949,11 +8968,11 @@
       <c r="I126" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="J126" s="1" t="s">
+      <c r="J126" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>130</v>
       </c>
@@ -8963,10 +8982,12 @@
       <c r="C127" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E127" s="1"/>
+      <c r="E127" s="1" t="s">
+        <v>920</v>
+      </c>
       <c r="F127" s="1" t="s">
         <v>509</v>
       </c>
@@ -8979,11 +9000,11 @@
       <c r="I127" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="J127" s="1" t="s">
+      <c r="J127" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>131</v>
       </c>
@@ -8993,7 +9014,7 @@
       <c r="C128" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E128" s="1" t="s">
@@ -9011,11 +9032,11 @@
       <c r="I128" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="J128" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>132</v>
       </c>
@@ -9025,7 +9046,7 @@
       <c r="C129" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -9043,11 +9064,11 @@
       <c r="I129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="J129" s="1" t="s">
+      <c r="J129" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>133</v>
       </c>
@@ -9057,7 +9078,7 @@
       <c r="C130" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E130" s="1" t="s">
@@ -9075,7 +9096,7 @@
       <c r="I130" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="J130" s="1" t="s">
+      <c r="J130" t="s">
         <v>525</v>
       </c>
     </row>
@@ -9107,7 +9128,7 @@
       <c r="I131" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="J131" s="1" t="s">
+      <c r="J131" t="s">
         <v>531</v>
       </c>
     </row>
@@ -9139,7 +9160,7 @@
       <c r="I132" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="J132" s="1" t="s">
+      <c r="J132" t="s">
         <v>535</v>
       </c>
     </row>
@@ -9267,7 +9288,7 @@
       <c r="I136" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="J136" s="1" t="s">
+      <c r="J136" t="s">
         <v>553</v>
       </c>
     </row>
@@ -9299,7 +9320,7 @@
       <c r="I137" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="J137" s="1" t="s">
+      <c r="J137" t="s">
         <v>557</v>
       </c>
     </row>
@@ -9331,7 +9352,7 @@
       <c r="I138" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="J138" s="1" t="s">
+      <c r="J138" t="s">
         <v>561</v>
       </c>
     </row>
@@ -9363,7 +9384,7 @@
       <c r="I139" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="J139" s="1" t="s">
+      <c r="J139" t="s">
         <v>565</v>
       </c>
     </row>
@@ -9395,7 +9416,7 @@
       <c r="I140" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J140" t="s">
         <v>568</v>
       </c>
     </row>
@@ -9427,7 +9448,7 @@
       <c r="I141" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="J141" s="1" t="s">
+      <c r="J141" t="s">
         <v>571</v>
       </c>
     </row>
@@ -9459,7 +9480,7 @@
       <c r="I142" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="J142" s="1" t="s">
+      <c r="J142" t="s">
         <v>575</v>
       </c>
     </row>
@@ -9491,7 +9512,7 @@
       <c r="I143" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="J143" s="1" t="s">
+      <c r="J143" t="s">
         <v>578</v>
       </c>
     </row>
@@ -9523,7 +9544,7 @@
       <c r="I144" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="J144" s="1" t="s">
+      <c r="J144" t="s">
         <v>582</v>
       </c>
     </row>
@@ -9587,7 +9608,7 @@
       <c r="I146" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="J146" t="s">
         <v>588</v>
       </c>
     </row>
@@ -9715,7 +9736,7 @@
       <c r="I150" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="J150" s="1" t="s">
+      <c r="J150" t="s">
         <v>598</v>
       </c>
     </row>
@@ -9747,7 +9768,7 @@
       <c r="I151" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J151" s="1" t="s">
+      <c r="J151" t="s">
         <v>602</v>
       </c>
     </row>
@@ -9779,7 +9800,7 @@
       <c r="I152" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="J152" t="s">
         <v>606</v>
       </c>
     </row>
@@ -9811,7 +9832,7 @@
       <c r="I153" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="J153" s="1" t="s">
+      <c r="J153" t="s">
         <v>610</v>
       </c>
     </row>
@@ -9843,7 +9864,7 @@
       <c r="I154" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="J154" s="1" t="s">
+      <c r="J154" t="s">
         <v>614</v>
       </c>
     </row>
@@ -9875,7 +9896,7 @@
       <c r="I155" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="J155" s="1" t="s">
+      <c r="J155" t="s">
         <v>618</v>
       </c>
     </row>
@@ -9907,7 +9928,7 @@
       <c r="I156" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="J156" s="1" t="s">
+      <c r="J156" t="s">
         <v>622</v>
       </c>
     </row>
@@ -9939,7 +9960,7 @@
       <c r="I157" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J157" s="1" t="s">
+      <c r="J157" t="s">
         <v>628</v>
       </c>
     </row>
@@ -9963,7 +9984,7 @@
         <v>623</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>630</v>
@@ -9971,7 +9992,7 @@
       <c r="I158" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J158" s="1" t="s">
+      <c r="J158" t="s">
         <v>632</v>
       </c>
     </row>
@@ -9995,7 +10016,7 @@
         <v>623</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>633</v>
@@ -10003,7 +10024,7 @@
       <c r="I159" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="J159" s="1" t="s">
+      <c r="J159" t="s">
         <v>635</v>
       </c>
     </row>
@@ -10035,7 +10056,7 @@
       <c r="I160" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="J160" s="1" t="s">
+      <c r="J160" t="s">
         <v>638</v>
       </c>
     </row>
@@ -10067,7 +10088,7 @@
       <c r="I161" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="J161" s="1" t="s">
+      <c r="J161" t="s">
         <v>642</v>
       </c>
     </row>
@@ -10099,7 +10120,7 @@
       <c r="I162" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="J162" t="s">
         <v>646</v>
       </c>
     </row>
@@ -10123,7 +10144,7 @@
         <v>623</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>647</v>
@@ -10131,7 +10152,7 @@
       <c r="I163" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="J163" s="1" t="s">
+      <c r="J163" t="s">
         <v>649</v>
       </c>
     </row>
@@ -10155,7 +10176,7 @@
         <v>623</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>647</v>
@@ -10163,7 +10184,7 @@
       <c r="I164" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" t="s">
         <v>651</v>
       </c>
     </row>
@@ -10187,7 +10208,7 @@
         <v>623</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>652</v>
@@ -10195,7 +10216,7 @@
       <c r="I165" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" t="s">
         <v>654</v>
       </c>
     </row>
@@ -10212,7 +10233,9 @@
       <c r="D166" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="E166" s="1"/>
+      <c r="E166" s="1" t="s">
+        <v>921</v>
+      </c>
       <c r="F166" s="1" t="s">
         <v>656</v>
       </c>
@@ -10225,7 +10248,7 @@
       <c r="I166" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="J166" s="1" t="s">
+      <c r="J166" t="s">
         <v>659</v>
       </c>
     </row>
@@ -10257,7 +10280,7 @@
       <c r="I167" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="J167" s="1" t="s">
+      <c r="J167" t="s">
         <v>662</v>
       </c>
     </row>
@@ -10289,7 +10312,7 @@
       <c r="I168" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="J168" s="1" t="s">
+      <c r="J168" t="s">
         <v>666</v>
       </c>
     </row>
@@ -10321,7 +10344,7 @@
       <c r="I169" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="J169" s="1" t="s">
+      <c r="J169" t="s">
         <v>671</v>
       </c>
     </row>
@@ -10353,7 +10376,7 @@
       <c r="I170" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="J170" s="1" t="s">
+      <c r="J170" t="s">
         <v>676</v>
       </c>
     </row>
@@ -10385,7 +10408,7 @@
       <c r="I171" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="J171" s="1" t="s">
+      <c r="J171" t="s">
         <v>681</v>
       </c>
     </row>
@@ -10417,7 +10440,7 @@
       <c r="I172" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="J172" s="1" t="s">
+      <c r="J172" t="s">
         <v>686</v>
       </c>
     </row>
@@ -10449,7 +10472,7 @@
       <c r="I173" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="J173" s="1" t="s">
+      <c r="J173" t="s">
         <v>691</v>
       </c>
     </row>
@@ -10481,7 +10504,7 @@
       <c r="I174" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="J174" s="1" t="s">
+      <c r="J174" t="s">
         <v>712</v>
       </c>
     </row>
@@ -10513,7 +10536,7 @@
       <c r="I175" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="J175" s="1" t="s">
+      <c r="J175" t="s">
         <v>716</v>
       </c>
     </row>
@@ -10545,7 +10568,7 @@
       <c r="I176" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="J176" s="1" t="s">
+      <c r="J176" t="s">
         <v>720</v>
       </c>
     </row>
@@ -10577,7 +10600,7 @@
       <c r="I177" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="J177" s="1" t="s">
+      <c r="J177" t="s">
         <v>722</v>
       </c>
     </row>
@@ -10609,39 +10632,39 @@
       <c r="I178" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="J178" s="1" t="s">
+      <c r="J178" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179">
+      <c r="A179" s="1">
         <v>175</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F179" t="s">
+      <c r="F179" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H179" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="I179" t="s">
+      <c r="I179" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="J179" t="s">
+      <c r="J179" s="1" t="s">
         <v>751</v>
       </c>
     </row>
@@ -10667,7 +10690,7 @@
       <c r="G180" t="s">
         <v>756</v>
       </c>
-      <c r="H180" t="s">
+      <c r="H180" s="1" t="s">
         <v>757</v>
       </c>
       <c r="I180" t="s">
@@ -10677,32 +10700,32 @@
         <v>755</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181">
+    <row r="181" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
         <v>177</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F181" t="s">
         <v>157</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G181" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="H181" t="s">
+      <c r="H181" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="I181" t="s">
+      <c r="I181" s="1" t="s">
         <v>763</v>
       </c>
       <c r="J181" t="s">
@@ -10710,63 +10733,63 @@
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182">
+      <c r="A182" s="1">
         <v>178</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F182" t="s">
+      <c r="F182" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G182" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="H182" t="s">
+      <c r="H182" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="I182" t="s">
+      <c r="I182" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="J182" t="s">
+      <c r="J182" s="1" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183">
+      <c r="A183" s="1">
         <v>179</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F183" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G183" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="H183" t="s">
+      <c r="H183" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="I183" t="s">
+      <c r="I183" s="1" t="s">
         <v>774</v>
       </c>
       <c r="J183" t="s">
@@ -10774,31 +10797,31 @@
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184">
+      <c r="A184" s="1">
         <v>180</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F184" t="s">
+      <c r="F184" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H184" t="s">
+      <c r="H184" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="I184" t="s">
+      <c r="I184" s="1" t="s">
         <v>779</v>
       </c>
       <c r="J184" t="s">
@@ -10806,31 +10829,31 @@
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185">
+      <c r="A185" s="1">
         <v>181</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F185" t="s">
+      <c r="F185" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G185" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H185" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="I185" t="s">
+      <c r="I185" s="1" t="s">
         <v>783</v>
       </c>
       <c r="J185" t="s">
@@ -10838,31 +10861,31 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186">
+      <c r="A186" s="1">
         <v>182</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G186" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="H186" t="s">
+      <c r="H186" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="I186" t="s">
+      <c r="I186" s="1" t="s">
         <v>787</v>
       </c>
       <c r="J186" t="s">
@@ -10870,867 +10893,867 @@
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187">
+      <c r="A187" s="1">
         <v>183</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="C187" t="s">
+      <c r="E187" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D187" t="s">
+      <c r="F187" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="E187" t="s">
+      <c r="G187" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="F187" t="s">
+      <c r="H187" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G187" t="s">
+      <c r="I187" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="H187" t="s">
+      <c r="J187" t="s">
         <v>797</v>
       </c>
-      <c r="I187" t="s">
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>184</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="G188" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="J187" t="s">
+      <c r="H188" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="I188" s="1" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>184</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="J188" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>185</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="C188" t="s">
+      <c r="E189" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D188" t="s">
+      <c r="F189" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="E188" t="s">
-        <v>794</v>
-      </c>
-      <c r="F188" t="s">
+      <c r="G189" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="H189" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G188" t="s">
-        <v>800</v>
-      </c>
-      <c r="H188" t="s">
-        <v>797</v>
-      </c>
-      <c r="I188" t="s">
-        <v>801</v>
-      </c>
-      <c r="J188" t="s">
+      <c r="I189" s="1" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>185</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="J189" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>186</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="C189" t="s">
+      <c r="E190" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D189" t="s">
-        <v>793</v>
-      </c>
-      <c r="E189" t="s">
-        <v>794</v>
-      </c>
-      <c r="F189" t="s">
-        <v>795</v>
-      </c>
-      <c r="G189" t="s">
-        <v>803</v>
-      </c>
-      <c r="H189" t="s">
-        <v>797</v>
-      </c>
-      <c r="I189" t="s">
+      <c r="F190" t="s">
         <v>804</v>
       </c>
-      <c r="J189" t="s">
+      <c r="G190" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="H190" s="1" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>186</v>
-      </c>
-      <c r="B190" t="s">
-        <v>791</v>
-      </c>
-      <c r="C190" t="s">
-        <v>792</v>
-      </c>
-      <c r="D190" t="s">
-        <v>793</v>
-      </c>
-      <c r="E190" t="s">
-        <v>794</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="I190" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G190" t="s">
-        <v>806</v>
-      </c>
-      <c r="H190" t="s">
+      <c r="J190" t="s">
         <v>807</v>
       </c>
-      <c r="I190" t="s">
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>187</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="J190" t="s">
+      <c r="E191" s="1" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>187</v>
-      </c>
-      <c r="B191" t="s">
+      <c r="F191" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>188</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D191" t="s">
-        <v>810</v>
-      </c>
-      <c r="E191" t="s">
-        <v>811</v>
-      </c>
-      <c r="F191" t="s">
-        <v>810</v>
-      </c>
-      <c r="G191" t="s">
-        <v>812</v>
-      </c>
-      <c r="H191" t="s">
-        <v>813</v>
-      </c>
-      <c r="I191" t="s">
+      <c r="D192" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="G192" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="J191" t="s">
+      <c r="H192" s="1" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192">
-        <v>188</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="I192" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>189</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C193" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D192" t="s">
-        <v>810</v>
-      </c>
-      <c r="E192" t="s">
-        <v>811</v>
-      </c>
-      <c r="F192" t="s">
-        <v>810</v>
-      </c>
-      <c r="G192" t="s">
-        <v>816</v>
-      </c>
-      <c r="H192" t="s">
-        <v>817</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="D193" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="G193" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="J192" t="s">
+      <c r="H193" s="1" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>189</v>
-      </c>
-      <c r="B193" t="s">
-        <v>434</v>
-      </c>
-      <c r="C193" t="s">
-        <v>435</v>
-      </c>
-      <c r="D193" t="s">
-        <v>810</v>
-      </c>
-      <c r="E193" t="s">
-        <v>811</v>
-      </c>
-      <c r="F193" t="s">
-        <v>810</v>
-      </c>
-      <c r="G193" t="s">
+      <c r="I193" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="H193" t="s">
+      <c r="J193" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="I193" t="s">
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>190</v>
+      </c>
+      <c r="B194" t="s">
+        <v>911</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="J193" t="s">
+      <c r="D194" s="1" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>190</v>
-      </c>
-      <c r="B194" t="s">
-        <v>913</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="E194" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D194" t="s">
+      <c r="F194" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G194" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="E194" t="s">
+      <c r="H194" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="F194" t="s">
-        <v>825</v>
-      </c>
-      <c r="G194" t="s">
+      <c r="I194" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="I194" t="s">
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>191</v>
+      </c>
+      <c r="B195" t="s">
+        <v>911</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G195" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="J194" t="s">
+      <c r="H195" s="1" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195">
-        <v>191</v>
-      </c>
-      <c r="B195" t="s">
-        <v>913</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="I195" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>192</v>
+      </c>
+      <c r="B196" t="s">
+        <v>911</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D195" t="s">
-        <v>825</v>
-      </c>
-      <c r="E195" t="s">
-        <v>826</v>
-      </c>
-      <c r="F195" t="s">
-        <v>825</v>
-      </c>
-      <c r="G195" t="s">
-        <v>831</v>
-      </c>
-      <c r="H195" t="s">
-        <v>832</v>
-      </c>
-      <c r="I195" t="s">
+      <c r="F196" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G196" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="J195" t="s">
+      <c r="H196" s="1" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>192</v>
-      </c>
-      <c r="B196" t="s">
-        <v>913</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="I196" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>193</v>
+      </c>
+      <c r="B197" t="s">
+        <v>911</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D196" t="s">
-        <v>825</v>
-      </c>
-      <c r="E196" t="s">
-        <v>826</v>
-      </c>
-      <c r="F196" t="s">
-        <v>825</v>
-      </c>
-      <c r="G196" t="s">
-        <v>835</v>
-      </c>
-      <c r="H196" t="s">
-        <v>836</v>
-      </c>
-      <c r="I196" t="s">
+      <c r="F197" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G197" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="J196" t="s">
+      <c r="H197" s="1" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>193</v>
-      </c>
-      <c r="B197" t="s">
-        <v>913</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="I197" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>194</v>
+      </c>
+      <c r="B198" t="s">
+        <v>911</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D197" t="s">
-        <v>825</v>
-      </c>
-      <c r="E197" t="s">
-        <v>826</v>
-      </c>
-      <c r="F197" t="s">
-        <v>825</v>
-      </c>
-      <c r="G197" t="s">
-        <v>839</v>
-      </c>
-      <c r="H197" t="s">
-        <v>840</v>
-      </c>
-      <c r="I197" t="s">
+      <c r="F198" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G198" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="J197" t="s">
+      <c r="H198" s="1" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>194</v>
-      </c>
-      <c r="B198" t="s">
-        <v>913</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="I198" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>195</v>
+      </c>
+      <c r="B199" t="s">
+        <v>911</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D198" t="s">
-        <v>825</v>
-      </c>
-      <c r="E198" t="s">
-        <v>826</v>
-      </c>
-      <c r="F198" t="s">
-        <v>825</v>
-      </c>
-      <c r="G198" t="s">
-        <v>843</v>
-      </c>
-      <c r="H198" t="s">
-        <v>844</v>
-      </c>
-      <c r="I198" t="s">
+      <c r="F199" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G199" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="J198" t="s">
+      <c r="H199" s="1" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199">
-        <v>195</v>
-      </c>
-      <c r="B199" t="s">
-        <v>913</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="I199" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>196</v>
+      </c>
+      <c r="B200" t="s">
+        <v>911</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D199" t="s">
-        <v>825</v>
-      </c>
-      <c r="E199" t="s">
-        <v>826</v>
-      </c>
-      <c r="F199" t="s">
-        <v>825</v>
-      </c>
-      <c r="G199" t="s">
-        <v>847</v>
-      </c>
-      <c r="H199" t="s">
-        <v>848</v>
-      </c>
-      <c r="I199" t="s">
+      <c r="F200" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G200" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="J199" t="s">
+      <c r="H200" s="1" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200">
-        <v>196</v>
-      </c>
-      <c r="B200" t="s">
-        <v>913</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="I200" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>197</v>
+      </c>
+      <c r="B201" t="s">
+        <v>911</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D200" t="s">
-        <v>825</v>
-      </c>
-      <c r="E200" t="s">
-        <v>826</v>
-      </c>
-      <c r="F200" t="s">
-        <v>825</v>
-      </c>
-      <c r="G200" t="s">
-        <v>851</v>
-      </c>
-      <c r="H200" t="s">
-        <v>852</v>
-      </c>
-      <c r="I200" t="s">
+      <c r="F201" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G201" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="J200" t="s">
+      <c r="H201" s="1" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201">
-        <v>197</v>
-      </c>
-      <c r="B201" t="s">
-        <v>913</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="I201" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>198</v>
+      </c>
+      <c r="B202" t="s">
+        <v>911</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D201" t="s">
-        <v>825</v>
-      </c>
-      <c r="E201" t="s">
-        <v>826</v>
-      </c>
-      <c r="F201" t="s">
-        <v>825</v>
-      </c>
-      <c r="G201" t="s">
-        <v>855</v>
-      </c>
-      <c r="H201" t="s">
-        <v>856</v>
-      </c>
-      <c r="I201" t="s">
+      <c r="F202" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G202" t="s">
         <v>857</v>
       </c>
-      <c r="J201" t="s">
+      <c r="H202" s="1" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202">
-        <v>198</v>
-      </c>
-      <c r="B202" t="s">
-        <v>913</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="I202" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>199</v>
+      </c>
+      <c r="B203" t="s">
+        <v>911</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D202" t="s">
-        <v>825</v>
-      </c>
-      <c r="E202" t="s">
-        <v>826</v>
-      </c>
-      <c r="F202" t="s">
-        <v>825</v>
-      </c>
-      <c r="G202" t="s">
-        <v>859</v>
-      </c>
-      <c r="H202" t="s">
-        <v>860</v>
-      </c>
-      <c r="I202" t="s">
+      <c r="F203" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G203" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="J202" t="s">
+      <c r="H203" s="1" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203">
-        <v>199</v>
-      </c>
-      <c r="B203" t="s">
-        <v>913</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="I203" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>200</v>
+      </c>
+      <c r="B204" t="s">
+        <v>911</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D203" t="s">
-        <v>825</v>
-      </c>
-      <c r="E203" t="s">
-        <v>826</v>
-      </c>
-      <c r="F203" t="s">
-        <v>825</v>
-      </c>
-      <c r="G203" t="s">
-        <v>863</v>
-      </c>
-      <c r="H203" t="s">
-        <v>864</v>
-      </c>
-      <c r="I203" t="s">
+      <c r="F204" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G204" t="s">
         <v>865</v>
       </c>
-      <c r="J203" t="s">
+      <c r="H204" s="1" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204">
-        <v>200</v>
-      </c>
-      <c r="B204" t="s">
-        <v>913</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="I204" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>201</v>
+      </c>
+      <c r="B205" t="s">
+        <v>911</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D204" t="s">
-        <v>825</v>
-      </c>
-      <c r="E204" t="s">
-        <v>826</v>
-      </c>
-      <c r="F204" t="s">
-        <v>825</v>
-      </c>
-      <c r="G204" t="s">
-        <v>867</v>
-      </c>
-      <c r="H204" t="s">
-        <v>868</v>
-      </c>
-      <c r="I204" t="s">
+      <c r="F205" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G205" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="J204" t="s">
+      <c r="H205" s="1" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205">
-        <v>201</v>
-      </c>
-      <c r="B205" t="s">
-        <v>913</v>
-      </c>
-      <c r="C205" t="s">
-        <v>824</v>
-      </c>
-      <c r="D205" t="s">
-        <v>825</v>
-      </c>
-      <c r="E205" t="s">
-        <v>826</v>
-      </c>
-      <c r="F205" t="s">
-        <v>825</v>
-      </c>
-      <c r="G205" t="s">
+      <c r="I205" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="H205" t="s">
+      <c r="J205" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="I205" t="s">
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>202</v>
+      </c>
+      <c r="B206" t="s">
+        <v>911</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="J205" t="s">
+      <c r="E206" s="1" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206">
-        <v>202</v>
-      </c>
-      <c r="B206" t="s">
-        <v>913</v>
-      </c>
-      <c r="C206" t="s">
-        <v>824</v>
-      </c>
-      <c r="D206" t="s">
+      <c r="F206" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="G206" t="s">
         <v>875</v>
       </c>
-      <c r="E206" t="s">
+      <c r="H206" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="F206" t="s">
-        <v>875</v>
-      </c>
-      <c r="G206" t="s">
+      <c r="I206" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="H206" t="s">
+      <c r="J206" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="I206" t="s">
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>203</v>
+      </c>
+      <c r="B207" t="s">
+        <v>911</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="G207" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="J206" t="s">
+      <c r="H207" s="1" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207">
-        <v>203</v>
-      </c>
-      <c r="B207" t="s">
-        <v>913</v>
-      </c>
-      <c r="C207" t="s">
-        <v>824</v>
-      </c>
-      <c r="D207" t="s">
-        <v>875</v>
-      </c>
-      <c r="E207" t="s">
-        <v>876</v>
-      </c>
-      <c r="F207" t="s">
-        <v>875</v>
-      </c>
-      <c r="G207" t="s">
+      <c r="I207" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="H207" t="s">
+      <c r="J207" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="I207" t="s">
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>204</v>
+      </c>
+      <c r="B208" t="s">
+        <v>911</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="J207" t="s">
+      <c r="E208" s="1" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208">
-        <v>204</v>
-      </c>
-      <c r="B208" t="s">
-        <v>913</v>
-      </c>
-      <c r="C208" t="s">
-        <v>824</v>
-      </c>
-      <c r="D208" t="s">
+      <c r="F208" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="E208" t="s">
+      <c r="G208" t="s">
+        <v>885</v>
+      </c>
+      <c r="H208" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F208" t="s">
+      <c r="I208" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="G208" t="s">
-        <v>887</v>
-      </c>
-      <c r="H208" t="s">
+      <c r="J208" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="I208" t="s">
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>205</v>
+      </c>
+      <c r="B209" t="s">
+        <v>911</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="J208" t="s">
+      <c r="E209" s="1" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209">
-        <v>205</v>
-      </c>
-      <c r="B209" t="s">
-        <v>913</v>
-      </c>
-      <c r="C209" t="s">
-        <v>824</v>
-      </c>
-      <c r="D209" t="s">
+      <c r="F209" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="H209" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E209" t="s">
+      <c r="I209" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F209" t="s">
-        <v>891</v>
-      </c>
-      <c r="G209" t="s">
-        <v>891</v>
-      </c>
-      <c r="H209" t="s">
+      <c r="J209" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="I209" t="s">
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>206</v>
+      </c>
+      <c r="B210" t="s">
+        <v>911</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="J209" t="s">
+      <c r="E210" s="1" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210">
-        <v>206</v>
-      </c>
-      <c r="B210" t="s">
-        <v>913</v>
-      </c>
-      <c r="C210" t="s">
-        <v>824</v>
-      </c>
-      <c r="D210" t="s">
+      <c r="F210" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="G210" t="s">
         <v>896</v>
       </c>
-      <c r="E210" t="s">
+      <c r="H210" t="s">
+        <v>896</v>
+      </c>
+      <c r="I210" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="F210" t="s">
-        <v>896</v>
-      </c>
-      <c r="G210" t="s">
+      <c r="J210" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="H210" t="s">
-        <v>898</v>
-      </c>
-      <c r="I210" t="s">
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>207</v>
+      </c>
+      <c r="B211" t="s">
+        <v>911</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="G211" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="J210" t="s">
+      <c r="H211" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="I211" s="1" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211">
-        <v>207</v>
-      </c>
-      <c r="B211" t="s">
-        <v>913</v>
-      </c>
-      <c r="C211" t="s">
-        <v>824</v>
-      </c>
-      <c r="D211" t="s">
-        <v>896</v>
-      </c>
-      <c r="E211" t="s">
-        <v>897</v>
-      </c>
-      <c r="F211" t="s">
-        <v>896</v>
-      </c>
-      <c r="G211" t="s">
+      <c r="J211" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="H211" t="s">
-        <v>901</v>
-      </c>
-      <c r="I211" t="s">
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>208</v>
+      </c>
+      <c r="B212" t="s">
+        <v>911</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="J211" t="s">
+      <c r="E212" s="1" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212">
-        <v>208</v>
-      </c>
-      <c r="B212" t="s">
-        <v>913</v>
-      </c>
-      <c r="C212" t="s">
-        <v>824</v>
-      </c>
-      <c r="D212" t="s">
+      <c r="F212" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="G212" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="E212" t="s">
+      <c r="H212" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="I212" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="F212" t="s">
-        <v>904</v>
-      </c>
-      <c r="G212" t="s">
+      <c r="J212" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="H212" t="s">
-        <v>906</v>
-      </c>
-      <c r="I212" t="s">
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>209</v>
+      </c>
+      <c r="B213" t="s">
+        <v>911</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D213" t="s">
         <v>907</v>
       </c>
-      <c r="J212" t="s">
+      <c r="E213" s="1" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213">
-        <v>209</v>
-      </c>
-      <c r="B213" t="s">
-        <v>913</v>
-      </c>
-      <c r="C213" t="s">
-        <v>824</v>
-      </c>
-      <c r="D213" t="s">
+      <c r="F213" t="s">
+        <v>907</v>
+      </c>
+      <c r="G213" t="s">
+        <v>907</v>
+      </c>
+      <c r="H213" t="s">
+        <v>907</v>
+      </c>
+      <c r="I213" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="E213" t="s">
+      <c r="J213" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="F213" t="s">
-        <v>909</v>
-      </c>
-      <c r="G213" t="s">
-        <v>909</v>
-      </c>
-      <c r="H213" t="s">
-        <v>909</v>
-      </c>
-      <c r="I213" t="s">
-        <v>911</v>
-      </c>
-      <c r="J213" t="s">
-        <v>912</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CA4FDD-C543-4903-8BDA-550F0E3AA7E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BCE40-95F5-4A00-A23F-95FD7F1D41A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="920">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -4565,13 +4565,7 @@
     <t>child1_30.jpg</t>
   </si>
   <si>
-    <t>child1_27.jpg</t>
-  </si>
-  <si>
-    <t>child1_28.jpg</t>
-  </si>
-  <si>
-    <t>child1_29.jpg</t>
+    <t>Кран запірний</t>
   </si>
 </sst>
 </file>
@@ -7281,19 +7275,19 @@
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>265</v>
+        <v>918</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>311</v>
@@ -8940,7 +8934,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>129</v>
       </c>
@@ -8950,11 +8944,11 @@
       <c r="C126" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>504</v>
+      <c r="D126" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>919</v>
+        <v>515</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>504</v>
@@ -8972,7 +8966,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>130</v>
       </c>
@@ -8983,10 +8977,10 @@
         <v>316</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>920</v>
+        <v>515</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>509</v>
@@ -9009,10 +9003,10 @@
         <v>131</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>514</v>
@@ -9021,7 +9015,7 @@
         <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>514</v>
+        <v>919</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>739</v>
@@ -9041,10 +9035,10 @@
         <v>132</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>514</v>
@@ -9053,7 +9047,7 @@
         <v>515</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>514</v>
+        <v>919</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>740</v>
@@ -9073,10 +9067,10 @@
         <v>133</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>514</v>
@@ -9085,7 +9079,7 @@
         <v>515</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>514</v>
+        <v>919</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>522</v>
@@ -10225,16 +10219,16 @@
         <v>655</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>316</v>
+        <v>10</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>656</v>
+        <v>12</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>921</v>
+        <v>13</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>656</v>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BCE40-95F5-4A00-A23F-95FD7F1D41A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC50E8B-DBDF-4854-88AC-0A09A8BAAD89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="901">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3053,9 +3053,6 @@
     <t>child1_16.jpg</t>
   </si>
   <si>
-    <t>Муфта БРС ЄВРО з двостороннім розніманням (розривна) для гідравлічних систем</t>
-  </si>
-  <si>
     <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з двостороннім розніманням, що
 дозволяє реалізувати функцію «розриву» при аварійному натягу з’єднувального шланга.
 Підтримує функцію «Push-Pull» (підключення/відключення під тиском). З’єднувальні елементи —
@@ -3076,9 +3073,6 @@
     <t>child3_big_161.jpg</t>
   </si>
   <si>
-    <t>Муфта БРС ЄВРО з одностороннім розніманням для гідравлічних систем</t>
-  </si>
-  <si>
     <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням.
 З’єднувальні елементи — півмуфти (розетка та штуцер) виготовлені за європейським стандартом
 ISO 7241-A, завдяки чому повністю сумісні з іншими муфтами цього стандарту незалежно від їхніх
@@ -3087,23 +3081,6 @@
 Особливості та властивості:
 1. Матеріал напівмуфт - вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
 забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
-2. Номінальний робочий тиск - 250 bar</t>
-  </si>
-  <si>
-    <t>child3_small_162.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_162.jpg</t>
-  </si>
-  <si>
-    <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням.
-З’єднувальні елементи — півмуфти (розетка та штуцер) виготовлені за європейським стандартом
-ISO 7241-A, завдяки чому повністю сумісні з іншими муфтами цього стандарту незалежно від їхніх
-зовнішніх габаритних розмірів. Кожна півмуфта оснащена вбудованим клапаном, який запобігає витоку
-гідравлічної рідини під час роз’єднання.
-Особливості та властивості:
-1. Матеріал напівмуфт - вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
-забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
 2. Номінальний робочий тиск - 250 bar.
 3. Муфти комплектуються захисними гумовими ковпачками (жовтого або червоного кольору)</t>
   </si>
@@ -3112,25 +3089,6 @@
   </si>
   <si>
     <t>child3_big_163.jpg</t>
-  </si>
-  <si>
-    <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням.
-З’єднувальні елементи — півмуфти (розетка та штуцер) виготовлені за європейським стандартом
-ISO 7241-A, завдяки чому повністю сумісні з іншими муфтами цього стандарту незалежно від їхніх
-зовнішніх габаритних розмірів.
-Кожна півмуфта оснащена вбудованим клапаном, який запобігає витоку гідравлічної рідини під час
-роз’єднання.
-Особливості та властивості:
-1. Матеріал напівмуфт - вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
-забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
-2. Номінальний робочий тиск - 250 bar.
-3. Муфти комплектуються захисними ковпачками червоного кольору</t>
-  </si>
-  <si>
-    <t>child3_small_164.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_164.jpg</t>
   </si>
   <si>
     <t>Напівмуфта ніпель БРС ЄВРО для гідравлічних систем</t>
@@ -3154,9 +3112,6 @@
     <t>child3_big_165.jpg</t>
   </si>
   <si>
-    <t>Різьбова з’єднувальна муфта для гідравлічних систем</t>
-  </si>
-  <si>
     <t>З’єднувальні муфти з різьбовою фіксацією півмуфт, кожна з яких оснащена вбудованим шариковим
 клапаном, що запобігає витоку гідравлічної рідини під час роз’єднання. Відповідають міжнародному
 стандарту ISO 14541 та призначені для гідравлічних систем високого тиску.
@@ -3172,42 +3127,6 @@
   </si>
   <si>
     <t>child3_big_166.jpg</t>
-  </si>
-  <si>
-    <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням. Кожна
-півмуфта оснащена вбудованим клапаном, який запобігає витоку гідравлічної рідини під час
-роз’єднання.
-Особливості та властивості:
-1. Матеріал напівмуфт - вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
-забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
-2. Номінальний робочий тиск - 250 bar</t>
-  </si>
-  <si>
-    <t>child3_small_167.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_167.jpg</t>
-  </si>
-  <si>
-    <t>child3_small_168.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_168.jpg</t>
-  </si>
-  <si>
-    <t>Муфта швидкороз'ємного з’єднання конструктивно виконана з одностороннім розніманням. Кожна
-півмуфта оснащена вбудованим клапаном, який запобігає витоку гідравлічної рідини під час
-роз’єднання.
-Особливості та властивості:
-1. Матеріал напівмуфт - вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
-забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
-2. Номінальний робочий тиск - 250 bar.</t>
-  </si>
-  <si>
-    <t>child3_small_169.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_169.jpg</t>
   </si>
   <si>
     <t>18a</t>
@@ -4544,21 +4463,6 @@
     <t>Багатоцільові рукави та трубки</t>
   </si>
   <si>
-    <t>Муфта БРС ЄВРО з двостороннім розніманням для гідравлічних систем зовнішня різьба</t>
-  </si>
-  <si>
-    <t>Муфта БРС ЄВРО з одностороннім розніманням для гідравлічних систем внутрішня різьба</t>
-  </si>
-  <si>
-    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 1</t>
-  </si>
-  <si>
-    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 2</t>
-  </si>
-  <si>
-    <t>Муфта ШРЗ з двостороннім розніманням для гідравлічних систем 3</t>
-  </si>
-  <si>
     <t>З’єднувач кутовий з зовнішньою та внутрішньою різьбою для пневмо- та гідросистем</t>
   </si>
   <si>
@@ -4566,6 +4470,15 @@
   </si>
   <si>
     <t>Кран запірний</t>
+  </si>
+  <si>
+    <t>Муфта з’єднувальна муфта для гідравлічних систем</t>
+  </si>
+  <si>
+    <t>Муфта ШРЗ з двостороннім розніманням (розривна) для гідравлічних систем</t>
+  </si>
+  <si>
+    <t>Муфта ШРЗ з одностороннім розніманням  (розривна) для гідравлічних систем</t>
   </si>
 </sst>
 </file>
@@ -4925,7 +4838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5402,10 +5315,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -6074,7 +5987,7 @@
         <v>148</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>149</v>
@@ -6106,7 +6019,7 @@
         <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>152</v>
@@ -6522,10 +6435,10 @@
         <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>759</v>
+        <v>742</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>210</v>
@@ -6554,10 +6467,10 @@
         <v>157</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>776</v>
+        <v>759</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>760</v>
+        <v>743</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>212</v>
@@ -6746,10 +6659,10 @@
         <v>218</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>239</v>
@@ -7284,7 +7197,7 @@
         <v>317</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>317</v>
@@ -7316,13 +7229,13 @@
         <v>317</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>318</v>
@@ -7348,13 +7261,13 @@
         <v>317</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>318</v>
@@ -7380,13 +7293,13 @@
         <v>317</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>323</v>
@@ -7412,13 +7325,13 @@
         <v>317</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>323</v>
@@ -8058,16 +7971,16 @@
         <v>328</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="J98" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8090,16 +8003,16 @@
         <v>328</v>
       </c>
       <c r="G99" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="J99" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8122,16 +8035,16 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="J100" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8154,16 +8067,16 @@
         <v>328</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="J101" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -9015,10 +8928,10 @@
         <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>516</v>
@@ -9047,10 +8960,10 @@
         <v>515</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>519</v>
@@ -9079,7 +8992,7 @@
         <v>515</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>522</v>
@@ -9105,7 +9018,7 @@
         <v>435</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>527</v>
@@ -9137,7 +9050,7 @@
         <v>435</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>527</v>
@@ -9178,10 +9091,10 @@
         <v>540</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>542</v>
@@ -9210,10 +9123,10 @@
         <v>540</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>545</v>
@@ -9242,10 +9155,10 @@
         <v>540</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>548</v>
@@ -9562,10 +9475,10 @@
         <v>540</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>583</v>
@@ -9626,10 +9539,10 @@
         <v>540</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>589</v>
@@ -9658,10 +9571,10 @@
         <v>540</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>591</v>
@@ -9690,10 +9603,10 @@
         <v>540</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>593</v>
@@ -9946,21 +9859,21 @@
         <v>623</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="H157" s="1" t="s">
+      <c r="I157" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="I157" s="1" t="s">
+      <c r="J157" t="s">
         <v>627</v>
-      </c>
-      <c r="J157" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>434</v>
@@ -9978,21 +9891,21 @@
         <v>623</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
       <c r="H158" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J158" t="s">
         <v>630</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="J158" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>434</v>
@@ -10010,21 +9923,21 @@
         <v>623</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>913</v>
+        <v>631</v>
       </c>
       <c r="H159" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="J159" t="s">
         <v>634</v>
-      </c>
-      <c r="J159" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>434</v>
@@ -10042,36 +9955,36 @@
         <v>623</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>629</v>
+        <v>898</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" t="s">
         <v>637</v>
       </c>
-      <c r="J160" t="s">
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
-        <v>165</v>
-      </c>
       <c r="B161" s="1" t="s">
-        <v>434</v>
+        <v>10</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>435</v>
+        <v>11</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>623</v>
+        <v>12</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>624</v>
+        <v>13</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>639</v>
@@ -10087,58 +10000,58 @@
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="1">
-        <v>166</v>
+      <c r="A162" s="1" t="s">
+        <v>643</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>434</v>
+        <v>10</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>435</v>
+        <v>11</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>623</v>
+        <v>12</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>624</v>
+        <v>13</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>623</v>
+        <v>95</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>643</v>
+        <v>728</v>
       </c>
       <c r="H162" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I162" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="I162" s="1" t="s">
+      <c r="J162" t="s">
         <v>645</v>
       </c>
-      <c r="J162" t="s">
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
-        <v>167</v>
-      </c>
       <c r="B163" s="1" t="s">
-        <v>434</v>
+        <v>10</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>435</v>
+        <v>11</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>623</v>
+        <v>12</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>624</v>
+        <v>13</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>623</v>
+        <v>95</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>914</v>
+        <v>729</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>647</v>
@@ -10151,552 +10064,552 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="1">
-        <v>168</v>
+      <c r="A164" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>434</v>
+        <v>214</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>435</v>
+        <v>215</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>623</v>
+        <v>216</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>624</v>
+        <v>217</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>623</v>
+        <v>218</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>915</v>
+        <v>651</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J164" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
-        <v>169</v>
+      <c r="A165" s="1" t="s">
+        <v>655</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>434</v>
+        <v>214</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>435</v>
+        <v>215</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>623</v>
+        <v>216</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>624</v>
+        <v>217</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>623</v>
+        <v>218</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>916</v>
+        <v>656</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="J165" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>11</v>
+        <v>215</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>656</v>
+        <v>218</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="J166" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>11</v>
+        <v>215</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>745</v>
+        <v>666</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>96</v>
+        <v>667</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="J167" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>11</v>
+        <v>215</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>12</v>
+        <v>328</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>13</v>
+        <v>329</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>746</v>
+        <v>671</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="J168" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>667</v>
+      <c r="A169" s="1">
+        <v>170</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>214</v>
+        <v>536</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>215</v>
+        <v>537</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>216</v>
+        <v>691</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>217</v>
+        <v>690</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>218</v>
+        <v>691</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>669</v>
+        <v>693</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>670</v>
+        <v>694</v>
       </c>
       <c r="J169" t="s">
-        <v>671</v>
+        <v>695</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>672</v>
+      <c r="A170" s="1">
+        <v>171</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>214</v>
+        <v>536</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>215</v>
+        <v>537</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>216</v>
+        <v>691</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>217</v>
+        <v>690</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>218</v>
+        <v>691</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>674</v>
+        <v>697</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>675</v>
+        <v>698</v>
       </c>
       <c r="J170" t="s">
-        <v>676</v>
+        <v>699</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>677</v>
+      <c r="A171" s="1">
+        <v>172</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>214</v>
+        <v>536</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>215</v>
+        <v>537</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>216</v>
+        <v>691</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>217</v>
+        <v>690</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>218</v>
+        <v>691</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>678</v>
+        <v>700</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="J171" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
-        <v>682</v>
+      <c r="A172" s="1">
+        <v>173</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>214</v>
+        <v>536</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>215</v>
+        <v>537</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>216</v>
+        <v>691</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>217</v>
+        <v>690</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>218</v>
+        <v>691</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="J172" t="s">
-        <v>686</v>
+        <v>705</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>687</v>
+      <c r="A173" s="1">
+        <v>174</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>214</v>
+        <v>536</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>215</v>
+        <v>537</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>328</v>
+        <v>691</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>329</v>
+        <v>690</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>328</v>
+        <v>691</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="J173" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>536</v>
+        <v>434</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>707</v>
+        <v>527</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>709</v>
+        <v>749</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>710</v>
+        <v>750</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="J174" t="s">
-        <v>712</v>
+        <v>734</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>536</v>
+        <v>214</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>537</v>
+        <v>215</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>708</v>
+        <v>216</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>707</v>
+        <v>217</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>708</v>
+        <v>218</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>713</v>
+        <v>739</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>714</v>
+        <v>740</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>715</v>
+        <v>737</v>
       </c>
       <c r="J175" t="s">
-        <v>716</v>
+        <v>738</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>536</v>
+        <v>10</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>537</v>
+        <v>11</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>708</v>
+        <v>155</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>707</v>
+        <v>156</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>708</v>
+        <v>157</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="J176" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>536</v>
+        <v>434</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>707</v>
+        <v>527</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>717</v>
+        <v>751</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="J177" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>536</v>
+        <v>10</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>537</v>
+        <v>11</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>708</v>
+        <v>146</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>707</v>
+        <v>147</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>708</v>
+        <v>148</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>709</v>
+        <v>755</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>710</v>
+        <v>756</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>723</v>
+        <v>757</v>
       </c>
       <c r="J178" t="s">
-        <v>724</v>
+        <v>758</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>434</v>
+        <v>10</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>435</v>
+        <v>11</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>749</v>
+        <v>404</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>527</v>
+        <v>405</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>765</v>
+        <v>404</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B180" t="s">
-        <v>214</v>
+        <v>10</v>
       </c>
       <c r="C180" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
       <c r="D180" t="s">
-        <v>216</v>
+        <v>404</v>
       </c>
       <c r="E180" t="s">
-        <v>217</v>
+        <v>405</v>
       </c>
       <c r="F180" t="s">
-        <v>218</v>
+        <v>404</v>
       </c>
       <c r="G180" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="I180" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="J180" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>10</v>
@@ -10704,197 +10617,197 @@
       <c r="C181" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>155</v>
+      <c r="D181" t="s">
+        <v>404</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>156</v>
+        <v>405</v>
       </c>
       <c r="F181" t="s">
-        <v>157</v>
+        <v>404</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="J181" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>435</v>
+        <v>316</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>527</v>
+        <v>775</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>10</v>
+        <v>315</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>146</v>
+        <v>774</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>147</v>
+        <v>775</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>148</v>
+        <v>776</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="J183" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>10</v>
+        <v>315</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>404</v>
+        <v>774</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>405</v>
+        <v>775</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>404</v>
+        <v>776</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>778</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="J184" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>10</v>
+        <v>315</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>404</v>
+        <v>774</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>405</v>
+        <v>775</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>404</v>
+        <v>787</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="J185" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>10</v>
+        <v>434</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>11</v>
+        <v>435</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>404</v>
+        <v>791</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>405</v>
+        <v>792</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>404</v>
+        <v>791</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="J186" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>315</v>
+        <v>434</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>316</v>
+        <v>435</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>791</v>
@@ -10903,30 +10816,30 @@
         <v>792</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="J187" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>315</v>
+        <v>434</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>316</v>
+        <v>435</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>791</v>
@@ -10935,819 +10848,659 @@
         <v>792</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="J188" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>315</v>
+        <v>894</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>316</v>
+        <v>805</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>793</v>
+        <v>806</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="J189" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>315</v>
+        <v>894</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>316</v>
+        <v>805</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="F190" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="J190" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>434</v>
+        <v>894</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>435</v>
+        <v>805</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>434</v>
+        <v>894</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>435</v>
+        <v>805</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>434</v>
+        <v>894</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>435</v>
+        <v>805</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B194" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B195" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B196" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B197" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B199" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B200" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>824</v>
+        <v>857</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B202" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>824</v>
+        <v>857</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="G202" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B203" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>823</v>
+        <v>866</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>824</v>
+        <v>867</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>823</v>
+        <v>868</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B204" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>823</v>
+        <v>872</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>824</v>
+        <v>873</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>823</v>
+        <v>872</v>
       </c>
       <c r="G204" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B205" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>823</v>
+        <v>877</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>824</v>
+        <v>878</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>823</v>
+        <v>877</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B206" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="G206" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B207" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="G208" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="1">
-        <v>205</v>
-      </c>
-      <c r="B209" t="s">
-        <v>911</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="J209" s="1" t="s">
         <v>893</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="1">
-        <v>206</v>
-      </c>
-      <c r="B210" t="s">
-        <v>911</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="G210" t="s">
-        <v>896</v>
-      </c>
-      <c r="H210" t="s">
-        <v>896</v>
-      </c>
-      <c r="I210" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="J210" s="1" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="1">
-        <v>207</v>
-      </c>
-      <c r="B211" t="s">
-        <v>911</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="I211" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="J211" s="1" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="1">
-        <v>208</v>
-      </c>
-      <c r="B212" t="s">
-        <v>911</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="J212" s="1" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="1">
-        <v>209</v>
-      </c>
-      <c r="B213" t="s">
-        <v>911</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D213" t="s">
-        <v>907</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="F213" t="s">
-        <v>907</v>
-      </c>
-      <c r="G213" t="s">
-        <v>907</v>
-      </c>
-      <c r="H213" t="s">
-        <v>907</v>
-      </c>
-      <c r="I213" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="J213" s="1" t="s">
-        <v>910</v>
       </c>
     </row>
   </sheetData>
